--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -149,10 +149,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -769,73 +769,73 @@
         <v>186.2</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>90</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>24.3</v>
+        <v>28.2</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>84.3</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="H4" s="8" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>9.9</v>
+        <v>2.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>20.2</v>
+        <v>2.2</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>20.1</v>
+        <v>26.1</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>23.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>28.7</v>
+        <v>28.2</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.8</v>
+        <v>27.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>168.9</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>25.2</v>
+        <v>25.8</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>811.8</v>
+        <v>81.8</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>403.5</v>
+        <v>438.5</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>32.6</v>
@@ -859,23 +859,23 @@
       <c r="E5" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>16.8</v>
+        <v>6.2</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>32.5</v>
+        <v>3.5</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>18.9</v>
@@ -884,10 +884,10 @@
         <v>18.8</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>28.6</v>
+        <v>21.6</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0.2</v>
@@ -902,22 +902,22 @@
         <v>27.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>156.6</v>
+        <v>56.6</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>27.2</v>
+        <v>87.2</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="X5" s="8" t="n">
-        <v>27.8</v>
+        <v>24.6</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>8.199999999999999</v>
@@ -936,15 +936,15 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>422.3</v>
+        <v>22.3</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>34.2</v>
+        <v>34.8</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -954,10 +954,10 @@
         <v>17.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>11.6</v>
+        <v>4.6</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -965,14 +965,14 @@
       <c r="L6" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>20</v>
+      <c r="M6" s="8" t="n">
+        <v>66</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0</v>
@@ -987,13 +987,13 @@
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>55.2</v>
+        <v>51.8</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>28.7</v>
+        <v>28.2</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>23.7</v>
@@ -1005,7 +1005,7 @@
         <v>66.40000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>4.1</v>
+        <v>13.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4335.1</v>
+        <v>4778.5</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>34.7</v>
@@ -1029,8 +1029,8 @@
       <c r="E7" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="F7" s="10" t="n">
-        <v>27</v>
+      <c r="F7" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>15.4</v>
@@ -1039,10 +1039,10 @@
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>43.3</v>
+        <v>2.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.9</v>
+        <v>7.9</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
@@ -1051,16 +1051,16 @@
         <v>20.1</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>20.1</v>
+        <v>2.1</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>35.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>34.2</v>
@@ -1069,7 +1069,7 @@
         <v>25.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>27.1</v>
+        <v>22.1</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>50.6</v>
@@ -1081,16 +1081,16 @@
         <v>29.5</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>24.4</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>27.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>66.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>13.8</v>
+        <v>438.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1106,28 +1106,28 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>299</v>
+        <v>299.6</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>34.41</v>
       </c>
-      <c r="E8" s="11" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>27.6</v>
+      <c r="E8" s="8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>2.6</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="H8" s="8" t="n">
-        <v>119</v>
+      <c r="H8" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>30.9</v>
@@ -1145,28 +1145,28 @@
         <v>96.5</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Q8" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q8" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>25.1</v>
+        <v>23.1</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>10.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>21.9</v>
+        <v>24.9</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>26.1</v>
@@ -1175,7 +1175,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0.6</v>
+        <v>26.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1196,10 +1196,10 @@
       <c r="D9" s="10" t="n">
         <v>164.8</v>
       </c>
-      <c r="E9" s="12" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="F9" s="10" t="n">
+      <c r="E9" s="11" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F9" s="11" t="n">
         <v>130.8</v>
       </c>
       <c r="G9" s="3" t="n">
@@ -1215,22 +1215,22 @@
         <v>27.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>30.9</v>
+        <v>3.9</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>100.2</v>
+        <v>16.2</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>115.8</v>
+        <v>15.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1894.5</v>
+        <v>494.5</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>149.6</v>
@@ -1242,7 +1242,7 @@
         <v>135.7</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>229.9</v>
+        <v>329.9</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>81</v>
@@ -1259,7 +1259,13 @@
       <c r="Y9" s="3" t="n">
         <v>388.8</v>
       </c>
-      <c r="Z9" s="3" t="n"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222424272
+777
+</t>
+        </is>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1279,17 +1285,17 @@
       <c r="D10" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="E10" s="12" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F10" s="10" t="n">
+      <c r="E10" s="11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F10" s="11" t="n">
         <v>26.2</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>17.9</v>
+        <v>12.9</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>3.3</v>
@@ -1297,48 +1303,54 @@
       <c r="J10" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n">
-        <v>20</v>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+2221
+</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="N10" s="8" t="n">
+      <c r="N10" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>98.90000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>29.9</v>
       </c>
-      <c r="R10" s="8" t="n">
+      <c r="R10" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>27.1</v>
+        <v>2.1</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>66</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>16.2</v>
+        <v>1.2</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="W10" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W10" s="3" t="n">
         <v>23.4</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>77.8</v>
+        <v>272.8</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>41.6</v>
@@ -1359,26 +1371,26 @@
       <c r="C11" s="3" t="n">
         <v>265.6</v>
       </c>
-      <c r="D11" s="3" t="n">
-        <v>20.1</v>
+      <c r="D11" s="10" t="n">
+        <v>30.1</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="10" t="n">
         <v>24.9</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>10.3</v>
+        <v>1.3</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="I11" s="8" t="n">
-        <v>86.59999999999999</v>
+      <c r="I11" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>82.8</v>
+        <v>2.8</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
@@ -1389,11 +1401,16 @@
       <c r="M11" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="N11" s="8" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>92.3</v>
+      <c r="N11" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">897
+505
+1799
+</t>
+        </is>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.6</v>
@@ -1401,32 +1418,36 @@
       <c r="Q11" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R11" s="8" t="n">
+      <c r="R11" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="S11" s="8" t="n">
+      <c r="S11" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="U11" s="8" t="n">
+        <v>720.6</v>
+      </c>
+      <c r="U11" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V11" s="8" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="W11" s="8" t="n">
+      <c r="V11" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W11" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>24</v>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+744
+</t>
+        </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1442,15 +1463,15 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>347.1</v>
-      </c>
-      <c r="D12" s="3" t="n">
+        <v>342.4</v>
+      </c>
+      <c r="D12" s="10" t="n">
         <v>31.8</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="10" t="n">
         <v>27.2</v>
       </c>
       <c r="G12" s="3" t="n">
@@ -1462,11 +1483,11 @@
       <c r="I12" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="J12" s="8" t="n">
-        <v>44.6</v>
+      <c r="J12" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>23.3</v>
@@ -1475,10 +1496,10 @@
         <v>23</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>27.9</v>
+        <v>2.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>97.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.5</v>
@@ -1496,22 +1517,22 @@
         <v>57.8</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>19.8</v>
+        <v>1.8</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="W12" s="8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W12" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>76.7</v>
+        <v>7.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>5.7</v>
+        <v>57.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1527,16 +1548,16 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1428.6</v>
-      </c>
-      <c r="D13" s="3" t="n">
+        <v>428.6</v>
+      </c>
+      <c r="D13" s="10" t="n">
         <v>32.8</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>96.59999999999999</v>
+      <c r="E13" s="12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>26.6</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>12.4</v>
@@ -1548,13 +1569,13 @@
         <v>3.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="8" t="n">
-        <v>22.1</v>
+      <c r="L13" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>21.9</v>
@@ -1563,10 +1584,10 @@
         <v>26.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>98</v>
+        <v>9.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>10.4</v>
+        <v>26.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>32.6</v>
@@ -1583,8 +1604,8 @@
       <c r="U13" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="V13" s="8" t="n">
-        <v>28</v>
+      <c r="V13" s="3" t="n">
+        <v>28.6</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>24.8</v>
@@ -1593,10 +1614,10 @@
         <v>29.3</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>23.1</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1614,47 +1635,47 @@
       <c r="C14" s="3" t="n">
         <v>190.3</v>
       </c>
-      <c r="D14" s="8" t="n">
-        <v>20.7</v>
+      <c r="D14" s="10" t="n">
+        <v>30.7</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="10" t="n">
         <v>26.3</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>20.3</v>
+        <v>2.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>52.1</v>
+        <v>22.1</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>22.4</v>
+        <v>2.4</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>22.1</v>
+        <v>2.1</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>97.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>22.4</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>21.1</v>
@@ -1669,10 +1690,10 @@
         <v>2.9</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>21.6</v>
+        <v>26</v>
+      </c>
+      <c r="W14" s="8" t="n">
+        <v>41.6</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>25.5</v>
@@ -1681,7 +1702,7 @@
         <v>96</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1697,22 +1718,22 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>359.6</v>
-      </c>
-      <c r="D15" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D15" s="10" t="n">
         <v>32.5</v>
       </c>
-      <c r="E15" s="8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="F15" s="3" t="n">
+      <c r="E15" s="12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F15" s="10" t="n">
         <v>26.7</v>
       </c>
-      <c r="G15" s="8" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>419.6</v>
+      <c r="G15" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>2.4</v>
@@ -1721,7 +1742,7 @@
         <v>3.9</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>21.6</v>
@@ -1733,7 +1754,7 @@
         <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>180</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0</v>
@@ -1745,7 +1766,7 @@
         <v>25.8</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>89.2</v>
+        <v>29.2</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>61.7</v>
@@ -1757,7 +1778,7 @@
         <v>28.7</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>24.8</v>
+        <v>4.8</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>28.8</v>
@@ -1766,7 +1787,7 @@
         <v>73.09999999999999</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0.9</v>
+        <v>20.9</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1784,20 +1805,20 @@
       <c r="C16" s="3" t="n">
         <v>1591.2</v>
       </c>
-      <c r="D16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="12" t="n">
-        <v>105.5</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>131.7</v>
+      <c r="D16" s="10" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>1317.2</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>52.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>99.2</v>
+        <v>929.2</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.5</v>
@@ -1805,19 +1826,37 @@
       <c r="J16" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">790691
+22
+5682
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>10.6</v>
+      </c>
       <c r="M16" s="3" t="n">
-        <v>109.5</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>130.7</v>
-      </c>
-      <c r="O16" s="3" t="n">
-        <v>490.1</v>
+        <v>19.5</v>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">791727
+14
+000
+</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11722
+77218
+</t>
+        </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>148.7</v>
@@ -1829,24 +1868,42 @@
         <v>136.1</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>331.8</v>
+        <v>31.8</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>76.59999999999999</v>
       </c>
-      <c r="V16" s="3" t="n">
-        <v>133.7</v>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v>120.7</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>142.5</v>
-      </c>
-      <c r="Y16" s="3" t="n">
-        <v>407.4</v>
-      </c>
-      <c r="Z16" s="3" t="n"/>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7277978
+7566
+</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22414
+8711011466 7
+</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36595
+99781
+</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5555
+5721
+</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>741.1</v>
+      </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1861,22 +1918,22 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>318.2</v>
-      </c>
-      <c r="D17" s="12" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="D17" s="10" t="n">
         <v>31.6</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="11" t="n">
         <v>21.1</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F17" s="10" t="n">
         <v>26.3</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H17" s="3" t="n">
-        <v>19.8</v>
+      <c r="H17" s="8" t="n">
+        <v>292.8</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>2.3</v>
@@ -1887,20 +1944,20 @@
       <c r="K17" s="3" t="n">
         <v>36.8</v>
       </c>
-      <c r="L17" s="8" t="n">
-        <v>10.6</v>
+      <c r="L17" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>26.1</v>
+      <c r="N17" s="8" t="n">
+        <v>30.7</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P17" s="8" t="n">
-        <v>10.4</v>
+        <v>490.1</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>29.7</v>
@@ -1908,26 +1965,26 @@
       <c r="R17" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="S17" s="8" t="n">
-        <v>72.2</v>
+      <c r="S17" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="8" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="W17" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="W17" s="3" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="X17" s="3" t="n">
-        <v>28.5</v>
+      <c r="X17" s="8" t="n">
+        <v>42.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>81.5</v>
+        <v>47.6</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>6.9</v>
@@ -1948,17 +2005,17 @@
       <c r="C18" s="3" t="n">
         <v>368</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E18" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>10.9</v>
+        <v>16.9</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>20.4</v>
@@ -1967,20 +2024,30 @@
         <v>2.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K18" s="3" t="n"/>
+        <v>4.3</v>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+222
+</t>
+        </is>
+      </c>
       <c r="L18" s="3" t="n">
-        <v>22.1</v>
+        <v>24.4</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v>92.3</v>
+        <v>26.1</v>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27844
+171719
+</t>
+        </is>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
@@ -1988,32 +2055,40 @@
       <c r="Q18" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="R18" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>27.7</v>
+        <v>7.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="U18" s="8" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>28.5</v>
+        <v>26.7</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X18" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="Y18" s="3" t="n">
-        <v>71.7</v>
+        <v>4.1</v>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7444
+1779 7
+</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09442
+77 7
+</t>
+        </is>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>1.1</v>
+        <v>17.1</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2031,13 +2106,13 @@
       <c r="C19" s="3" t="n">
         <v>265.6</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="3" t="n">
         <v>30.4</v>
       </c>
-      <c r="E19" s="10" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="F19" s="10" t="n">
+      <c r="E19" s="8" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="G19" s="3" t="n">
@@ -2053,19 +2128,19 @@
         <v>2.8</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>10.4</v>
+        <v>1.4</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>21.4</v>
+        <v>2.3</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>26.3</v>
+        <v>24.8</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>97.59999999999999</v>
+        <v>297.3</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.6</v>
@@ -2085,17 +2160,17 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="8" t="n">
-        <v>24.3</v>
+      <c r="V19" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>22.9</v>
+        <v>24.4</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>21.4</v>
+        <v>2.9</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>22</v>
+        <v>7218.7</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>3.3</v>
@@ -2116,13 +2191,13 @@
       <c r="C20" s="3" t="n">
         <v>365.9</v>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="E20" s="10" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F20" s="10" t="n">
+      <c r="E20" s="12" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F20" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="G20" s="3" t="n">
@@ -2135,26 +2210,24 @@
         <v>2.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>22.3</v>
+        <v>21.6</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>25.4</v>
+        <v>26.3</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>9.6</v>
+      </c>
+      <c r="P20" s="3" t="n"/>
       <c r="Q20" s="3" t="n">
         <v>30.7</v>
       </c>
@@ -2168,19 +2241,19 @@
         <v>62.3</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>16.6</v>
+        <v>1.6</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>27.3</v>
+        <v>24.3</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>23.8</v>
+        <v>2.9</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>9.1</v>
@@ -2201,13 +2274,13 @@
       <c r="C21" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D21" s="10" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E21" s="10" t="n">
+      <c r="D21" s="12" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="E21" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="F21" s="10" t="n">
+      <c r="F21" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2223,22 +2296,22 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>21.6</v>
+        <v>2.6</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>99</v>
+        <v>986</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>30.6</v>
@@ -2250,22 +2323,22 @@
         <v>31.2</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>71.2</v>
+        <v>4.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>12.6</v>
+        <v>1.6</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>27.8</v>
+        <v>2.3</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>24.6</v>
+        <v>23.8</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>28.9</v>
+        <v>7.2</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>772.3</v>
+        <v>75</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>8.4</v>
@@ -2284,22 +2357,22 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>399.3</v>
-      </c>
-      <c r="D22" s="10" t="n">
+        <v>395.3</v>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>32.9</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E22" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="F22" s="10" t="n">
-        <v>27</v>
+      <c r="F22" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>11.8</v>
+        <v>14.8</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>19.8</v>
+        <v>12.8</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.5</v>
@@ -2308,22 +2381,25 @@
         <v>4.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="8" t="n">
-        <v>21.6</v>
+        <v>0.6</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>21</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>24.7</v>
+        <v>25.6</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>0.4</v>
+        <v>99.59999999999999</v>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68 2
+</t>
+        </is>
       </c>
       <c r="Q22" s="3" t="n">
         <v>32.4</v>
@@ -2334,23 +2410,26 @@
       <c r="S22" s="3" t="n">
         <v>89.3</v>
       </c>
-      <c r="T22" s="3" t="n">
-        <v>60.5</v>
+      <c r="T22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65 2
+</t>
+        </is>
       </c>
       <c r="U22" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>26.5</v>
+        <v>27.8</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>29.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>86</v>
+        <v>72.3</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>4.9</v>
@@ -2369,43 +2448,62 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1739.6</v>
-      </c>
-      <c r="D23" s="12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>132.4</v>
+        <v>739.6</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>432.4</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>50.3</v>
       </c>
-      <c r="H23" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>19.3</v>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41444444
+1
+8684
+</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27955
+42
+12141
+</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+1141089
+</t>
+        </is>
       </c>
       <c r="K23" s="3" t="n">
         <v>7.7</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>7.7</v>
+        <v>18.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="O23" s="3" t="n">
-        <v>1489.4</v>
+        <v>24.7</v>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">418686866
+50756012
+1441
+</t>
+        </is>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.2</v>
@@ -2417,28 +2515,28 @@
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1146.8</v>
+        <v>146.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>395.7</v>
+        <v>325.7</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>792.4</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>134.4</v>
+        <v>86.5</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>120.3</v>
+        <v>24.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>1408.1</v>
+        <v>2.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>3940.4</v>
+        <v>860.6</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2454,73 +2552,81 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>343.9</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>26.5</v>
+        <v>739.6</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>432.4</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>10.1</v>
+        <v>50.3</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>3.9</v>
+        <v>19.3</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="L24" s="8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="M24" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="N24" s="8" t="n">
-        <v>26.8</v>
+      <c r="L24" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6169690911
+2929
+</t>
+        </is>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q24" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>29.4</v>
+        <v>2.2</v>
+      </c>
+      <c r="Q24" s="8" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="R24" s="8" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="S24" s="8" t="n">
+        <v>46.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>325.7</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>26.9</v>
+        <v>79.40000000000001</v>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v>34.4</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>22.2</v>
+        <v>2.3</v>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74950
+448468
+</t>
+        </is>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>79.8</v>
+        <v>399</v>
       </c>
       <c r="Z24" s="3" t="n">
         <v>7.3</v>
@@ -2539,31 +2645,31 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>106.7</v>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F25" s="10" t="n">
-        <v>23.5</v>
+        <v>34.9</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>26.5</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.2</v>
+        <v>19.3</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>21.6</v>
@@ -2571,41 +2677,41 @@
       <c r="M25" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="N25" s="3" t="n">
-        <v>25.4</v>
+      <c r="N25" s="8" t="n">
+        <v>26.8</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>97.90000000000001</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="R25" s="8" t="n">
-        <v>146.1</v>
+        <v>31.1</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>156.1</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>28.7</v>
+        <v>29.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>5.3</v>
+        <v>15.9</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>244.1</v>
+        <v>26.9</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="X25" s="3" t="n">
-        <v>26.8</v>
+      <c r="X25" s="8" t="n">
+        <v>40.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>79.8</v>
+        <v>2.8</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>7.3</v>
@@ -2624,76 +2730,92 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="D26" s="10" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="F26" s="10" t="n">
-        <v>23.1</v>
+        <v>16.7</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>23.5</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>14.1</v>
+        <v>5.7</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="I26" s="3" t="n">
-        <v>0.5</v>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215852
+147
+</t>
+        </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>0.2</v>
+        <v>6.8</v>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+77
+</t>
+        </is>
       </c>
       <c r="L26" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="V26" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="M26" s="3" t="n">
-        <v>924</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>1297</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>22.8</v>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7771717
+11811408 7
+</t>
+        </is>
       </c>
       <c r="X26" s="3" t="n">
-        <v>27.1</v>
+        <v>2.2</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>87.7</v>
       </c>
-      <c r="Z26" s="3" t="n">
-        <v>3.8</v>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+893
+</t>
+        </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2709,76 +2831,68 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>322</v>
-      </c>
-      <c r="D27" s="10" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F27" s="10" t="n">
-        <v>25.5</v>
+        <v>90</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>23.1</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>9.9</v>
+        <v>4.1</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="I27" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
       <c r="L27" s="3" t="n">
-        <v>24.4</v>
+        <v>21.4</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="N27" s="8" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>100</v>
-      </c>
+        <v>2.4</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="O27" s="3" t="n"/>
       <c r="P27" s="3" t="n">
-        <v>10.4</v>
+        <v>8</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>28.8</v>
+        <v>4.3</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>89</v>
+        <v>23.3</v>
+      </c>
+      <c r="S27" s="8" t="n">
+        <v>86</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>73.2</v>
+        <v>926</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>10.5</v>
+        <v>2.4</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>29</v>
+        <v>26.8</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>91.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2794,76 +2908,84 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2990.7</v>
-      </c>
-      <c r="D28" s="10" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F28" s="10" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="G28" s="8" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>19.1</v>
+        <v>322</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138938798
+305
+</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="8" t="n">
-        <v>20.9</v>
+        <v>2</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>20.6</v>
+        <v>26.5</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="O28" s="3" t="n">
-        <v>4.9</v>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
+2923
+</t>
+        </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.8</v>
+        <v>16.4</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>31.2</v>
+        <v>28.8</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>27.2</v>
+        <v>29</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>60.2</v>
+        <v>73.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.1</v>
+        <v>1.5</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>28.6</v>
+        <v>26.9</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>24.4</v>
+        <v>2.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>28.4</v>
+        <v>27.1</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>81.8</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>6.4</v>
+        <v>2.4</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2879,34 +3001,34 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3468.1</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E29" s="10" t="n">
+        <v>290.7</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E29" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="F29" s="10" t="n">
-        <v>26</v>
+      <c r="F29" s="3" t="n">
+        <v>26.1</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="H29" s="8" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H29" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>28.1</v>
+        <v>21.9</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>20.6</v>
@@ -2914,41 +3036,45 @@
       <c r="N29" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="O29" s="3" t="n">
-        <v>195.3</v>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
+2923
+</t>
+        </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Q29" s="8" t="n">
-        <v>25.3</v>
+        <v>0.5</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>31.2</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>23.6</v>
+        <v>24.8</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>28</v>
+        <v>27.2</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>27</v>
+        <v>60.2</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>14.2</v>
+        <v>18.1</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>22.4</v>
+        <v>28.6</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>36.1</v>
+        <v>29.1</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>724.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2964,76 +3090,76 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1056.2</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>145.2</v>
-      </c>
-      <c r="E30" s="12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>124.2</v>
+        <v>846.2</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>26</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>119.2</v>
+        <v>12.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>111</v>
+        <v>2.6</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>38.8</v>
+        <v>8.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>106.5</v>
+        <v>21.1</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1159.2</v>
+        <v>20.6</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>487.6</v>
+        <v>95.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>1185.8</v>
+        <v>825.3</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>120.7</v>
+        <v>23.6</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>140.9</v>
+        <v>28</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>396.8</v>
+        <v>8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>14.2</v>
+        <v>4.1</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>126.1</v>
+        <v>2.4</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>21.3</v>
+        <v>24.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>135.8</v>
+        <v>2.4</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>90.8</v>
+        <v>4.2</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3049,76 +3175,76 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>211.2</v>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>24.8</v>
+        <v>15.2</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>452.1</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>2.2</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>96.59999999999999</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>38.8</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>21.3</v>
+        <v>16.5</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>21</v>
+        <v>15.1</v>
       </c>
       <c r="N31" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>97.5</v>
+        <v>487.6</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>28.2</v>
+        <v>2.8</v>
+      </c>
+      <c r="Q31" s="8" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="R31" s="8" t="n">
+        <v>280.7</v>
+      </c>
+      <c r="S31" s="8" t="n">
+        <v>40.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="W31" s="8" t="n">
-        <v>15.9</v>
+        <v>396.8</v>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>27.2</v>
+        <v>4.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>4.2</v>
+        <v>44.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>5.8</v>
+        <v>2.5</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3134,76 +3260,74 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>384.7</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>31.1</v>
+        <v>211.2</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F32" s="11" t="n">
-        <v>95.21000000000001</v>
+        <v>20.6</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>11.8</v>
+        <v>8.4</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J32" s="8" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>20.1</v>
+        <v>72.09999999999999</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K32" s="3" t="n"/>
+      <c r="L32" s="3" t="n">
+        <v>41.3</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="N32" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="N32" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>100</v>
+        <v>9.5</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="R32" s="8" t="n">
-        <v>24.9</v>
+        <v>7.2</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>24.1</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>22.5</v>
+        <v>28.2</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>61</v>
+        <v>22.9</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>17.5</v>
+        <v>8.1</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="W32" s="3" t="n">
-        <v>23.2</v>
+        <v>25.2</v>
+      </c>
+      <c r="W32" s="8" t="n">
+        <v>15.9</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>27.2</v>
+        <v>2.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>24.9</v>
+        <v>4.9</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3219,76 +3343,74 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>213.3</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>29.2</v>
+        <v>384.7</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>31.1</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>24.4</v>
+        <v>25.2</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H33" s="8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H33" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>51.6</v>
+        <v>4.4</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>23.5</v>
+        <v>20</v>
+      </c>
+      <c r="L33" s="8" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>23.3</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>0.2</v>
+        <v>6</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="R33" s="8" t="n">
-        <v>84.59999999999999</v>
+        <v>31.1</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>982.1</v>
+        <v>2.5</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>61</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>25.6</v>
+        <v>2.4</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>23.8</v>
+        <v>23.2</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="Y33" s="3" t="n">
-        <v>74.59999999999999</v>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="Y33" s="3" t="n"/>
       <c r="Z33" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3304,76 +3426,72 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>311.6</v>
-      </c>
-      <c r="D34" s="10" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>26.7</v>
+        <v>213.3</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>24.4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.2</v>
+        <v>4.8</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="N34" s="8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="N34" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>1199</v>
+        <v>992.6</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>20.5</v>
+        <v>28.9</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>25.8</v>
+        <v>4.6</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>30.2</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>2720.9</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>13.3</v>
+        <v>11.5</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="W34" s="8" t="n">
-        <v>138248.4</v>
-      </c>
-      <c r="X34" s="3" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="Y34" s="3" t="n">
-        <v>262.1</v>
-      </c>
+        <v>25.6</v>
+      </c>
+      <c r="W34" s="3" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="X34" s="3" t="n"/>
+      <c r="Y34" s="3" t="n"/>
       <c r="Z34" s="3" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3389,76 +3507,88 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>353.4</v>
-      </c>
-      <c r="D35" s="10" t="n">
-        <v>31.1</v>
+        <v>311.6</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>31.9</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>20.8</v>
+        <v>21.4</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>25.9</v>
+        <v>26.7</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>10.3</v>
+        <v>1.5</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>12.4</v>
+        <v>2.2</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+9217
+</t>
+        </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>21.3</v>
+        <v>21.7</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>97.8</v>
+        <v>996</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q35" s="8" t="n">
-        <v>31.1</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>30.5</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>26.9</v>
+        <v>25.8</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>27.5</v>
+        <v>30.2</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>61.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="W35" s="8" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="X35" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="Y35" s="3" t="n">
-        <v>82</v>
+        <v>13.3</v>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="W35" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242461
+289
+</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26282
+79794
+</t>
+        </is>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3474,74 +3604,74 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>430.7</v>
-      </c>
-      <c r="D36" s="10" t="n">
-        <v>32.1</v>
+        <v>353.4</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>31.1</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>26.5</v>
+        <v>25.9</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>19.8</v>
-      </c>
+        <v>10.3</v>
+      </c>
+      <c r="H36" s="3" t="n"/>
       <c r="I36" s="3" t="n">
-        <v>2.4</v>
+        <v>22.4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>14.4</v>
+        <v>4</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="L36" s="8" t="n">
-        <v>41</v>
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>20.7</v>
+        <v>21.3</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>972.5</v>
+        <v>97.2</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>10.6</v>
+        <v>0.7</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>32.1</v>
+        <v>31.1</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>26</v>
+        <v>24.9</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>29.7</v>
+        <v>27.5</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>62.2</v>
+        <v>6.3</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>18</v>
+        <v>17.4</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="W36" s="8" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="Y36" s="3" t="n">
-        <v>79.40000000000001</v>
-      </c>
+        <v>27.8</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242461
+289
+</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="n"/>
       <c r="Z36" s="3" t="n">
         <v>8.4</v>
       </c>
@@ -3559,76 +3689,70 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1693.7</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>155.4</v>
-      </c>
-      <c r="E37" s="12" t="n">
-        <v>102</v>
-      </c>
-      <c r="F37" s="12" t="n">
-        <v>1887.1</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>53.4</v>
-      </c>
+        <v>430.7</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
       <c r="H37" s="3" t="n">
-        <v>96.5</v>
+        <v>13.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>10.1</v>
+        <v>2.4</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>35.6</v>
+        <v>30.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>1015.9</v>
+        <v>20.7</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>24.2</v>
+        <v>242.8</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1192.7</v>
+        <v>9.5</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>153.7</v>
+        <v>32.1</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>126.2</v>
+        <v>26</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>1143.1</v>
+        <v>29.7</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>324.8</v>
+        <v>62.2</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>77.7</v>
+        <v>18.4</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>136.8</v>
+        <v>28.7</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>121.6</v>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Y37" s="3" t="n">
-        <v>72</v>
-      </c>
+        <v>26.6</v>
+      </c>
+      <c r="X37" s="3" t="n"/>
+      <c r="Y37" s="3" t="n"/>
       <c r="Z37" s="3" t="n">
-        <v>1.1</v>
+        <v>7909.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3644,77 +3768,83 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>338.7</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>31</v>
-      </c>
-      <c r="E38" s="12" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F38" s="12" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>10.6</v>
+        <v>693.7</v>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>53.4</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>19.3</v>
+        <v>96.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>18.1</v>
+        <v>4</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">887 1
+18 74
+</t>
+        </is>
       </c>
       <c r="K38" s="3" t="n">
         <v>35.6</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N38" s="8" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="O38" s="3" t="n">
-        <v>98.5</v>
+        <v>16</v>
+      </c>
+      <c r="M38" s="8" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42477
+114111
+</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24268701
+6888
+</t>
+        </is>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q38" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="S38" s="3" t="n">
-        <v>28.6</v>
+        <v>1.7</v>
+      </c>
+      <c r="Q38" s="8" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="R38" s="8" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="S38" s="8" t="n">
+        <v>43.1</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>65</v>
+        <v>324.8</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="V38" s="3" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="X38" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="Y38" s="3" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="Z38" s="3" t="n">
-        <v>1.9</v>
-      </c>
+        <v>77.7</v>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="X38" s="3" t="n"/>
+      <c r="Y38" s="3" t="n"/>
+      <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3729,76 +3859,78 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>20.2</v>
+        <v>38.7</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>2.4</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>26.1</v>
+        <v>25.7</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H39" s="8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1.7</v>
+        <v>20.6</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>0.6</v>
-      </c>
+        <v>18.1</v>
+      </c>
+      <c r="K39" s="3" t="n"/>
       <c r="L39" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="N39" s="8" t="n">
-        <v>14.8</v>
+        <v>24.1</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>99</v>
+        <v>492.7</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>36.7</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>86</v>
+        <v>25.2</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>89.8</v>
+        <v>28.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>63.2</v>
+        <v>65</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>17.3</v>
+        <v>15.5</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="W39" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="Y39" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>32.4</v>
+      </c>
+      <c r="W39" s="8" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="X39" s="8" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+1
+</t>
+        </is>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>38.6</v>
+        <v>2.9</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3814,76 +3946,76 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>453.7</v>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>18.8</v>
+        <v>32.5</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>25.9</v>
+        <v>26.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>18.2</v>
+        <v>11.7</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>19.3</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>12.7</v>
+        <v>21.7</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>19.8</v>
+        <v>21</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="N40" s="8" t="n">
-        <v>46.8</v>
+        <v>20.9</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>32.8</v>
+        <v>31.9</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="S40" s="8" t="n">
-        <v>29.3</v>
+      <c r="S40" s="3" t="n">
+        <v>89.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>20.2</v>
+        <v>63.2</v>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v>27.3</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>27.8</v>
+        <v>24.7</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>23.8</v>
+        <v>24.3</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>26.9</v>
+        <v>2.5</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>98.2</v>
+        <v>88.2</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>10.4</v>
+        <v>0.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3899,76 +4031,74 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>265.6</v>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="E41" s="10" t="n">
+        <v>453.7</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M41" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="F41" s="8" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="N41" s="8" t="n">
-        <v>28.6</v>
+      <c r="N41" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>99</v>
+        <v>97.8</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>21.4</v>
+        <v>32.8</v>
+      </c>
+      <c r="R41" s="8" t="n">
+        <v>66</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>24.9</v>
+        <v>29.3</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>92.3</v>
+        <v>59.2</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v>28.1</v>
+        <v>2.2</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>7.8</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>23.4</v>
+        <v>23.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y41" s="3" t="n">
-        <v>22</v>
-      </c>
+        <v>26.9</v>
+      </c>
+      <c r="Y41" s="3" t="n"/>
       <c r="Z41" s="3" t="n">
-        <v>8.9</v>
+        <v>1</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3984,76 +4114,76 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>236.3</v>
-      </c>
-      <c r="D42" s="10" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D42" s="3" t="n">
         <v>31.6</v>
       </c>
-      <c r="E42" s="10" t="n">
-        <v>20.3</v>
+      <c r="E42" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>25.9</v>
+        <v>25.6</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>20</v>
+        <v>12</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>28.7</v>
+        <v>4.6</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="M42" s="8" t="n">
-        <v>21.8</v>
+        <v>19.9</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>199</v>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>0.2</v>
+        <v>99</v>
+      </c>
+      <c r="P42" s="8" t="n">
+        <v>12.6</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>24.1</v>
+        <v>22.3</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>23.8</v>
+        <v>21.4</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>89.3</v>
+        <v>24.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>97.7</v>
+        <v>92.3</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4069,77 +4199,75 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>372.2</v>
-      </c>
-      <c r="D43" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F43" s="11" t="n">
-        <v>85.7</v>
+        <v>236.3</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>25.9</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>19.8</v>
+        <v>1.3</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>20.6</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>10</v>
+        <v>88.7</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>95.59999999999999</v>
+        <v>26</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>99</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>29.1</v>
+        <v>24.1</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>25.5</v>
+        <v>23.8</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>30.4</v>
+        <v>29.3</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>27.8</v>
+        <v>24.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>84.7</v>
+        <v>23.5</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>9.1</v>
+        <v>88.2</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="Z43" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>96.59999999999999</v>
+      </c>
+      <c r="Z43" s="3" t="n"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4154,77 +4282,75 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>365.9</v>
-      </c>
-      <c r="D44" s="10" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E44" s="10" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E44" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>26.9</v>
+      <c r="F44" s="12" t="n">
+        <v>85.7</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>11.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>19.4</v>
+        <v>19.8</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>0</v>
+        <v>3.7</v>
+      </c>
+      <c r="K44" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>22.3</v>
+        <v>21.6</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>82.3</v>
+        <v>21.5</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>26.9</v>
+        <v>25.6</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>80</v>
+        <v>1.8</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>22.6</v>
+        <v>29.1</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>26.4</v>
+        <v>25.5</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>62</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>18.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>88.5</v>
+        <v>2.8</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>26.3</v>
+        <v>24.2</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>22.8</v>
+        <v>1.1</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="Z44" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>31.2</v>
+      </c>
+      <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4239,76 +4365,85 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="D45" s="12" t="n">
-        <v>1901.6</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>121.6</v>
-      </c>
-      <c r="F45" s="12" t="n">
-        <v>156.1</v>
+        <v>365.9</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>26.9</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>427.4</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v>18.8</v>
+        <v>49.4</v>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79727222
+785
+</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79272
+1
+77
+</t>
+        </is>
       </c>
       <c r="K45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="M45" s="3" t="n">
         <v>22.3</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>1825.9</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>5983.8</v>
+        <v>40</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>172.8</v>
+        <v>32.6</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>29.7</v>
+        <v>26.4</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>0.7</v>
+        <v>30.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>25.8</v>
+        <v>18.6</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>5.8</v>
+        <v>828.5</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>144.9</v>
+        <v>26.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>77.5</v>
+        <v>32.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>503.7</v>
+        <v>84.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>8</v>
+        <v>60.6</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4324,22 +4459,22 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>237.6</v>
-      </c>
-      <c r="D46" s="10" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F46" s="12" t="n">
-        <v>86</v>
+        <v>22.2</v>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>797.5</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>16.1</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>11.5</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>19.1</v>
+        <v>7.7</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>1.7</v>
@@ -4347,51 +4482,49 @@
       <c r="J46" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n">
-        <v>21.1</v>
+      <c r="K46" s="3" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="L46" s="8" t="n">
+        <v>26.5</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>84.8</v>
-      </c>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="N46" s="3" t="n"/>
       <c r="O46" s="3" t="n">
-        <v>99</v>
+        <v>593.8</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>28.8</v>
+        <v>1.3</v>
+      </c>
+      <c r="Q46" s="8" t="n">
+        <v>72.8</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>21.8</v>
+        <v>79.7</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>29</v>
+        <v>72.7</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>75</v>
+        <v>7.7</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="W46" s="8" t="n">
-        <v>14.1</v>
-      </c>
+        <v>68.59999999999999</v>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="W46" s="3" t="n"/>
       <c r="X46" s="3" t="n">
-        <v>28.7</v>
+        <v>0.3</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>5.7</v>
+        <v>2</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,8 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,8 +53,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -143,7 +149,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -152,7 +158,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -768,74 +774,72 @@
       <c r="C4" s="3" t="n">
         <v>186.2</v>
       </c>
-      <c r="D4" s="10" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="E4" s="3" t="n">
+      <c r="D4" s="3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E4" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="F4" s="12" t="n">
-        <v>84.3</v>
+      <c r="F4" s="11" t="n">
+        <v>84.31</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>18.2</v>
+        <v>18.7</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>118.2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>2.9</v>
+        <v>12.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>2.2</v>
+        <v>0</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>20.2</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>23.4</v>
+        <v>20.1</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>83.40000000000001</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>9</v>
+        <v>199</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>28.2</v>
-      </c>
+        <v>10.2</v>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
       <c r="R4" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="S4" s="3" t="n">
+      <c r="S4" s="8" t="n">
         <v>27.1</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="U4" s="3" t="n">
+      <c r="U4" s="8" t="n">
         <v>12.2</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X4" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X4" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>81.8</v>
+        <v>1811.8</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>5.8</v>
+        <v>15.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -851,22 +855,22 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>438.5</v>
-      </c>
-      <c r="D5" s="10" t="n">
+        <v>2903.8</v>
+      </c>
+      <c r="D5" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="10" t="n">
         <v>18.2</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>14.4</v>
+        <v>34.1</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>6.2</v>
+        <v>16.8</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>3.5</v>
@@ -875,52 +879,52 @@
         <v>5.5</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>9</v>
+        <v>199</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="8" t="n">
         <v>25.4</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>56.6</v>
+        <v>156.6</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="V5" s="3" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>2.8</v>
+      <c r="V5" s="8" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="W5" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="X5" s="8" t="n">
+        <v>27.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -936,12 +940,12 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E6" s="3" t="n">
+        <v>1422.3</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="E6" s="10" t="n">
         <v>18.8</v>
       </c>
       <c r="F6" s="3" t="n">
@@ -950,46 +954,46 @@
       <c r="G6" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>17.2</v>
+      <c r="H6" s="8" t="n">
+        <v>872.6</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.6</v>
+        <v>14.6</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.7</v>
+        <v>7.2</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M6" s="8" t="n">
-        <v>66</v>
+      <c r="M6" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>32.7</v>
+        <v>10</v>
+      </c>
+      <c r="Q6" s="8" t="n">
+        <v>21.7</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="S6" s="3" t="n">
+      <c r="S6" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="U6" s="3" t="n">
+        <v>2929.8</v>
+      </c>
+      <c r="U6" s="8" t="n">
         <v>20.7</v>
       </c>
       <c r="V6" s="3" t="n">
@@ -1002,10 +1006,10 @@
         <v>26.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>166.4</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1021,16 +1025,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4778.5</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="E7" s="3" t="n">
+        <v>4785.1</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="E7" s="10" t="n">
         <v>19.3</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>22</v>
+      <c r="F7" s="8" t="n">
+        <v>27</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>15.4</v>
@@ -1039,58 +1043,58 @@
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>35.1</v>
+        <v>20.1</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>23.5</v>
       </c>
       <c r="O7" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="P7" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="P7" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" s="8" t="n">
         <v>34.2</v>
       </c>
-      <c r="R7" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>22.1</v>
+      <c r="R7" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="S7" s="8" t="n">
+        <v>27.1</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="U7" s="3" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="U7" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="W7" s="3" t="n">
-        <v>84.09999999999999</v>
+      <c r="W7" s="8" t="n">
+        <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>27.3</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>66.2</v>
+        <v>166.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>438.5</v>
+        <v>13.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1106,67 +1110,67 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>299.6</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>34.41</v>
-      </c>
-      <c r="E8" s="8" t="n">
+        <v>1299</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="E8" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="F8" s="12" t="n">
-        <v>2.6</v>
+      <c r="F8" s="3" t="n">
+        <v>27.6</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="8" t="n">
         <v>19</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="K8" s="8" t="n">
         <v>30.9</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="N8" s="8" t="n">
-        <v>40.9</v>
+      <c r="N8" s="3" t="n">
+        <v>24</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>96.5</v>
+        <v>196.5</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q8" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="Q8" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>2.2</v>
+        <v>21.2</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>28</v>
+        <v>298</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>24.9</v>
+        <v>22.2</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>1.9</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>26.1</v>
@@ -1175,7 +1179,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>26.6</v>
+        <v>20.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1191,19 +1195,19 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1783.5</v>
-      </c>
-      <c r="D9" s="10" t="n">
+        <v>11783.5</v>
+      </c>
+      <c r="D9" s="9" t="n">
         <v>164.8</v>
       </c>
-      <c r="E9" s="11" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>130.8</v>
+      <c r="E9" s="9" t="n">
+        <v>196.9</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>1130.8</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>161.9</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>89.40000000000001</v>
@@ -1212,22 +1216,22 @@
         <v>16.5</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>27.5</v>
+        <v>127.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>3.9</v>
+        <v>30.9</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>16.2</v>
+        <v>100.2</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>199.6</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>15.8</v>
+        <v>112.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>494.5</v>
+        <v>1494.5</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>1.2</v>
@@ -1239,32 +1243,28 @@
         <v>121.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>135.7</v>
+        <v>1135.7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>329.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>132.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>116.8</v>
+        <v>1116.8</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>133.5</v>
+        <v>1133.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>388.8</v>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222424272
-777
-</t>
-        </is>
+        <v>1388.8</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>141.6</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1282,20 +1282,20 @@
       <c r="C10" s="3" t="n">
         <v>356.7</v>
       </c>
-      <c r="D10" s="10" t="n">
-        <v>33</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="F10" s="11" t="n">
+      <c r="D10" s="9" t="n">
+        <v>393</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F10" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="8" t="n">
         <v>13.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>12.9</v>
+        <v>17.9</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>3.3</v>
@@ -1303,15 +1303,9 @@
       <c r="J10" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-2221
-</t>
-        </is>
-      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="8" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>19.9</v>
@@ -1323,37 +1317,37 @@
         <v>98.90000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q10" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q10" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>2.1</v>
+        <v>27.1</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>66.90000000000001</v>
+        <v>166</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>1.2</v>
+        <v>16.2</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W10" s="3" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="W10" s="8" t="n">
         <v>23.4</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>272.8</v>
+        <v>79.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>41.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1369,53 +1363,48 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>265.6</v>
-      </c>
-      <c r="D11" s="10" t="n">
+        <v>1265.6</v>
+      </c>
+      <c r="D11" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="10" t="n">
         <v>19.8</v>
       </c>
       <c r="F11" s="10" t="n">
         <v>24.9</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1.3</v>
+        <v>10.3</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="N11" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">897
-505
-1799
-</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>927.3</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q11" s="8" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Q11" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="R11" s="3" t="n">
@@ -1425,13 +1414,13 @@
         <v>29.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>720.6</v>
+        <v>170.6</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V11" s="3" t="n">
-        <v>2.1</v>
+      <c r="V11" s="8" t="n">
+        <v>27.1</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>24.9</v>
@@ -1440,14 +1429,10 @@
         <v>30.1</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-744
-</t>
-        </is>
+        <v>684</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>5.1</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1463,12 +1448,12 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>342.4</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E12" s="3" t="n">
+        <v>247.1</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="E12" s="10" t="n">
         <v>22.6</v>
       </c>
       <c r="F12" s="10" t="n">
@@ -1477,32 +1462,32 @@
       <c r="G12" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2.7</v>
+        <v>22.1</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>4.6</v>
+        <v>14.6</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L12" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="8" t="n">
         <v>23</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>2.9</v>
+        <v>21.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>27.5</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.5</v>
+        <v>10.8</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>31.8</v>
@@ -1514,25 +1499,25 @@
         <v>27.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>57.8</v>
+        <v>59.8</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>1.8</v>
+        <v>19.8</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>24.6</v>
+        <v>27.9</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>284.6</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>7.7</v>
+        <v>76.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>57.2</v>
+        <v>181.7</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1548,13 +1533,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>428.6</v>
-      </c>
-      <c r="D13" s="10" t="n">
+        <v>1428.6</v>
+      </c>
+      <c r="D13" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="E13" s="12" t="n">
-        <v>2.4</v>
+      <c r="E13" s="10" t="n">
+        <v>20.1</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>26.6</v>
@@ -1566,16 +1551,16 @@
         <v>19.9</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>3.3</v>
+        <v>13.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>2.1</v>
+        <v>22.1</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>21.9</v>
@@ -1584,15 +1569,15 @@
         <v>26.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>9.5</v>
+        <v>98</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>26.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1604,8 +1589,8 @@
       <c r="U13" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="V13" s="3" t="n">
-        <v>28.6</v>
+      <c r="V13" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>24.8</v>
@@ -1614,10 +1599,10 @@
         <v>29.3</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>7.6</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>23.1</v>
+        <v>18.3</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1635,10 +1620,10 @@
       <c r="C14" s="3" t="n">
         <v>190.3</v>
       </c>
-      <c r="D14" s="10" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E14" s="3" t="n">
+      <c r="D14" s="3" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E14" s="10" t="n">
         <v>21.9</v>
       </c>
       <c r="F14" s="10" t="n">
@@ -1647,32 +1632,32 @@
       <c r="G14" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="H14" s="3" t="n">
-        <v>2.3</v>
+      <c r="H14" s="8" t="n">
+        <v>20.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J14" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="K14" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>2.1</v>
-      </c>
       <c r="N14" s="3" t="n">
-        <v>26.4</v>
+        <v>264</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>197.3</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>22.4</v>
@@ -1680,29 +1665,29 @@
       <c r="R14" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="S14" s="3" t="n">
+      <c r="S14" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>89</v>
+        <v>189</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="W14" s="8" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="X14" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="X14" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>96</v>
+        <v>196</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>2.5</v>
+        <v>9.1</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1718,31 +1703,31 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="D15" s="10" t="n">
+        <v>359.6</v>
+      </c>
+      <c r="D15" s="3" t="n">
         <v>32.5</v>
       </c>
-      <c r="E15" s="12" t="n">
-        <v>2.8</v>
+      <c r="E15" s="10" t="n">
+        <v>20.8</v>
       </c>
       <c r="F15" s="10" t="n">
         <v>26.7</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>1.7</v>
+      <c r="G15" s="8" t="n">
+        <v>11.7</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>2.4</v>
+        <v>18.4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>25.7</v>
+        <v>25.1</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>21.6</v>
@@ -1754,12 +1739,12 @@
         <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>1100</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="8" t="n">
         <v>32</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1769,7 +1754,7 @@
         <v>29.2</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>61.7</v>
+        <v>161.7</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>18.2</v>
@@ -1777,8 +1762,8 @@
       <c r="V15" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W15" s="3" t="n">
-        <v>4.8</v>
+      <c r="W15" s="8" t="n">
+        <v>24.8</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>28.8</v>
@@ -1787,7 +1772,7 @@
         <v>73.09999999999999</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1803,57 +1788,43 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1591.2</v>
-      </c>
-      <c r="D16" s="10" t="n">
+        <v>1291.2</v>
+      </c>
+      <c r="D16" s="9" t="n">
         <v>157.9</v>
       </c>
-      <c r="E16" s="11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>1317.2</v>
+      <c r="E16" s="9" t="n">
+        <v>1105.5</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>5131.7</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>52.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>929.2</v>
+        <v>99.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>11.5</v>
+        <v>111.5</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">790691
-22
-5682
-</t>
-        </is>
+      <c r="K16" s="3" t="n">
+        <v>36.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>10.6</v>
+        <v>1110.6</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">791727
-14
-000
-</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11722
-77218
-</t>
-        </is>
+        <v>109.5</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>1130.7</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>27490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
@@ -1862,47 +1833,31 @@
         <v>148.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>121.9</v>
+        <v>1121.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>136.1</v>
+        <v>1136.1</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>31.8</v>
+        <v>331.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="V16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7277978
-7566
-</t>
-        </is>
-      </c>
-      <c r="W16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22414
-8711011466 7
-</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36595
-99781
-</t>
-        </is>
-      </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5555
-5721
-</t>
-        </is>
+        <v>176.6</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>133.7</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>1120.7</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="Y16" s="3" t="n">
+        <v>1407.4</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>741.1</v>
+        <v>34.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1918,12 +1873,12 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="D17" s="10" t="n">
+        <v>1318.2</v>
+      </c>
+      <c r="D17" s="9" t="n">
         <v>31.6</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="10" t="n">
         <v>21.1</v>
       </c>
       <c r="F17" s="10" t="n">
@@ -1932,32 +1887,30 @@
       <c r="G17" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H17" s="8" t="n">
-        <v>292.8</v>
+      <c r="H17" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2.3</v>
+        <v>12.3</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" s="3" t="n">
-        <v>36.8</v>
-      </c>
+      <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="M17" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="M17" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="N17" s="8" t="n">
-        <v>30.7</v>
+      <c r="N17" s="3" t="n">
+        <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>490.1</v>
+        <v>98</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>29.7</v>
@@ -1965,29 +1918,29 @@
       <c r="R17" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="S17" s="3" t="n">
-        <v>2.2</v>
+      <c r="S17" s="8" t="n">
+        <v>28.2</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>6.4</v>
+        <v>166.4</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>33.7</v>
+        <v>26.7</v>
       </c>
       <c r="W17" s="8" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="X17" s="8" t="n">
-        <v>42.5</v>
+        <v>24.1</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>47.6</v>
+        <v>181.5</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>6.9</v>
+        <v>16.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -2003,19 +1956,19 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>368</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>32.1</v>
+        <v>1368</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>26.7</v>
+        <v>24.2</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>28.61</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>16.9</v>
+        <v>10.9</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>20.4</v>
@@ -2023,31 +1976,23 @@
       <c r="I18" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J18" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-222
-</t>
-        </is>
+      <c r="J18" s="8" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>10.4</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>24.4</v>
+        <v>21.4</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="N18" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27844
-171719
-</t>
-        </is>
+      <c r="N18" s="8" t="n">
+        <v>224.8</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>97.3</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
@@ -2055,40 +2000,32 @@
       <c r="Q18" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="S18" s="3" t="n">
-        <v>7.7</v>
+      <c r="S18" s="8" t="n">
+        <v>27.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>58.5</v>
+        <v>98</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="V18" s="3" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7444
-1779 7
-</t>
-        </is>
-      </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09442
-77 7
-</t>
-        </is>
+      <c r="V18" s="8" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W18" s="8" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="Y18" s="3" t="n">
+        <v>71.2</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>17.1</v>
+        <v>111</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2104,46 +2041,46 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>265.6</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="F19" s="3" t="n">
+        <v>2260.6</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>30.84</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="F19" s="8" t="n">
         <v>26.3</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>2.3</v>
+        <v>11.2</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>22.3</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>24.8</v>
+        <v>86.3</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>297.3</v>
+        <v>197.6</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>0.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>29.9</v>
@@ -2160,20 +2097,20 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="3" t="n">
-        <v>28.5</v>
+      <c r="V19" s="8" t="n">
+        <v>24.3</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X19" s="3" t="n">
-        <v>2.9</v>
+        <v>22.9</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <v>71.09999999999999</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>7218.7</v>
+        <v>89</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>3.3</v>
+        <v>78.3</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2194,26 +2131,26 @@
       <c r="D20" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="E20" s="12" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="F20" s="3" t="n">
+      <c r="E20" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F20" s="8" t="n">
         <v>26.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>9.9</v>
+        <v>19.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="I20" s="3" t="n">
-        <v>2.5</v>
+      <c r="I20" s="8" t="n">
+        <v>28.1</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>21.6</v>
@@ -2221,42 +2158,44 @@
       <c r="M20" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>26.3</v>
+      <c r="N20" s="8" t="n">
+        <v>35.4</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="P20" s="3" t="n"/>
+        <v>98</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q20" s="3" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="R20" s="3" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="R20" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>62.3</v>
+        <v>162.3</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>1.6</v>
+        <v>16.6</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>2.9</v>
+        <v>27.3</v>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>23.8</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>89</v>
+        <v>715</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>9.1</v>
+        <v>19.1</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2274,8 +2213,8 @@
       <c r="C21" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D21" s="12" t="n">
-        <v>60.7</v>
+      <c r="D21" s="3" t="n">
+        <v>30.7</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>21.2</v>
@@ -2284,7 +2223,7 @@
         <v>25.9</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>9.5</v>
+        <v>29.5</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>19.6</v>
@@ -2296,22 +2235,22 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>2.6</v>
+        <v>10</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>18.6</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>986</v>
+        <v>199</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>6.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>30.6</v>
@@ -2323,25 +2262,25 @@
         <v>31.2</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>4.2</v>
+        <v>71.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>23.8</v>
+        <v>12.6</v>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="W21" s="8" t="n">
+        <v>16.6</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>7.2</v>
+        <v>28.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>75</v>
+        <v>77.3</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2357,49 +2296,46 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>395.3</v>
-      </c>
-      <c r="D22" s="3" t="n">
+        <v>399.3</v>
+      </c>
+      <c r="D22" s="8" t="n">
         <v>32.9</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="F22" s="12" t="n">
-        <v>2</v>
+      <c r="F22" s="8" t="n">
+        <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>14.8</v>
+        <v>12.8</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>12.8</v>
+        <v>19.8</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2.5</v>
+        <v>12.5</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>4.3</v>
+        <v>14.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2.3</v>
+        <v>21.3</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>25.6</v>
+      <c r="N22" s="8" t="n">
+        <v>24.7</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68 2
-</t>
-        </is>
+        <v>97.5</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.4</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>32.4</v>
@@ -2410,29 +2346,26 @@
       <c r="S22" s="3" t="n">
         <v>89.3</v>
       </c>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65 2
-</t>
-        </is>
+      <c r="T22" s="3" t="n">
+        <v>160.5</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>27.8</v>
+        <v>26.8</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X22" s="3" t="n">
-        <v>84.90000000000001</v>
+      <c r="X22" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>72.3</v>
+        <v>186</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>4.9</v>
+        <v>14.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2448,62 +2381,43 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>739.6</v>
-      </c>
-      <c r="D23" s="11" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="E23" s="11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="F23" s="11" t="n">
-        <v>432.4</v>
+        <v>17439.6</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>132.4</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41444444
-1
-8684
-</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27955
-42
-12141
-</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-1141089
-</t>
-        </is>
+        <v>250.3</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>1101.8</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>19.3</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>7.7</v>
+        <v>19.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>18.2</v>
+        <v>108.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>17</v>
+        <v>1107</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">418686866
-50756012
-1441
-</t>
-        </is>
+        <v>1126.8</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>1489.4</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.2</v>
@@ -2515,28 +2429,28 @@
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>146.8</v>
+        <v>1146.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>325.7</v>
+        <v>325.1</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>86.5</v>
+        <v>134.4</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>24.6</v>
+        <v>120.3</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>2.7</v>
+        <v>140.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>860.6</v>
+        <v>2399</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>3.7</v>
+        <v>36.7</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2552,84 +2466,74 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>739.6</v>
-      </c>
-      <c r="D24" s="11" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="E24" s="11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="F24" s="11" t="n">
-        <v>432.4</v>
+        <v>347.9</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>315.1</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>26.5</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>1.8</v>
+        <v>10.1</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>1.9</v>
+        <v>12.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>19.3</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>18.2</v>
+        <v>21.6</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6169690911
-2929
-</t>
-        </is>
+        <v>21.4</v>
+      </c>
+      <c r="N24" s="8" t="n">
+        <v>22.4</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q24" s="8" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="R24" s="8" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="S24" s="8" t="n">
-        <v>46.8</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>29.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>325.7</v>
+        <v>165.1</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74950
-448468
-</t>
-        </is>
+        <v>15.9</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="W24" s="8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>282.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>399</v>
+        <v>79.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>7.3</v>
+        <v>17.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2645,77 +2549,73 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>21.4</v>
+        <v>106.7</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>20.6</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>26.5</v>
+        <v>23.5</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>19.3</v>
+        <v>23.7</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>21.6</v>
+        <v>22.4</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="N25" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>264.4</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>284.1</v>
+      </c>
+      <c r="S25" s="8" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>184.4</v>
+      </c>
+      <c r="U25" s="3" t="inlineStr"/>
+      <c r="V25" s="3" t="n">
+        <v>244.1</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X25" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="O25" s="3" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>156.1</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X25" s="8" t="n">
-        <v>40.8</v>
-      </c>
       <c r="Y25" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v>7.3</v>
-      </c>
+        <v>81.7</v>
+      </c>
+      <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2730,92 +2630,76 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="D26" s="12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>23.5</v>
+        <v>290</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>5.7</v>
+        <v>14.1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215852
-147
-</t>
-        </is>
+        <v>19.2</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>10.9</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-77
-</t>
-        </is>
+        <v>0.7</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>16.1</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>22.4</v>
+        <v>21.4</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>24.1</v>
+        <v>21.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>6.7</v>
+        <v>10</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>28.7</v>
+        <v>24.3</v>
+      </c>
+      <c r="R26" s="8" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="S26" s="8" t="n">
+        <v>280.9</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>192</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>5.3</v>
+        <v>12.9</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="W26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7771717
-11811408 7
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>2.2</v>
+        <v>23.8</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>79.09999999999999</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="Z26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-893
-</t>
-        </is>
+        <v>191.8</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2831,69 +2715,73 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>90</v>
+        <v>2322</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>23.1</v>
+        <v>20.5</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>25.5</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>4.1</v>
+        <v>19.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="n"/>
+        <v>19.1</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="L27" s="3" t="n">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.4</v>
+        <v>20.5</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="O27" s="3" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>198</v>
+      </c>
       <c r="P27" s="3" t="n">
-        <v>8</v>
+        <v>0.4</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R27" s="3" t="n">
-        <v>23.3</v>
+        <v>28.8</v>
+      </c>
+      <c r="R27" s="8" t="n">
+        <v>24.9</v>
       </c>
       <c r="S27" s="8" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>926</v>
+        <v>73.2</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>2.4</v>
+        <v>10.5</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>23.8</v>
+        <v>26.9</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>26.8</v>
+        <v>24.4</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>29</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v>3.8</v>
-      </c>
+        <v>81.8</v>
+      </c>
+      <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2908,84 +2796,74 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>322</v>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138938798
-305
-</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
+        <v>1290.7</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M28" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H28" s="8" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-2923
-</t>
-        </is>
+      <c r="N28" s="8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>297.3</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>16.4</v>
+        <v>10.8</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="R28" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v>29</v>
+        <v>31.2</v>
+      </c>
+      <c r="R28" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="S28" s="8" t="n">
+        <v>27.2</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>73.2</v>
+        <v>160.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>26.9</v>
+        <v>18.1</v>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v>28.6</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>2.8</v>
+        <v>24.6</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>27.1</v>
+        <v>28.4</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>81.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>2.4</v>
+        <v>10.7</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -3001,80 +2879,74 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>290.7</v>
+        <v>12146.8</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E29" s="3" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E29" s="10" t="n">
         <v>20.5</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>18.9</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
       <c r="I29" s="3" t="n">
-        <v>1.9</v>
+        <v>11.6</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="M29" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="M29" s="8" t="n">
         <v>20.6</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-2923
-</t>
-        </is>
+        <v>23.9</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>95.3</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="R29" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>27.2</v>
+        <v>85.3</v>
+      </c>
+      <c r="R29" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>60.2</v>
+        <v>87</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>18.1</v>
+        <v>14.2</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>28.6</v>
+        <v>22.4</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X29" s="3" t="n">
-        <v>29.1</v>
+        <v>21.3</v>
+      </c>
+      <c r="X29" s="8" t="n">
+        <v>14.6</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>724.6</v>
+        <v>90.8</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>1.3</v>
+        <v>22.5</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -3090,76 +2962,76 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>846.2</v>
-      </c>
-      <c r="D30" s="11" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E30" s="11" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="F30" s="11" t="n">
-        <v>26</v>
+        <v>11056.2</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>1145.2</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>1103.2</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>124.2</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>12.2</v>
+        <v>196.6</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2.2</v>
+        <v>7.1</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2.6</v>
+        <v>111</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>8.4</v>
+        <v>38.8</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>21.1</v>
+        <v>1106.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>20.6</v>
+        <v>1105.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>23.9</v>
+        <v>123.9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>95.3</v>
+        <v>487.6</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>1.1</v>
+        <v>12.8</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>825.3</v>
+        <v>11135.8</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>23.6</v>
+        <v>120.1</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>28</v>
+        <v>1140.9</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>8</v>
+        <v>396.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>4.1</v>
+        <v>18.5</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>2.4</v>
+        <v>1126.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>24.6</v>
+        <v>1115.9</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>2.4</v>
+        <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>4.2</v>
+        <v>1424.7</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>1.3</v>
+        <v>21.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3175,76 +3047,74 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="D31" s="11" t="n">
-        <v>452.1</v>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F31" s="11" t="n">
+        <v>211.2</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J31" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="G31" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>38.8</v>
-      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>15.1</v>
+        <v>21.3</v>
+      </c>
+      <c r="M31" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="N31" s="8" t="n">
-        <v>23.9</v>
+        <v>24.8</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>487.6</v>
+        <v>97.5</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q31" s="8" t="n">
-        <v>35.8</v>
+        <v>10.6</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>27.2</v>
       </c>
       <c r="R31" s="8" t="n">
-        <v>280.7</v>
-      </c>
-      <c r="S31" s="8" t="n">
-        <v>40.9</v>
+        <v>24.1</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>396.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="U31" s="8" t="n">
-        <v>81.5</v>
+        <v>88.8</v>
       </c>
       <c r="V31" s="8" t="n">
-        <v>26.1</v>
+        <v>25.2</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>21.3</v>
+        <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>4.6</v>
+        <v>27.2</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>44.2</v>
+        <v>24.9</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>2.5</v>
+        <v>145.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3260,74 +3130,72 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>211.2</v>
-      </c>
-      <c r="D32" s="12" t="n">
-        <v>2</v>
+        <v>384.7</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>31.1</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>24.8</v>
+        <v>19.3</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>25.2</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H32" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="N32" s="3" t="inlineStr"/>
+      <c r="O32" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="R32" s="8" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>161</v>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="V32" s="3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X32" s="3" t="inlineStr"/>
+      <c r="Y32" s="3" t="n">
+        <v>174.6</v>
+      </c>
+      <c r="Z32" s="3" t="n">
         <v>19.3</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="S32" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="T32" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="W32" s="8" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>5.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3343,74 +3211,72 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>384.7</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>31.1</v>
+        <v>213.3</v>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>29.2</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>25.2</v>
+        <v>19.6</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>24.4</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>18</v>
+        <v>19.6</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>18.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1.4</v>
+        <v>11</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>23.3</v>
-      </c>
+        <v>21.4</v>
+      </c>
+      <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>10</v>
+        <v>299</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>6</v>
+        <v>10.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="R33" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>2.5</v>
+        <v>28.9</v>
+      </c>
+      <c r="R33" s="8" t="n">
+        <v>206.6</v>
+      </c>
+      <c r="S33" s="8" t="n">
+        <v>28.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>61</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W33" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y33" s="3" t="n"/>
+        <v>16.5</v>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="W33" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X33" s="3" t="inlineStr"/>
+      <c r="Y33" s="3" t="n">
+        <v>861.4</v>
+      </c>
       <c r="Z33" s="3" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3426,72 +3292,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>213.3</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>24.4</v>
+        <v>311.6</v>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>26.7</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>18.8</v>
+        <v>20.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>21.5</v>
+        <v>0.2</v>
+      </c>
+      <c r="L34" s="8" t="n">
+        <v>21.8</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>25.4</v>
+        <v>25.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>992.6</v>
+        <v>199</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>28.9</v>
+        <v>30.5</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>4.6</v>
+        <v>25.8</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>30.2</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>2720.9</v>
+        <v>169.4</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>11.5</v>
+        <v>13.3</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>25.6</v>
+        <v>27.3</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="X34" s="3" t="n"/>
-      <c r="Y34" s="3" t="n"/>
+        <v>24.8</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="Y34" s="3" t="n">
+        <v>82.8</v>
+      </c>
       <c r="Z34" s="3" t="n">
-        <v>2.3</v>
+        <v>16.5</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3507,88 +3377,76 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>311.6</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>26.7</v>
+        <v>353.4</v>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>25.9</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1.5</v>
+        <v>10.3</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-9217
-</t>
-        </is>
+        <v>19.7</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>3.5</v>
+        <v>14</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="L35" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>197.2</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="R35" s="8" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="S35" s="8" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>1614.3</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="V35" s="8" t="n">
         <v>21.8</v>
       </c>
-      <c r="M35" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>996</v>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q35" s="3" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="W35" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242461
-289
-</t>
-        </is>
-      </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26282
-79794
-</t>
-        </is>
+      <c r="W35" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>4.5</v>
+        <v>18.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3604,76 +3462,76 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>353.4</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>25.9</v>
+        <v>430.7</v>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>26.5</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="H36" s="3" t="n"/>
+        <v>11.2</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>19.8</v>
+      </c>
       <c r="I36" s="3" t="n">
-        <v>22.4</v>
+        <v>2.4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>14.4</v>
+      </c>
+      <c r="K36" s="8" t="n">
+        <v>30.6</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>21.3</v>
+        <v>21</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>20.1</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>25.1</v>
+        <v>26.2</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>97.2</v>
+        <v>918.5</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.7</v>
+        <v>10.6</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>31.1</v>
+        <v>32.1</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>24.9</v>
+        <v>26</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>27.5</v>
+        <v>29.7</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>6.3</v>
+        <v>62.2</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>17.4</v>
+        <v>18</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>27.8</v>
+        <v>28.7</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242461
-289
-</t>
-        </is>
-      </c>
-      <c r="Y36" s="3" t="n"/>
+        <v>24.6</v>
+      </c>
+      <c r="X36" s="8" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>42.4</v>
+      </c>
       <c r="Z36" s="3" t="n">
-        <v>8.4</v>
+        <v>211</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3689,70 +3547,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>430.7</v>
-      </c>
-      <c r="D37" s="11" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E37" s="11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F37" s="11" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G37" s="3" t="n"/>
+        <v>1693.7</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>1155.4</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>1102</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>128.7</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>53.4</v>
+      </c>
       <c r="H37" s="3" t="n">
-        <v>13.8</v>
+        <v>96.5</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>2.4</v>
+        <v>110.1</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>4.4</v>
+        <v>18.1</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>30.6</v>
+        <v>135.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>21</v>
+        <v>1106</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>20.7</v>
+        <v>1803.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>242.8</v>
+        <v>121.1</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>9.5</v>
+        <v>492.9</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>32.1</v>
+        <v>143.1</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>26</v>
+        <v>1126.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>29.7</v>
+        <v>1143.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>62.2</v>
+        <v>13821.8</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>18.4</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>28.7</v>
+        <v>136.8</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="X37" s="3" t="n"/>
-      <c r="Y37" s="3" t="n"/>
+        <v>121.6</v>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v>1142.4</v>
+      </c>
+      <c r="Y37" s="3" t="n">
+        <v>398.2</v>
+      </c>
       <c r="Z37" s="3" t="n">
-        <v>7909.7</v>
+        <v>1392.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3768,83 +3632,75 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>693.7</v>
-      </c>
-      <c r="D38" s="11" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="E38" s="11" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="F38" s="11" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="G38" s="8" t="n">
-        <v>53.4</v>
+        <v>338.7</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>96.5</v>
+        <v>19.3</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">887 1
-18 74
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>35.6</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>185.8</v>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42477
-114111
-</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24268701
-6888
-</t>
-        </is>
+        <v>21.2</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>98.5</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>53.7</v>
+        <v>10.3</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="R38" s="8" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="S38" s="8" t="n">
-        <v>43.1</v>
+        <v>25.2</v>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>28.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>324.8</v>
+        <v>169</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>77.7</v>
+        <v>13.5</v>
       </c>
       <c r="V38" s="8" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="W38" s="8" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X38" s="3" t="n"/>
-      <c r="Y38" s="3" t="n"/>
-      <c r="Z38" s="3" t="n"/>
+        <v>87.40000000000001</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="Y38" s="3" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>2.9</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3859,78 +3715,74 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E39" s="12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H39" s="3" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H39" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>20.6</v>
+        <v>1.7</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="M39" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="N39" s="8" t="n">
-        <v>24.1</v>
+      <c r="M39" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>492.7</v>
+        <v>99</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>0.3</v>
+        <v>10.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="R39" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>28.6</v>
+        <v>31.9</v>
+      </c>
+      <c r="R39" s="8" t="n">
+        <v>126</v>
+      </c>
+      <c r="S39" s="8" t="n">
+        <v>29.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>65</v>
+        <v>163.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="W39" s="8" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="X39" s="8" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-1
-</t>
-        </is>
+        <v>17.3</v>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="W39" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="Y39" s="3" t="n">
+        <v>288.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>2.9</v>
+        <v>13.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3946,76 +3798,76 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>32.5</v>
+        <v>1453.1</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E40" s="3" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>1797.8</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="R40" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="T40" s="3" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="U40" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="N40" s="3" t="n">
+      <c r="V40" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="O40" s="3" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="P40" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="S40" s="3" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="T40" s="3" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>24.3</v>
+      <c r="W40" s="8" t="n">
+        <v>23.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>2.5</v>
+        <v>26.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>88.2</v>
+        <v>72</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>0.8</v>
+        <v>10.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -4031,74 +3883,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>453.7</v>
-      </c>
-      <c r="D41" s="12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>25.9</v>
+        <v>269.6</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>85.59999999999999</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>4.1</v>
+        <v>12</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>1.6</v>
+      </c>
+      <c r="K41" s="8" t="n">
+        <v>43.6</v>
       </c>
       <c r="L41" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="M41" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M41" s="3" t="n">
-        <v>19.6</v>
-      </c>
       <c r="N41" s="3" t="n">
-        <v>4.6</v>
+        <v>23</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>97.8</v>
+        <v>199</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.5</v>
+        <v>10.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="R41" s="8" t="n">
-        <v>66</v>
+        <v>22.3</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>29.3</v>
+        <v>24.9</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>59.2</v>
+        <v>192.8</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="Y41" s="3" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v>816.6</v>
+      </c>
+      <c r="W41" s="8" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y41" s="3" t="n">
+        <v>190.5</v>
+      </c>
       <c r="Z41" s="3" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4114,77 +3968,75 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>26.5</v>
+        <v>1236.3</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>31.6</v>
       </c>
-      <c r="E42" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>12</v>
+      <c r="E42" s="10" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>11.3</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>18.6</v>
+        <v>20</v>
       </c>
       <c r="I42" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J42" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J42" s="3" t="n">
-        <v>1.6</v>
-      </c>
       <c r="K42" s="3" t="n">
-        <v>4.6</v>
+        <v>28.1</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>19.9</v>
+        <v>21.9</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>23</v>
+        <v>21.8</v>
+      </c>
+      <c r="N42" s="8" t="n">
+        <v>26</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P42" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="Q42" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R42" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>24.9</v>
+        <v>199</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q42" s="8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="R42" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="S42" s="8" t="n">
+        <v>29.3</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>92.3</v>
+        <v>197.7</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>2.8</v>
+        <v>10.1</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>23.4</v>
+        <v>21.7</v>
+      </c>
+      <c r="W42" s="8" t="n">
+        <v>23.5</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="Z42" s="3" t="n">
-        <v>2.9</v>
-      </c>
+        <v>190.6</v>
+      </c>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4199,75 +4051,77 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>236.3</v>
-      </c>
-      <c r="D43" s="8" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>20.3</v>
+        <v>372.2</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>21.3</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>1.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>20.6</v>
+        <v>19.8</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>6.7</v>
+        <v>12</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>88.7</v>
+        <v>10</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>26</v>
+        <v>25.6</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>199</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>24.1</v>
+        <v>29.1</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>23.8</v>
+        <v>25.5</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>29.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>97.2</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="V43" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="W43" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="W43" s="3" t="n">
-        <v>23.5</v>
-      </c>
       <c r="X43" s="3" t="n">
-        <v>88.2</v>
+        <v>29.1</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4282,75 +4136,77 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
+        <v>365.9</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="N44" s="8" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>162</v>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X44" s="8" t="n">
         <v>32.2</v>
       </c>
-      <c r="D44" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F44" s="12" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K44" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="M44" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="T44" s="3" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y44" s="3" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="Z44" s="3" t="n"/>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v>166</v>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4364,86 +4220,65 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>365.9</v>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F45" s="11" t="n">
-        <v>26.9</v>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="12" t="inlineStr"/>
+      <c r="E45" s="9" t="n">
+        <v>1121</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>1796.1</v>
       </c>
       <c r="G45" s="3" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>114.7</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>172.3</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>1166.9</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>122.9</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>148.7</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>293.8</v>
+      </c>
+      <c r="P45" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="H45" s="3" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79727222
-785
-</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79272
-1
-77
-</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="P45" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3" t="n">
-        <v>32.6</v>
+        <v>1752.8</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="T45" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>149.1</v>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
       <c r="U45" s="3" t="n">
-        <v>18.6</v>
+        <v>168.6</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>828.5</v>
-      </c>
-      <c r="W45" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="X45" s="3" t="n">
-        <v>32.8</v>
-      </c>
+        <v>138.1</v>
+      </c>
+      <c r="W45" s="3" t="inlineStr"/>
+      <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>84.8</v>
+        <v>3503.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>60.6</v>
+        <v>9316</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4459,72 +4294,74 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="D46" s="11" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="E46" s="11" t="n">
-        <v>797.5</v>
-      </c>
-      <c r="F46" s="11" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>2337.6</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>11.5</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>7.7</v>
+        <v>19.1</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>98.3</v>
-      </c>
+        <v>53.1</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="8" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="N46" s="3" t="n"/>
+        <v>11.1</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>24.8</v>
+      </c>
       <c r="O46" s="3" t="n">
-        <v>593.8</v>
+        <v>99</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Q46" s="8" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>72.7</v>
+        <v>10.2</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="R46" s="8" t="n">
+        <v>216.8</v>
+      </c>
+      <c r="S46" s="8" t="n">
+        <v>29</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>7.7</v>
+        <v>729</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="V46" s="8" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="W46" s="3" t="n"/>
+        <v>643.4</v>
+      </c>
+      <c r="W46" s="8" t="n">
+        <v>24.1</v>
+      </c>
       <c r="X46" s="3" t="n">
-        <v>0.3</v>
+        <v>28.1</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>23.7</v>
+        <v>283.9</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>2</v>
+        <v>15.7</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -55,12 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -146,7 +140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -155,10 +149,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -772,74 +766,76 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>186.2</v>
-      </c>
-      <c r="D4" s="3" t="n">
+        <v>136.2</v>
+      </c>
+      <c r="D4" s="10" t="n">
         <v>28.1</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F4" s="11" t="n">
-        <v>84.31</v>
+      <c r="F4" s="3" t="n">
+        <v>24.5</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>118.2</v>
+        <v>81.7</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>12.9</v>
+        <v>2.9</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="8" t="n">
+      <c r="L4" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>83.40000000000001</v>
+      <c r="N4" s="3" t="n">
+        <v>23.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q4" s="3" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>28.8</v>
+      </c>
       <c r="R4" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="S4" s="8" t="n">
-        <v>27.1</v>
+      <c r="S4" s="3" t="n">
+        <v>22.1</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="U4" s="8" t="n">
+      <c r="U4" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X4" s="8" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="X4" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>1811.8</v>
+        <v>181.8</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>15.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -855,19 +851,19 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2903.8</v>
-      </c>
-      <c r="D5" s="8" t="n">
+        <v>203.8</v>
+      </c>
+      <c r="D5" s="10" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>34.1</v>
+        <v>14.4</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>16.8</v>
@@ -879,52 +875,52 @@
         <v>5.5</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N5" s="8" t="n">
+      <c r="N5" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>199</v>
+        <v>909</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R5" s="8" t="n">
+      <c r="R5" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>156.6</v>
+        <v>56.6</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="V5" s="8" t="n">
+      <c r="V5" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X5" s="8" t="n">
-        <v>27.8</v>
+      <c r="X5" s="11" t="n">
+        <v>72.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>11</v>
+        <v>141.1</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -940,13 +936,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1422.3</v>
-      </c>
-      <c r="D6" s="8" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="D6" s="10" t="n">
         <v>34.2</v>
       </c>
-      <c r="E6" s="10" t="n">
-        <v>18.8</v>
+      <c r="E6" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>26.5</v>
@@ -954,8 +950,8 @@
       <c r="G6" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="H6" s="8" t="n">
-        <v>872.6</v>
+      <c r="H6" s="11" t="n">
+        <v>184.6</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>14.6</v>
@@ -964,7 +960,7 @@
         <v>7.2</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>20</v>
@@ -978,38 +974,38 @@
       <c r="O6" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="P6" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" s="8" t="n">
-        <v>21.7</v>
+      <c r="P6" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>32.7</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="S6" s="8" t="n">
+      <c r="S6" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>2929.8</v>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v>20.7</v>
+        <v>22.8</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W6" s="3" t="n">
-        <v>23.7</v>
+      <c r="W6" s="11" t="n">
+        <v>31.7</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>166.4</v>
+        <v>16614.1</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1025,16 +1021,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4785.1</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>27</v>
+        <v>6472.5</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>15.4</v>
@@ -1043,13 +1039,13 @@
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>4.3</v>
+        <v>47.9</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>7.9</v>
+        <v>1.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>20.1</v>
@@ -1064,37 +1060,37 @@
         <v>100</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q7" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q7" s="3" t="n">
         <v>34.2</v>
       </c>
-      <c r="R7" s="8" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="S7" s="8" t="n">
+      <c r="R7" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>120.6</v>
-      </c>
-      <c r="U7" s="8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="U7" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="V7" s="11" t="n">
         <v>29.5</v>
       </c>
-      <c r="W7" s="8" t="n">
+      <c r="W7" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>27.3</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>166.2</v>
+        <v>66.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>13.8</v>
+        <v>15.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1110,12 +1106,12 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1299</v>
-      </c>
-      <c r="D8" s="8" t="n">
+        <v>299</v>
+      </c>
+      <c r="D8" s="10" t="n">
         <v>34.6</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="F8" s="3" t="n">
@@ -1124,59 +1120,59 @@
       <c r="G8" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="H8" s="8" t="n">
-        <v>19</v>
+      <c r="H8" s="11" t="n">
+        <v>12</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K8" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="K8" s="3" t="n">
         <v>30.9</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="M8" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>24</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>196.5</v>
+        <v>96.5</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Q8" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q8" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>23.1</v>
+        <v>25.1</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>298</v>
+        <v>98</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W8" s="8" t="n">
-        <v>1.9</v>
+      <c r="W8" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>20.6</v>
@@ -1195,28 +1191,28 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>11783.5</v>
+        <v>1781.2</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>164.8</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>196.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>1130.8</v>
+        <v>1301.7</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>161.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>127.5</v>
+        <v>12.8</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>30.9</v>
@@ -1225,31 +1221,31 @@
         <v>100.2</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>199.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>112.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1494.5</v>
+        <v>894.2</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>1.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>149.6</v>
+        <v>1179.6</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>121.9</v>
+        <v>122.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1135.7</v>
+        <v>155.1</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>329.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>132.8</v>
@@ -1258,10 +1254,10 @@
         <v>1116.8</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>1133.5</v>
+        <v>133.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>1388.8</v>
+        <v>388.8</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>141.6</v>
@@ -1280,31 +1276,31 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>356.7</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>393</v>
-      </c>
-      <c r="E10" s="10" t="n">
+        <v>8188.5</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>19.4</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G10" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>17.9</v>
+        <v>11.9</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="8" t="n">
+      <c r="L10" s="3" t="n">
         <v>20</v>
       </c>
       <c r="M10" s="3" t="n">
@@ -1319,17 +1315,17 @@
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="8" t="n">
+      <c r="Q10" s="3" t="n">
         <v>29.9</v>
       </c>
-      <c r="R10" s="8" t="n">
-        <v>24.4</v>
+      <c r="R10" s="3" t="n">
+        <v>94.40000000000001</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>27.1</v>
+        <v>27.8</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>166</v>
+        <v>66</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>16.2</v>
@@ -1337,17 +1333,17 @@
       <c r="V10" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="W10" s="8" t="n">
+      <c r="W10" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>26.7</v>
+      <c r="X10" s="11" t="n">
+        <v>16.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>79.8</v>
+        <v>72.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>18.3</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1365,13 +1361,13 @@
       <c r="C11" s="3" t="n">
         <v>1265.6</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="G11" s="3" t="n">
@@ -1381,28 +1377,28 @@
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M11" s="8" t="n">
+      <c r="M11" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="N11" s="8" t="n">
-        <v>24.5</v>
+      <c r="N11" s="3" t="n">
+        <v>24.3</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>927.3</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>29.9</v>
@@ -1410,29 +1406,29 @@
       <c r="R11" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="S11" s="3" t="n">
+      <c r="S11" s="11" t="n">
         <v>29.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>170.6</v>
+        <v>720.6</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V11" s="8" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>24.9</v>
+      <c r="V11" s="11" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="W11" s="11" t="n">
+        <v>16.9</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>684</v>
+        <v>2894</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>5.1</v>
+        <v>11.8</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1448,46 +1444,46 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>247.1</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="F12" s="10" t="n">
+        <v>347.1</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="F12" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="I12" s="3" t="n">
-        <v>22.1</v>
+      <c r="I12" s="11" t="n">
+        <v>227.1</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>21.9</v>
+      <c r="M12" s="11" t="n">
+        <v>350.5</v>
+      </c>
+      <c r="N12" s="11" t="n">
+        <v>17.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>27.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>10.8</v>
+        <v>0.5</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>31.8</v>
@@ -1496,19 +1492,19 @@
         <v>24.9</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>27.1</v>
+        <v>21.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>59.8</v>
+        <v>51.8</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="W12" s="8" t="n">
-        <v>284.6</v>
+        <v>21.9</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>28.8</v>
@@ -1517,7 +1513,7 @@
         <v>76.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>181.7</v>
+        <v>21.6</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1533,16 +1529,16 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1428.6</v>
-      </c>
-      <c r="D13" s="8" t="n">
+        <v>428.6</v>
+      </c>
+      <c r="D13" s="3" t="n">
         <v>32.8</v>
       </c>
-      <c r="E13" s="10" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>26.6</v>
+      <c r="E13" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>86.59999999999999</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>12.4</v>
@@ -1551,13 +1547,13 @@
         <v>19.9</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>13.3</v>
+        <v>18.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>22.1</v>
@@ -1577,32 +1573,32 @@
       <c r="Q13" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R13" s="8" t="n">
+      <c r="R13" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>25.8</v>
+      <c r="S13" s="11" t="n">
+        <v>21.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>52.7</v>
+        <v>427.4</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="V13" s="8" t="n">
+      <c r="V13" s="3" t="n">
         <v>28</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>29.3</v>
+        <v>29.5</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>77.59999999999999</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1621,18 +1617,18 @@
         <v>190.3</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E14" s="10" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E14" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="I14" s="3" t="n">
@@ -1641,9 +1637,7 @@
       <c r="J14" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K14" s="8" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="K14" s="3" t="inlineStr"/>
       <c r="L14" s="3" t="n">
         <v>22.4</v>
       </c>
@@ -1651,25 +1645,25 @@
         <v>22.1</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>264</v>
+        <v>26.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>197.3</v>
+        <v>97.3</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>22.4</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="S14" s="8" t="n">
+      <c r="S14" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>189</v>
+        <v>89</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>2.9</v>
@@ -1677,17 +1671,17 @@
       <c r="V14" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W14" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="X14" s="8" t="n">
+      <c r="W14" s="11" t="n">
+        <v>211.6</v>
+      </c>
+      <c r="X14" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>9.1</v>
+        <v>10.9</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1703,48 +1697,48 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>359.6</v>
+        <v>282.8</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>32.5</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E15" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="F15" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="G15" s="11" t="n">
         <v>11.7</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K15" s="3" t="n">
-        <v>25.1</v>
+      <c r="K15" s="11" t="n">
+        <v>51.7</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="11" t="n">
         <v>21.6</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q15" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="3" t="n">
         <v>32</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1754,7 +1748,7 @@
         <v>29.2</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>161.7</v>
+        <v>61.7</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>18.2</v>
@@ -1762,17 +1756,17 @@
       <c r="V15" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W15" s="8" t="n">
+      <c r="W15" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>738.1</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>10.1</v>
+        <v>100.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1791,13 +1785,13 @@
         <v>1291.2</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>157.9</v>
+        <v>167.9</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>1105.5</v>
+        <v>105.5</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>5131.7</v>
+        <v>151.4</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>52.4</v>
@@ -1806,7 +1800,7 @@
         <v>99.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>111.5</v>
+        <v>11.5</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>19.4</v>
@@ -1821,10 +1815,10 @@
         <v>109.5</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1130.7</v>
+        <v>1230.7</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>27490.1</v>
+        <v>2490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
@@ -1833,28 +1827,28 @@
         <v>148.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1121.9</v>
+        <v>121.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1136.1</v>
+        <v>1136.2</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>331.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>176.6</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>133.7</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1120.7</v>
+        <v>120.7</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>162.5</v>
+        <v>142.5</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1407.4</v>
+        <v>1407.6</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>34.4</v>
@@ -1873,15 +1867,15 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1318.2</v>
+        <v>318.2</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="E17" s="10" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="E17" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="9" t="n">
         <v>26.3</v>
       </c>
       <c r="G17" s="3" t="n">
@@ -1896,48 +1890,50 @@
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="L17" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>98</v>
+        <v>398</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>29.7</v>
+        <v>29.1</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="S17" s="8" t="n">
-        <v>28.2</v>
+      <c r="S17" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>166.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="W17" s="8" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X17" s="3" t="n">
-        <v>28.5</v>
+        <v>15.8</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W17" s="11" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="X17" s="11" t="n">
+        <v>84.59999999999999</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>181.5</v>
+        <v>81.5</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>16.9</v>
@@ -1956,31 +1952,31 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1368</v>
-      </c>
-      <c r="D18" s="11" t="n">
+        <v>368</v>
+      </c>
+      <c r="D18" s="12" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="E18" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>28.61</v>
+      <c r="E18" s="10" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>20.4</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J18" s="8" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="K18" s="8" t="n">
-        <v>10.4</v>
+      <c r="J18" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K18" s="11" t="n">
+        <v>6.4</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>21.4</v>
@@ -1988,11 +1984,11 @@
       <c r="M18" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="N18" s="8" t="n">
-        <v>224.8</v>
+      <c r="N18" s="11" t="n">
+        <v>12.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>97.3</v>
+        <v>91.3</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
@@ -2000,29 +1996,29 @@
       <c r="Q18" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="R18" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="S18" s="8" t="n">
+      <c r="S18" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="V18" s="8" t="n">
+      <c r="V18" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>71.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>111</v>
@@ -2041,55 +2037,55 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2260.6</v>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>30.84</v>
-      </c>
-      <c r="E19" s="3" t="n">
+        <v>265.6</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E19" s="10" t="n">
         <v>22.2</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H19" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="L19" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>22</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>86.3</v>
+        <v>26.3</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>197.6</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q19" s="3" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="Q19" s="11" t="n">
         <v>29.9</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>26</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>31.1</v>
+        <v>51.1</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>73.7</v>
@@ -2097,20 +2093,20 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="8" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="W19" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X19" s="8" t="n">
-        <v>71.09999999999999</v>
+      <c r="V19" s="11" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="W19" s="11" t="n">
+        <v>289.8</v>
+      </c>
+      <c r="X19" s="3" t="n">
+        <v>24.1</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>89</v>
+        <v>829</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>78.3</v>
+        <v>185.9</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2126,16 +2122,16 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>365.9</v>
+        <v>3865.9</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="10" t="n">
         <v>21.5</v>
       </c>
-      <c r="F20" s="8" t="n">
-        <v>26.5</v>
+      <c r="F20" s="11" t="n">
+        <v>8.1</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>19.9</v>
@@ -2143,8 +2139,8 @@
       <c r="H20" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="I20" s="8" t="n">
-        <v>28.1</v>
+      <c r="I20" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>14.5</v>
@@ -2158,26 +2154,26 @@
       <c r="M20" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="N20" s="8" t="n">
-        <v>35.4</v>
+      <c r="N20" s="3" t="n">
+        <v>25.4</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>98</v>
+        <v>928</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="R20" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="R20" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>162.3</v>
+        <v>12.3</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>16.6</v>
@@ -2185,14 +2181,14 @@
       <c r="V20" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="W20" s="8" t="n">
-        <v>23.8</v>
+      <c r="W20" s="11" t="n">
+        <v>28.8</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>27.2</v>
+        <v>21.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>715</v>
+        <v>125</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>19.1</v>
@@ -2216,14 +2212,14 @@
       <c r="D21" s="3" t="n">
         <v>30.7</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="10" t="n">
         <v>21.2</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>29.5</v>
+        <v>9.5</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>19.6</v>
@@ -2235,22 +2231,22 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>18.6</v>
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>25.6</v>
+        <v>23.6</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>30.6</v>
@@ -2259,7 +2255,7 @@
         <v>26.2</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>31.2</v>
+        <v>91.2</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>71.2</v>
@@ -2267,20 +2263,20 @@
       <c r="U21" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V21" s="8" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="W21" s="8" t="n">
-        <v>16.6</v>
+      <c r="V21" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W21" s="11" t="n">
+        <v>46.6</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>77.3</v>
+        <v>712.3</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2298,13 +2294,13 @@
       <c r="C22" s="3" t="n">
         <v>399.3</v>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="3" t="n">
         <v>32.9</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="10" t="n">
         <v>21.1</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="3" t="n">
         <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
@@ -2314,21 +2310,21 @@
         <v>19.8</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N22" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="N22" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="O22" s="3" t="n">
@@ -2347,25 +2343,25 @@
         <v>89.3</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>160.5</v>
+        <v>60.5</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>26.8</v>
+        <v>86.5</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X22" s="8" t="n">
-        <v>29.1</v>
+      <c r="X22" s="11" t="n">
+        <v>29.4</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>186</v>
+        <v>86</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>14.9</v>
+        <v>1244.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2381,31 +2377,31 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>17439.6</v>
+        <v>8519.6</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>164.5</v>
+        <v>1468.5</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>107.2</v>
+        <v>1074.2</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>132.4</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>250.3</v>
+        <v>50.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1101.8</v>
+        <v>101.8</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>19.3</v>
+        <v>104.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>19.3</v>
+        <v>495.1</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>108.2</v>
@@ -2414,31 +2410,31 @@
         <v>1107</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1126.8</v>
+        <v>126.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1489.4</v>
+        <v>489.4</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>155.7</v>
+        <v>1565.7</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1146.8</v>
+        <v>146.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>325.1</v>
+        <v>3325.1</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>134.4</v>
+        <v>138.4</v>
       </c>
       <c r="W23" s="3" t="n">
         <v>120.3</v>
@@ -2447,10 +2443,10 @@
         <v>140.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>2399</v>
+        <v>399</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>36.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2466,12 +2462,12 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>347.9</v>
+        <v>343.9</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>315.1</v>
-      </c>
-      <c r="E24" s="9" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E24" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="F24" s="9" t="n">
@@ -2489,21 +2485,23 @@
       <c r="J24" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="N24" s="8" t="n">
-        <v>22.4</v>
+      <c r="N24" s="3" t="n">
+        <v>25.4</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.4</v>
+        <v>10.4</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>31.1</v>
@@ -2512,10 +2510,10 @@
         <v>25.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>29.4</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>165.1</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>15.9</v>
@@ -2523,17 +2521,17 @@
       <c r="V24" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="W24" s="8" t="n">
+      <c r="W24" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="X24" s="8" t="n">
-        <v>282.2</v>
+      <c r="X24" s="11" t="n">
+        <v>29.2</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>17.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2551,17 +2549,17 @@
       <c r="C25" s="3" t="n">
         <v>106.7</v>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D25" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="E25" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>23.5</v>
+        <v>23.9</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>20.2</v>
@@ -2573,7 +2571,7 @@
         <v>0.5</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>22.4</v>
@@ -2582,38 +2580,38 @@
         <v>22.1</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>264.4</v>
+        <v>26.4</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>97</v>
+        <v>914</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="R25" s="8" t="n">
-        <v>284.1</v>
-      </c>
-      <c r="S25" s="8" t="n">
+      <c r="R25" s="3" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="S25" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>184.4</v>
-      </c>
-      <c r="U25" s="3" t="inlineStr"/>
-      <c r="V25" s="3" t="n">
-        <v>244.1</v>
-      </c>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="V25" s="3" t="inlineStr"/>
       <c r="W25" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="11" t="n">
         <v>26.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>81.7</v>
+        <v>8417.4</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2635,26 +2633,26 @@
       <c r="D26" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="E26" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="F26" s="8" t="n">
-        <v>29.1</v>
+      <c r="E26" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>23.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>14.1</v>
+        <v>12.1</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>10.9</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>16.1</v>
+        <v>6.1</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>21.4</v>
@@ -2663,28 +2661,28 @@
         <v>21.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>25.5</v>
+        <v>25.9</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>100</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="R26" s="8" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="S26" s="8" t="n">
-        <v>280.9</v>
+      <c r="R26" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>28</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>192</v>
+        <v>92</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>23.8</v>
@@ -2692,14 +2690,14 @@
       <c r="W26" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X26" s="8" t="n">
-        <v>79.09999999999999</v>
+      <c r="X26" s="11" t="n">
+        <v>71.09999999999999</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>191.8</v>
+        <v>91.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>2.4</v>
+        <v>124.5</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2715,16 +2713,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2322</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="E27" s="10" t="n">
+        <v>322</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="F27" s="8" t="n">
-        <v>25.5</v>
+      <c r="F27" s="12" t="n">
+        <v>85.40000000000001</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>19.9</v>
@@ -2735,12 +2733,14 @@
       <c r="I27" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="n">
+        <v>3.4</v>
+      </c>
       <c r="K27" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>20.7</v>
+        <v>50.3</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>20.5</v>
@@ -2749,7 +2749,7 @@
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.4</v>
@@ -2757,31 +2757,33 @@
       <c r="Q27" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R27" s="8" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S27" s="8" t="n">
-        <v>89</v>
+      <c r="R27" s="11" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>73.2</v>
+        <v>23.2</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>26.9</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X27" s="8" t="n">
-        <v>29</v>
+        <v>94.40000000000001</v>
+      </c>
+      <c r="X27" s="11" t="n">
+        <v>289</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>81.8</v>
       </c>
-      <c r="Z27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2796,21 +2798,23 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1290.7</v>
-      </c>
-      <c r="D28" s="11" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="E28" s="10" t="n">
+        <v>290.7</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="E28" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="G28" s="8" t="n">
+      <c r="G28" s="11" t="n">
         <v>11.3</v>
       </c>
-      <c r="H28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="I28" s="3" t="n">
         <v>2.2</v>
       </c>
@@ -2818,39 +2822,39 @@
         <v>3.8</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="N28" s="8" t="n">
+      <c r="N28" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>297.3</v>
+        <v>97.3</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="S28" s="8" t="n">
+      <c r="S28" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>160.2</v>
+        <v>60.2</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="V28" s="8" t="n">
+      <c r="V28" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="W28" s="3" t="n">
@@ -2863,7 +2867,7 @@
         <v>72.59999999999999</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>10.7</v>
+        <v>107.4</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2879,26 +2883,28 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>12146.8</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E29" s="10" t="n">
+        <v>246.8</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E29" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="G29" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="H29" s="3" t="inlineStr"/>
+      <c r="F29" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="I29" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.6</v>
+        <v>12.6</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>8.4</v>
@@ -2906,7 +2912,7 @@
       <c r="L29" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="M29" s="8" t="n">
+      <c r="M29" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2919,16 +2925,16 @@
         <v>1.1</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="R29" s="8" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="R29" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="S29" s="8" t="n">
+      <c r="S29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>87</v>
+        <v>821</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>14.2</v>
@@ -2939,14 +2945,14 @@
       <c r="W29" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="X29" s="8" t="n">
-        <v>14.6</v>
+      <c r="X29" s="11" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>90.8</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>22.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2968,13 +2974,13 @@
         <v>1145.2</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>1103.2</v>
+        <v>103.2</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>124.2</v>
+        <v>1124.2</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>142</v>
+        <v>42</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>196.6</v>
@@ -2986,52 +2992,52 @@
         <v>111</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>38.8</v>
+        <v>28.8</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>1106.5</v>
+        <v>106.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1105.2</v>
+        <v>105.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>123.9</v>
+        <v>125.9</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>487.6</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>11135.8</v>
+        <v>1135.8</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>120.1</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>1140.9</v>
+        <v>140.9</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>396.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>1126.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>1115.9</v>
+        <v>115.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>135.9</v>
+        <v>132.9</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>1424.7</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>21.8</v>
+        <v>28.1</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3050,13 +3056,13 @@
         <v>211.2</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>20.6</v>
+        <v>0.9</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>8.6</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>24.8</v>
+        <v>14.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>8.4</v>
@@ -3070,26 +3076,28 @@
       <c r="J31" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="L31" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="M31" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="N31" s="8" t="n">
+      <c r="M31" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="N31" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.5</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="R31" s="8" t="n">
+      <c r="R31" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3098,23 +3106,23 @@
       <c r="T31" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
-      <c r="U31" s="8" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="V31" s="8" t="n">
+      <c r="U31" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="V31" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>27.2</v>
+        <v>97.2</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>145.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3130,12 +3138,12 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>384.7</v>
+        <v>8816.9</v>
       </c>
       <c r="D32" s="10" t="n">
         <v>31.1</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="10" t="n">
         <v>19.3</v>
       </c>
       <c r="F32" s="10" t="n">
@@ -3144,17 +3152,17 @@
       <c r="G32" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="H32" s="8" t="n">
+      <c r="H32" s="11" t="n">
         <v>18</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>12.3</v>
+        <v>2.9</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>20.1</v>
@@ -3162,9 +3170,11 @@
       <c r="M32" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="N32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="n">
+        <v>23.9</v>
+      </c>
       <c r="O32" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0</v>
@@ -3172,17 +3182,17 @@
       <c r="Q32" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S32" s="3" t="n">
-        <v>27.5</v>
+      <c r="S32" s="11" t="n">
+        <v>72.5</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>161</v>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v>18.5</v>
+        <v>61</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>27.4</v>
@@ -3190,9 +3200,11 @@
       <c r="W32" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X32" s="3" t="inlineStr"/>
+      <c r="X32" s="3" t="n">
+        <v>97.2</v>
+      </c>
       <c r="Y32" s="3" t="n">
-        <v>174.6</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>19.3</v>
@@ -3216,67 +3228,71 @@
       <c r="D33" s="10" t="n">
         <v>29.2</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="10" t="n">
         <v>19.6</v>
       </c>
       <c r="F33" s="10" t="n">
         <v>24.4</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="H33" s="8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H33" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L33" s="8" t="n">
-        <v>21.5</v>
+        <v>14.8</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>81.5</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="N33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="n">
+        <v>17.8</v>
+      </c>
       <c r="O33" s="3" t="n">
-        <v>299</v>
+        <v>99</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="R33" s="8" t="n">
-        <v>206.6</v>
-      </c>
-      <c r="S33" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S33" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>20.9</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="V33" s="8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="11" t="n">
         <v>23.8</v>
       </c>
-      <c r="X33" s="3" t="inlineStr"/>
+      <c r="X33" s="3" t="n">
+        <v>28.3</v>
+      </c>
       <c r="Y33" s="3" t="n">
-        <v>861.4</v>
+        <v>86.2</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3297,14 +3313,14 @@
       <c r="D34" s="10" t="n">
         <v>31.9</v>
       </c>
-      <c r="E34" s="8" t="n">
-        <v>11.4</v>
+      <c r="E34" s="10" t="n">
+        <v>21.4</v>
       </c>
       <c r="F34" s="10" t="n">
         <v>26.7</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>20.2</v>
@@ -3313,12 +3329,12 @@
         <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>3.5</v>
+        <v>39.5</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L34" s="8" t="n">
+      <c r="L34" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="M34" s="3" t="n">
@@ -3328,22 +3344,22 @@
         <v>25.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>30.5</v>
+        <v>3</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>25.8</v>
+        <v>23.8</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>30.2</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>169.4</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>13.3</v>
@@ -3358,7 +3374,7 @@
         <v>29.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>82.8</v>
+        <v>182.8</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>16.5</v>
@@ -3382,7 +3398,7 @@
       <c r="D35" s="10" t="n">
         <v>31.1</v>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="E35" s="10" t="n">
         <v>20.8</v>
       </c>
       <c r="F35" s="10" t="n">
@@ -3398,55 +3414,55 @@
         <v>2.4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M35" s="8" t="n">
+      <c r="M35" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>197.2</v>
+        <v>97.2</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>10.7</v>
+        <v>7.1</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="8" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="S35" s="8" t="n">
+      <c r="R35" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="S35" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>1614.3</v>
+        <v>61.3</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="V35" s="8" t="n">
+      <c r="V35" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="W35" s="8" t="n">
+      <c r="W35" s="11" t="n">
         <v>16.6</v>
       </c>
-      <c r="X35" s="8" t="n">
+      <c r="X35" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>19.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>18.4</v>
+        <v>811.1</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3467,13 +3483,13 @@
       <c r="D36" s="10" t="n">
         <v>32.1</v>
       </c>
-      <c r="E36" s="8" t="n">
+      <c r="E36" s="10" t="n">
         <v>20.9</v>
       </c>
       <c r="F36" s="10" t="n">
         <v>26.5</v>
       </c>
-      <c r="G36" s="3" t="n">
+      <c r="G36" s="11" t="n">
         <v>11.2</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3483,25 +3499,25 @@
         <v>2.4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K36" s="8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K36" s="3" t="n">
         <v>30.6</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="M36" s="8" t="n">
-        <v>20.1</v>
+      <c r="M36" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>26.2</v>
+        <v>24.2</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>918.5</v>
+        <v>98.5</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>32.1</v>
@@ -3524,14 +3540,14 @@
       <c r="W36" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X36" s="8" t="n">
-        <v>28.3</v>
+      <c r="X36" s="11" t="n">
+        <v>83.90000000000001</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>42.4</v>
+        <v>172</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>211</v>
+        <v>11</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3549,11 +3565,11 @@
       <c r="C37" s="3" t="n">
         <v>1693.7</v>
       </c>
-      <c r="D37" s="9" t="n">
-        <v>1155.4</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>1102</v>
+      <c r="D37" s="10" t="n">
+        <v>155.4</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>102</v>
       </c>
       <c r="F37" s="10" t="n">
         <v>128.7</v>
@@ -3571,52 +3587,52 @@
         <v>18.1</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>135.6</v>
+        <v>35.6</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>1106</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>1803.2</v>
+        <v>105.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>121.1</v>
+        <v>126.1</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>492.9</v>
+        <v>492.7</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>1.7</v>
+        <v>17.1</v>
       </c>
       <c r="Q37" s="3" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="S37" s="3" t="n">
         <v>143.1</v>
       </c>
-      <c r="R37" s="3" t="n">
-        <v>1126.2</v>
-      </c>
-      <c r="S37" s="3" t="n">
-        <v>1143.1</v>
-      </c>
       <c r="T37" s="3" t="n">
-        <v>13821.8</v>
+        <v>8216.799999999999</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>136.8</v>
+        <v>126.8</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>1142.4</v>
+        <v>102.4</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>398.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>1392.7</v>
+        <v>892.1</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3637,7 +3653,7 @@
       <c r="D38" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="10" t="n">
         <v>20.4</v>
       </c>
       <c r="F38" s="10" t="n">
@@ -3647,10 +3663,10 @@
         <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>19.3</v>
+        <v>19.8</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.6</v>
@@ -3669,37 +3685,37 @@
         <v>98.5</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>10.3</v>
+        <v>0.3</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="R38" s="8" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="R38" s="11" t="n">
         <v>25.2</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>169</v>
+        <v>62</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="V38" s="8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="V38" s="3" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>26.3</v>
+        <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>28.5</v>
+        <v>88.5</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>2.9</v>
+        <v>566.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3715,21 +3731,21 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="E39" s="10" t="n">
+        <v>3232.5</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>821.8100000000001</v>
+      </c>
+      <c r="E39" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F39" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="G39" s="8" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H39" s="8" t="n">
+      <c r="G39" s="11" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3738,11 +3754,13 @@
       <c r="J39" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="8" t="n">
+      <c r="K39" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L39" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="M39" s="8" t="n">
+      <c r="M39" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3752,37 +3770,37 @@
         <v>99</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="R39" s="8" t="n">
-        <v>126</v>
-      </c>
-      <c r="S39" s="8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="R39" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="S39" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>163.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v>24.9</v>
+        <v>11.9</v>
+      </c>
+      <c r="V39" s="11" t="n">
+        <v>49.1</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>27.6</v>
+        <v>2.7</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>288.2</v>
+        <v>88.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>13.6</v>
+        <v>8.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3798,12 +3816,12 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1453.1</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E40" s="10" t="n">
+        <v>1534.1</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="E40" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="F40" s="3" t="n">
@@ -3816,33 +3834,33 @@
         <v>18.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>12.7</v>
+        <v>2.1</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M40" s="8" t="n">
+      <c r="M40" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>28.6</v>
+        <v>22.6</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>1797.8</v>
+        <v>97.8</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>32.8</v>
       </c>
-      <c r="R40" s="8" t="n">
+      <c r="R40" s="3" t="n">
         <v>26</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3855,19 +3873,19 @@
         <v>20.2</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W40" s="8" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W40" s="11" t="n">
         <v>23.8</v>
       </c>
       <c r="X40" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>72</v>
+        <v>22.8</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>10.4</v>
+        <v>101.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3883,16 +3901,16 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>269.6</v>
+        <v>965.6</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>31.6</v>
       </c>
-      <c r="E41" s="10" t="n">
+      <c r="E41" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>85.59999999999999</v>
+        <v>25.6</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>12</v>
@@ -3906,8 +3924,8 @@
       <c r="J41" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="K41" s="8" t="n">
-        <v>43.6</v>
+      <c r="K41" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>19.9</v>
@@ -3919,10 +3937,10 @@
         <v>23</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>199</v>
+        <v>98</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>22.3</v>
@@ -3934,25 +3952,25 @@
         <v>24.9</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>192.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v>816.6</v>
-      </c>
-      <c r="W41" s="8" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="X41" s="8" t="n">
-        <v>28</v>
+        <v>2.8</v>
+      </c>
+      <c r="V41" s="11" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X41" s="11" t="n">
+        <v>9218</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>190.5</v>
+        <v>90.5</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>2.9</v>
+        <v>18.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3968,30 +3986,30 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1236.3</v>
+        <v>836.3</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>31.6</v>
       </c>
-      <c r="E42" s="10" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F42" s="8" t="n">
+      <c r="E42" s="12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F42" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="G42" s="8" t="n">
+      <c r="G42" s="11" t="n">
         <v>11.3</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>20</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K42" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K42" s="11" t="n">
         <v>28.1</v>
       </c>
       <c r="L42" s="3" t="n">
@@ -4000,43 +4018,45 @@
       <c r="M42" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="N42" s="8" t="n">
-        <v>26</v>
+      <c r="N42" s="3" t="n">
+        <v>26.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>199</v>
+        <v>1899</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="8" t="n">
+      <c r="Q42" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="R42" s="8" t="n">
+      <c r="R42" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="S42" s="8" t="n">
+      <c r="S42" s="3" t="n">
         <v>29.3</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>197.7</v>
+        <v>97.7</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="W42" s="8" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>28.2</v>
+        <v>0.8</v>
+      </c>
+      <c r="V42" s="11" t="n">
+        <v>822.9</v>
+      </c>
+      <c r="W42" s="11" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="X42" s="11" t="n">
+        <v>88.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>190.6</v>
-      </c>
-      <c r="Z42" s="3" t="inlineStr"/>
+        <v>90.59999999999999</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>2.9</v>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4056,11 +4076,11 @@
       <c r="D43" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="E43" s="10" t="n">
+      <c r="E43" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>25.7</v>
+        <v>29.1</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>8.699999999999999</v>
@@ -4069,13 +4089,13 @@
         <v>19.8</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>3.7</v>
+        <v>13.7</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>21.6</v>
@@ -4087,7 +4107,7 @@
         <v>25.6</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>0.2</v>
@@ -4096,22 +4116,22 @@
         <v>29.1</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v>79.8</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>24.7</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="W43" s="11" t="n">
+        <v>41.4</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>29.1</v>
@@ -4120,7 +4140,7 @@
         <v>18</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>18.2</v>
+        <v>198.2</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4136,61 +4156,61 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>365.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="E44" s="10" t="n">
+      <c r="E44" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="F44" s="8" t="n">
+      <c r="F44" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="H44" s="8" t="n">
-        <v>19.4</v>
+      <c r="H44" s="3" t="n">
+        <v>89.40000000000001</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>28.3</v>
+        <v>22.3</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="N44" s="8" t="n">
+      <c r="N44" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R44" s="3" t="n">
+      <c r="R44" s="11" t="n">
         <v>26.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>30.1</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="U44" s="8" t="n">
-        <v>18.6</v>
+      <c r="U44" s="3" t="n">
+        <v>8.6</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>28.5</v>
@@ -4198,14 +4218,14 @@
       <c r="W44" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="X44" s="8" t="n">
-        <v>32.2</v>
+      <c r="X44" s="3" t="n">
+        <v>82.8</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>84.40000000000001</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>166</v>
+        <v>16</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4220,65 +4240,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="12" t="inlineStr"/>
+      <c r="C45" s="3" t="n">
+        <v>2026.2</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>19165.6</v>
+      </c>
       <c r="E45" s="9" t="n">
-        <v>1121</v>
+        <v>1128</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1796.1</v>
+        <v>2026.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>109.1</v>
+        <v>9.1</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>114.7</v>
+        <v>1114.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>10.7</v>
+        <v>1101</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>18.4</v>
+        <v>118.4</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>172.3</v>
+        <v>743.1</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>1166.9</v>
+        <v>11665.9</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>122.9</v>
+        <v>128.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>148.7</v>
+        <v>1148.8</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>293.8</v>
+        <v>292.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1752.8</v>
+        <v>172.8</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="S45" s="3" t="inlineStr"/>
-      <c r="T45" s="3" t="inlineStr"/>
+        <v>1469.1</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>174.1</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>1450.8</v>
+      </c>
       <c r="U45" s="3" t="n">
-        <v>168.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>138.1</v>
-      </c>
-      <c r="W45" s="3" t="inlineStr"/>
-      <c r="X45" s="3" t="inlineStr"/>
+        <v>158.1</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>172.2</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>84.5</v>
+      </c>
       <c r="Y45" s="3" t="n">
-        <v>3503.7</v>
+        <v>900.1</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>9316</v>
+        <v>56</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4294,19 +4326,19 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>2337.6</v>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E46" s="10" t="n">
+        <v>237.6</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E46" s="9" t="n">
         <v>20.2</v>
       </c>
       <c r="F46" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="G46" s="8" t="n">
-        <v>11.5</v>
+      <c r="G46" s="11" t="n">
+        <v>21.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>19.1</v>
@@ -4315,13 +4347,15 @@
         <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="11" t="n">
         <v>11.1</v>
       </c>
-      <c r="M46" s="8" t="n">
+      <c r="M46" s="3" t="n">
         <v>20</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4331,37 +4365,37 @@
         <v>99</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="8" t="n">
-        <v>216.8</v>
-      </c>
-      <c r="S46" s="8" t="n">
+      <c r="R46" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S46" s="3" t="n">
         <v>29</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>729</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V46" s="8" t="n">
-        <v>643.4</v>
-      </c>
-      <c r="W46" s="8" t="n">
+      <c r="V46" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="W46" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>28.1</v>
+        <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>283.9</v>
+        <v>83.8</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>15.7</v>
+        <v>62.5</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -140,16 +140,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -766,7 +763,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>136.2</v>
+        <v>186.2</v>
       </c>
       <c r="D4" s="10" t="n">
         <v>28.1</v>
@@ -775,16 +772,16 @@
         <v>20</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>81.7</v>
+        <v>87.2</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1.7</v>
+        <v>11.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>2.9</v>
@@ -808,13 +805,13 @@
         <v>0.2</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>22.1</v>
+        <v>27.1</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>68.90000000000001</v>
@@ -826,13 +823,13 @@
         <v>25.2</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>82.8</v>
+        <v>22.8</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>181.8</v>
+        <v>81.8</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>5.8</v>
@@ -851,7 +848,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>203.8</v>
+        <v>403.8</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>32.6</v>
@@ -875,7 +872,7 @@
         <v>5.5</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>18.9</v>
@@ -887,7 +884,7 @@
         <v>21.6</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>909</v>
+        <v>99</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0.2</v>
@@ -913,11 +910,11 @@
       <c r="W5" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X5" s="11" t="n">
-        <v>72.8</v>
+      <c r="X5" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>141.1</v>
+        <v>7174</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>8.199999999999999</v>
@@ -936,13 +933,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>122.3</v>
+        <v>422.3</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>34.2</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>12.2</v>
+        <v>28.8</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>26.5</v>
@@ -950,8 +947,8 @@
       <c r="G6" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="H6" s="11" t="n">
-        <v>184.6</v>
+      <c r="H6" s="8" t="n">
+        <v>15.2</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>14.6</v>
@@ -974,8 +971,8 @@
       <c r="O6" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="P6" s="11" t="n">
-        <v>80</v>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>32.7</v>
@@ -987,22 +984,22 @@
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>22.8</v>
+        <v>92.8</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="W6" s="11" t="n">
-        <v>31.7</v>
+        <v>28.1</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>23.7</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>16614.1</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>13.2</v>
@@ -1021,16 +1018,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6472.5</v>
+        <v>472.5</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>21</v>
+        <v>34.8</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>72</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>15.4</v>
@@ -1039,10 +1036,10 @@
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>47.9</v>
+        <v>84.7</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.9</v>
+        <v>7.9</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
@@ -1066,7 +1063,7 @@
         <v>34.2</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>27.1</v>
@@ -1077,7 +1074,7 @@
       <c r="U7" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="V7" s="11" t="n">
+      <c r="V7" s="3" t="n">
         <v>29.5</v>
       </c>
       <c r="W7" s="3" t="n">
@@ -1090,7 +1087,7 @@
         <v>66.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>15.8</v>
+        <v>13.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1120,14 +1117,14 @@
       <c r="G8" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H8" s="8" t="n">
         <v>12</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>30.9</v>
@@ -1142,7 +1139,7 @@
         <v>24</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>96.5</v>
+        <v>296.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.8</v>
@@ -1172,7 +1169,7 @@
         <v>26.1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>20.6</v>
@@ -1191,7 +1188,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1781.2</v>
+        <v>1783.2</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>164.8</v>
@@ -1200,19 +1197,19 @@
         <v>96.90000000000001</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>1301.7</v>
+        <v>230.8</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>12.8</v>
+        <v>27.5</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>30.9</v>
@@ -1227,40 +1224,40 @@
         <v>112.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>894.2</v>
+        <v>494.2</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1179.6</v>
+        <v>149.6</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>122.9</v>
+        <v>121.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>155.1</v>
+        <v>135.7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>329.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>132.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1116.8</v>
+        <v>116.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>133.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>388.8</v>
+        <v>3788.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>141.6</v>
+        <v>41.6</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1276,13 +1273,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8188.5</v>
+        <v>35.4</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>33</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>19.4</v>
+        <v>19.8</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>26.2</v>
@@ -1291,15 +1288,17 @@
         <v>13.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>11.9</v>
+        <v>17.9</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
+        <v>5.5</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>20</v>
       </c>
@@ -1315,14 +1314,14 @@
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="8" t="n">
         <v>29.9</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>27.8</v>
+        <v>27.1</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>66</v>
@@ -1336,14 +1335,14 @@
       <c r="W10" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="X10" s="11" t="n">
-        <v>16.2</v>
+      <c r="X10" s="3" t="n">
+        <v>26.7</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>72.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>18.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1359,7 +1358,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1265.6</v>
+        <v>265.6</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>30.1</v>
@@ -1367,7 +1366,7 @@
       <c r="E11" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="10" t="n">
         <v>24.9</v>
       </c>
       <c r="G11" s="3" t="n">
@@ -1377,7 +1376,7 @@
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.8</v>
@@ -1392,10 +1391,10 @@
         <v>20.9</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>927.3</v>
+        <v>21.3</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.6</v>
@@ -1404,31 +1403,31 @@
         <v>29.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="S11" s="11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="S11" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>720.6</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V11" s="11" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="W11" s="11" t="n">
-        <v>16.9</v>
+      <c r="V11" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>94.90000000000001</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>2894</v>
+        <v>894</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>11.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1444,15 +1443,15 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>347.1</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="E12" s="12" t="n">
+        <v>242.1</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="E12" s="11" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="10" t="n">
         <v>27.2</v>
       </c>
       <c r="G12" s="3" t="n">
@@ -1461,8 +1460,8 @@
       <c r="H12" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="I12" s="11" t="n">
-        <v>227.1</v>
+      <c r="I12" s="3" t="n">
+        <v>2.7</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>14.6</v>
@@ -1473,14 +1472,14 @@
       <c r="L12" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="11" t="n">
-        <v>350.5</v>
-      </c>
-      <c r="N12" s="11" t="n">
-        <v>17.9</v>
+      <c r="M12" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>27.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>927.5</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.5</v>
@@ -1492,10 +1491,10 @@
         <v>24.9</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>21.1</v>
+        <v>27.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>51.8</v>
+        <v>59.8</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>19.8</v>
@@ -1513,7 +1512,7 @@
         <v>76.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>21.6</v>
+        <v>81.7</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1537,8 +1536,8 @@
       <c r="E13" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="F13" s="12" t="n">
-        <v>86.59999999999999</v>
+      <c r="F13" s="10" t="n">
+        <v>26.6</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>12.4</v>
@@ -1547,10 +1546,10 @@
         <v>19.9</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>18.3</v>
+        <v>3.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
@@ -1576,11 +1575,11 @@
       <c r="R13" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="S13" s="11" t="n">
-        <v>21.8</v>
+      <c r="S13" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>427.4</v>
+        <v>52.7</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>23.3</v>
@@ -1592,7 +1591,7 @@
         <v>24.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>77.59999999999999</v>
@@ -1616,13 +1615,13 @@
       <c r="C14" s="3" t="n">
         <v>190.3</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>30.7</v>
+      <c r="D14" s="8" t="n">
+        <v>7.1</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="10" t="n">
         <v>26.3</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1632,12 +1631,14 @@
         <v>20.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
+        <v>82.09999999999999</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="L14" s="3" t="n">
         <v>22.4</v>
       </c>
@@ -1671,8 +1672,8 @@
       <c r="V14" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W14" s="11" t="n">
-        <v>211.6</v>
+      <c r="W14" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>25.5</v>
@@ -1680,9 +1681,7 @@
       <c r="Y14" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="Z14" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="Z14" s="3" t="inlineStr"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1697,7 +1696,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>282.8</v>
+        <v>359.6</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>32.5</v>
@@ -1705,38 +1704,38 @@
       <c r="E15" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F15" s="10" t="n">
         <v>26.7</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="8" t="n">
         <v>11.7</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K15" s="11" t="n">
-        <v>51.7</v>
+      <c r="K15" s="3" t="n">
+        <v>23.7</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" s="11" t="n">
+      <c r="M15" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>32</v>
@@ -1763,10 +1762,10 @@
         <v>28.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>738.1</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>100.6</v>
+        <v>10.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1782,16 +1781,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1291.2</v>
+        <v>1221.2</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>167.9</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>105.5</v>
+        <v>1255.1</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>151.4</v>
+        <v>131.9</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>52.4</v>
@@ -1809,16 +1808,16 @@
         <v>36.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1110.6</v>
+        <v>110.6</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>109.5</v>
+        <v>109.8</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>1230.7</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2490.1</v>
+        <v>1490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
@@ -1827,10 +1826,10 @@
         <v>148.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>121.9</v>
+        <v>1221.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1136.2</v>
+        <v>1136.1</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>331.8</v>
@@ -1870,12 +1869,12 @@
         <v>318.2</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>81.59999999999999</v>
+        <v>31.6</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="10" t="n">
         <v>26.3</v>
       </c>
       <c r="G17" s="3" t="n">
@@ -1885,13 +1884,13 @@
         <v>19.8</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" s="3" t="n">
-        <v>1.1</v>
+      <c r="K17" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>22.1</v>
@@ -1903,13 +1902,13 @@
         <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>398</v>
+        <v>928</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>29.1</v>
+        <v>29.7</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>24.4</v>
@@ -1921,16 +1920,16 @@
         <v>66.40000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W17" s="11" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="X17" s="11" t="n">
-        <v>84.59999999999999</v>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>81.5</v>
@@ -1954,18 +1953,16 @@
       <c r="C18" s="3" t="n">
         <v>368</v>
       </c>
-      <c r="D18" s="12" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="E18" s="10" t="n">
+      <c r="D18" s="3" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E18" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="F18" s="12" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="F18" s="3" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="n">
         <v>80.40000000000001</v>
       </c>
@@ -1973,10 +1970,10 @@
         <v>2.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K18" s="11" t="n">
-        <v>6.4</v>
+        <v>14.3</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>10.4</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>21.4</v>
@@ -1984,11 +1981,11 @@
       <c r="M18" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="N18" s="11" t="n">
-        <v>12.8</v>
+      <c r="N18" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>91.3</v>
+        <v>97.3</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
@@ -1996,14 +1993,14 @@
       <c r="Q18" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="11" t="n">
+      <c r="R18" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>20</v>
@@ -2018,10 +2015,10 @@
         <v>21.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2042,7 +2039,7 @@
       <c r="D19" s="3" t="n">
         <v>30.4</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="F19" s="3" t="n">
@@ -2051,8 +2048,8 @@
       <c r="G19" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H19" s="3" t="n">
-        <v>21.4</v>
+      <c r="H19" s="8" t="n">
+        <v>91.40000000000001</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.6</v>
@@ -2076,16 +2073,16 @@
         <v>97.59999999999999</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="Q19" s="11" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Q19" s="8" t="n">
         <v>29.9</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>26</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>51.1</v>
+        <v>31.1</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>73.7</v>
@@ -2093,20 +2090,20 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="11" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="W19" s="11" t="n">
-        <v>289.8</v>
+      <c r="V19" s="3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="W19" s="8" t="n">
+        <v>28.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>24.1</v>
+        <v>27.1</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>829</v>
+        <v>89</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>185.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2122,16 +2119,16 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3865.9</v>
+        <v>365.9</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="E20" s="10" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>8.1</v>
+      <c r="E20" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>19.9</v>
@@ -2140,13 +2137,13 @@
         <v>20.6</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>21.6</v>
@@ -2158,19 +2155,19 @@
         <v>25.4</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>928</v>
+        <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>20.9</v>
+        <v>30.7</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="S20" s="3" t="n">
-        <v>27.5</v>
+      <c r="S20" s="8" t="n">
+        <v>17.5</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>12.3</v>
@@ -2181,17 +2178,17 @@
       <c r="V20" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="W20" s="11" t="n">
-        <v>28.8</v>
+      <c r="W20" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>21.2</v>
+        <v>27.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>125</v>
+        <v>725</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2209,10 +2206,10 @@
       <c r="C21" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D21" s="3" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E21" s="10" t="n">
+      <c r="D21" s="8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E21" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="F21" s="3" t="n">
@@ -2237,10 +2234,10 @@
         <v>21.6</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>23.6</v>
+        <v>25.6</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>99</v>
@@ -2255,7 +2252,7 @@
         <v>26.2</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>91.2</v>
+        <v>31.2</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>71.2</v>
@@ -2266,14 +2263,14 @@
       <c r="V21" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W21" s="11" t="n">
-        <v>46.6</v>
+      <c r="W21" s="8" t="n">
+        <v>26.6</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>712.3</v>
+        <v>72.3</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>8.4</v>
@@ -2297,14 +2294,14 @@
       <c r="D22" s="3" t="n">
         <v>32.9</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E22" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>19.8</v>
@@ -2316,13 +2313,13 @@
         <v>4.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>24.7</v>
@@ -2337,7 +2334,7 @@
         <v>32.4</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>25.9</v>
+        <v>29.9</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>89.3</v>
@@ -2346,22 +2343,22 @@
         <v>60.5</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="V22" s="3" t="n">
-        <v>86.5</v>
+        <v>19.2</v>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v>26.5</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X22" s="11" t="n">
-        <v>29.4</v>
+      <c r="X22" s="3" t="n">
+        <v>29.7</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>86</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1244.9</v>
+        <v>144.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2377,19 +2374,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>8519.6</v>
+        <v>1739.6</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1468.5</v>
+        <v>167.5</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1074.2</v>
+        <v>107.2</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>132.4</v>
+        <v>138.8</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>50.3</v>
+        <v>20.3</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>101.8</v>
@@ -2398,10 +2395,10 @@
         <v>10.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>104.5</v>
+        <v>10.4</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>495.1</v>
+        <v>49.1</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>108.2</v>
@@ -2419,7 +2416,7 @@
         <v>2.2</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1565.7</v>
+        <v>155.7</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>128.1</v>
@@ -2428,16 +2425,16 @@
         <v>146.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>3325.1</v>
+        <v>325.1</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>138.4</v>
+        <v>134.4</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>120.3</v>
+        <v>20.3</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>140.8</v>
@@ -2446,7 +2443,7 @@
         <v>399</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>362.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2462,16 +2459,16 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>343.9</v>
+        <v>343.2</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>31.5</v>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E24" s="9" t="n">
         <v>21.4</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>10.1</v>
@@ -2480,13 +2477,13 @@
         <v>20.4</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>21.6</v>
@@ -2507,10 +2504,10 @@
         <v>31.1</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>25.6</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>29.4</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>65.09999999999999</v>
@@ -2524,14 +2521,14 @@
       <c r="W24" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="X24" s="11" t="n">
-        <v>29.2</v>
+      <c r="X24" s="3" t="n">
+        <v>23.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>79.8</v>
+        <v>2981.3</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2549,17 +2546,17 @@
       <c r="C25" s="3" t="n">
         <v>106.7</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="10" t="n">
         <v>26.3</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>23.9</v>
+      <c r="F25" s="10" t="n">
+        <v>23.5</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>20.2</v>
@@ -2571,7 +2568,7 @@
         <v>0.5</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>23.4</v>
+        <v>23.7</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>22.4</v>
@@ -2583,7 +2580,7 @@
         <v>26.4</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>914</v>
+        <v>97</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0.7</v>
@@ -2592,7 +2589,7 @@
         <v>26.2</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>24.1</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>28.7</v>
@@ -2601,17 +2598,19 @@
         <v>84.40000000000001</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="V25" s="3" t="inlineStr"/>
+        <v>5.3</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>14.4</v>
+      </c>
       <c r="W25" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X25" s="11" t="n">
+      <c r="X25" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>8417.4</v>
+        <v>8781.700000000001</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2630,26 +2629,26 @@
       <c r="C26" s="3" t="n">
         <v>290</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="10" t="n">
         <v>25.1</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="F26" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F26" s="10" t="n">
         <v>23.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>12.1</v>
+        <v>14.1</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>6.1</v>
@@ -2661,7 +2660,7 @@
         <v>21.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>100</v>
@@ -2673,13 +2672,13 @@
         <v>24.3</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>28</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>92</v>
+        <v>192</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>2.4</v>
@@ -2690,14 +2689,14 @@
       <c r="W26" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X26" s="11" t="n">
-        <v>71.09999999999999</v>
+      <c r="X26" s="3" t="n">
+        <v>27.1</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>91.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>124.5</v>
+        <v>2.4</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2715,14 +2714,14 @@
       <c r="C27" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D27" s="12" t="n">
-        <v>3</v>
+      <c r="D27" s="10" t="n">
+        <v>30.5</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="F27" s="12" t="n">
-        <v>85.40000000000001</v>
+      <c r="F27" s="10" t="n">
+        <v>25.5</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>19.9</v>
@@ -2740,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>20.5</v>
@@ -2757,8 +2756,8 @@
       <c r="Q27" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R27" s="11" t="n">
-        <v>16.9</v>
+      <c r="R27" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>29</v>
@@ -2769,20 +2768,20 @@
       <c r="U27" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="V27" s="3" t="n">
-        <v>86.90000000000001</v>
+      <c r="V27" s="8" t="n">
+        <v>826.9</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="X27" s="11" t="n">
-        <v>289</v>
+        <v>24.4</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>89</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>81.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>12.4</v>
+        <v>6.4</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2800,16 +2799,16 @@
       <c r="C28" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D28" s="12" t="n">
-        <v>91.8</v>
+      <c r="D28" s="10" t="n">
+        <v>31.8</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="F28" s="10" t="n">
         <v>26.1</v>
       </c>
-      <c r="G28" s="11" t="n">
+      <c r="G28" s="8" t="n">
         <v>11.3</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2834,10 +2833,10 @@
         <v>24.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>97.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>31.2</v>
@@ -2867,7 +2866,7 @@
         <v>72.59999999999999</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>107.4</v>
+        <v>10.7</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2885,16 +2884,16 @@
       <c r="C29" s="3" t="n">
         <v>246.8</v>
       </c>
-      <c r="D29" s="11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F29" s="12" t="n">
-        <v>96</v>
-      </c>
-      <c r="G29" s="11" t="n">
+      <c r="D29" s="10" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="G29" s="8" t="n">
         <v>11</v>
       </c>
       <c r="H29" s="3" t="n">
@@ -2904,7 +2903,7 @@
         <v>1.6</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>8.4</v>
@@ -2925,7 +2924,7 @@
         <v>1.1</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>25.3</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>23.6</v>
@@ -2934,10 +2933,10 @@
         <v>28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>14.2</v>
+        <v>94.2</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>22.4</v>
@@ -2945,8 +2944,8 @@
       <c r="W29" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="X29" s="11" t="n">
-        <v>16.6</v>
+      <c r="X29" s="8" t="n">
+        <v>14.6</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>90.8</v>
@@ -2970,20 +2969,20 @@
       <c r="C30" s="3" t="n">
         <v>11056.2</v>
       </c>
-      <c r="D30" s="9" t="n">
-        <v>1145.2</v>
+      <c r="D30" s="10" t="n">
+        <v>145.2</v>
       </c>
       <c r="E30" s="9" t="n">
         <v>103.2</v>
       </c>
-      <c r="F30" s="9" t="n">
-        <v>1124.2</v>
+      <c r="F30" s="10" t="n">
+        <v>124.2</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>42</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>196.6</v>
+        <v>296.6</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>7.1</v>
@@ -2992,7 +2991,7 @@
         <v>111</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>28.8</v>
+        <v>328.8</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>106.5</v>
@@ -3001,7 +3000,7 @@
         <v>105.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>125.9</v>
+        <v>123.9</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>487.6</v>
@@ -3013,31 +3012,29 @@
         <v>1135.8</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>120.1</v>
+        <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>140.9</v>
+        <v>1240.9</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>396.8</v>
       </c>
-      <c r="U30" s="3" t="n">
-        <v>18</v>
-      </c>
+      <c r="U30" s="3" t="inlineStr"/>
       <c r="V30" s="3" t="n">
-        <v>1126.1</v>
+        <v>126.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>115.8</v>
+        <v>115.9</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>132.9</v>
+        <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>1424.7</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>28.1</v>
+        <v>85.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3056,13 +3053,13 @@
         <v>211.2</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>14.8</v>
+        <v>90.59999999999999</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>8.4</v>
@@ -3077,7 +3074,7 @@
         <v>2.2</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>21.3</v>
@@ -3089,7 +3086,7 @@
         <v>24.8</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>97.5</v>
+        <v>927.5</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>0.6</v>
@@ -3107,7 +3104,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>18.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>25.2</v>
@@ -3116,13 +3113,13 @@
         <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>97.2</v>
+        <v>27.2</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>24.9</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3138,25 +3135,25 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>8816.9</v>
+        <v>384.7</v>
       </c>
       <c r="D32" s="10" t="n">
         <v>31.1</v>
       </c>
-      <c r="E32" s="10" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>25.2</v>
+      <c r="E32" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>23.2</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="H32" s="11" t="n">
+      <c r="H32" s="8" t="n">
         <v>18</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>4.6</v>
@@ -3171,7 +3168,7 @@
         <v>20.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>100</v>
@@ -3185,26 +3182,26 @@
       <c r="R32" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S32" s="11" t="n">
-        <v>72.5</v>
+      <c r="S32" s="3" t="n">
+        <v>27.5</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>61</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>27.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>23.8</v>
+        <v>83.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>97.2</v>
+        <v>27.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>7641.6</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>19.3</v>
@@ -3228,10 +3225,10 @@
       <c r="D33" s="10" t="n">
         <v>29.2</v>
       </c>
-      <c r="E33" s="10" t="n">
+      <c r="E33" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="F33" s="10" t="n">
+      <c r="F33" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="G33" s="3" t="n">
@@ -3250,13 +3247,13 @@
         <v>14.8</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>81.5</v>
+        <v>21.5</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>17.8</v>
+        <v>23.9</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>99</v>
@@ -3265,16 +3262,16 @@
         <v>0.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>22.9</v>
+        <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>20.6</v>
+        <v>28.6</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>20.9</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>11.5</v>
@@ -3282,17 +3279,17 @@
       <c r="V33" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="W33" s="11" t="n">
+      <c r="W33" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>28.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>86.2</v>
+        <v>26.1</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>12.5</v>
+        <v>144.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3313,14 +3310,14 @@
       <c r="D34" s="10" t="n">
         <v>31.9</v>
       </c>
-      <c r="E34" s="10" t="n">
+      <c r="E34" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="F34" s="10" t="n">
+      <c r="F34" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>20.2</v>
@@ -3329,7 +3326,7 @@
         <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>39.5</v>
+        <v>9.5</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.2</v>
@@ -3350,10 +3347,10 @@
         <v>0.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>3</v>
+        <v>30.5</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>23.8</v>
+        <v>25.8</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>30.2</v>
@@ -3374,7 +3371,7 @@
         <v>29.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>182.8</v>
+        <v>82.8</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>16.5</v>
@@ -3398,10 +3395,10 @@
       <c r="D35" s="10" t="n">
         <v>31.1</v>
       </c>
-      <c r="E35" s="10" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F35" s="10" t="n">
+      <c r="E35" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="F35" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3432,16 +3429,16 @@
         <v>97.2</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="3" t="n">
-        <v>24.9</v>
+      <c r="R35" s="8" t="n">
+        <v>46.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>27.8</v>
+        <v>21.8</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>61.3</v>
@@ -3450,19 +3447,19 @@
         <v>17.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W35" s="11" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W35" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>811.1</v>
+        <v>8.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3483,13 +3480,13 @@
       <c r="D36" s="10" t="n">
         <v>32.1</v>
       </c>
-      <c r="E36" s="10" t="n">
+      <c r="E36" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="F36" s="10" t="n">
+      <c r="F36" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="G36" s="11" t="n">
+      <c r="G36" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3514,7 +3511,7 @@
         <v>24.2</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>98.5</v>
+        <v>97.5</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.6</v>
@@ -3537,17 +3534,17 @@
       <c r="V36" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X36" s="11" t="n">
-        <v>83.90000000000001</v>
+      <c r="W36" s="8" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>28.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>172</v>
+        <v>72</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>11</v>
+        <v>1411</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3568,10 +3565,10 @@
       <c r="D37" s="10" t="n">
         <v>155.4</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="9" t="n">
         <v>102</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F37" s="9" t="n">
         <v>128.7</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3593,10 +3590,10 @@
         <v>1106</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>105.2</v>
+        <v>103.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>126.1</v>
+        <v>124.1</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>492.7</v>
@@ -3605,7 +3602,7 @@
         <v>17.1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>153.1</v>
+        <v>153.7</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>126.2</v>
@@ -3614,25 +3611,25 @@
         <v>143.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>8216.799999999999</v>
+        <v>324.8</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>11.7</v>
+        <v>19.7</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>126.8</v>
+        <v>136.8</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>102.4</v>
+        <v>122.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>398.2</v>
+        <v>3928.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>892.1</v>
+        <v>39.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3653,17 +3650,17 @@
       <c r="D38" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="F38" s="9" t="n">
         <v>25.7</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>2</v>
@@ -3690,20 +3687,20 @@
       <c r="Q38" s="3" t="n">
         <v>30.7</v>
       </c>
-      <c r="R38" s="11" t="n">
+      <c r="R38" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>27.4</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>24.3</v>
@@ -3715,7 +3712,7 @@
         <v>78</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>566.1</v>
+        <v>7.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3731,21 +3728,21 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>3232.5</v>
-      </c>
-      <c r="D39" s="12" t="n">
-        <v>821.8100000000001</v>
-      </c>
-      <c r="E39" s="3" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E39" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="F39" s="3" t="n">
+      <c r="F39" s="10" t="n">
         <v>26.1</v>
       </c>
-      <c r="G39" s="11" t="n">
+      <c r="G39" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="H39" s="3" t="n">
+      <c r="H39" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3755,7 +3752,7 @@
         <v>3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>21</v>
@@ -3773,9 +3770,9 @@
         <v>0.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="R39" s="11" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="R39" s="3" t="n">
         <v>26</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3785,13 +3782,13 @@
         <v>163.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="V39" s="11" t="n">
-        <v>49.1</v>
+        <v>11.3</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>22.2</v>
+        <v>23.2</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>2.7</v>
@@ -3800,7 +3797,7 @@
         <v>88.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>8.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3816,15 +3813,15 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1534.1</v>
-      </c>
-      <c r="D40" s="12" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="E40" s="3" t="n">
+        <v>153.7</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E40" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="F40" s="3" t="n">
+      <c r="F40" s="10" t="n">
         <v>25.9</v>
       </c>
       <c r="G40" s="3" t="n">
@@ -3834,10 +3831,10 @@
         <v>18.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -3867,7 +3864,7 @@
         <v>29.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>39.2</v>
+        <v>59.2</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>20.2</v>
@@ -3875,14 +3872,14 @@
       <c r="V40" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W40" s="11" t="n">
+      <c r="W40" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X40" s="3" t="n">
-        <v>26.9</v>
+      <c r="X40" s="8" t="n">
+        <v>86.90000000000001</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>22.8</v>
+        <v>72</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>101.6</v>
@@ -3901,15 +3898,15 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>965.6</v>
+        <v>8985.6</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>31.6</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="F41" s="11" t="n">
+      <c r="F41" s="10" t="n">
         <v>25.6</v>
       </c>
       <c r="G41" s="3" t="n">
@@ -3937,7 +3934,7 @@
         <v>23</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.2</v>
@@ -3948,29 +3945,29 @@
       <c r="R41" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="S41" s="3" t="n">
-        <v>24.9</v>
+      <c r="S41" s="8" t="n">
+        <v>16.9</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V41" s="11" t="n">
-        <v>46.6</v>
+        <v>2</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="X41" s="11" t="n">
-        <v>9218</v>
+      <c r="X41" s="3" t="n">
+        <v>98</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>90.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>18.9</v>
+        <v>8.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3991,13 +3988,13 @@
       <c r="D42" s="3" t="n">
         <v>31.6</v>
       </c>
-      <c r="E42" s="12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F42" s="3" t="n">
+      <c r="E42" s="10" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F42" s="10" t="n">
         <v>25.9</v>
       </c>
-      <c r="G42" s="11" t="n">
+      <c r="G42" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -4006,11 +4003,11 @@
       <c r="I42" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="J42" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K42" s="11" t="n">
-        <v>28.1</v>
+      <c r="J42" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>28.4</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>21.9</v>
@@ -4019,10 +4016,10 @@
         <v>21.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>1899</v>
+        <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
@@ -4042,14 +4039,14 @@
       <c r="U42" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="V42" s="11" t="n">
-        <v>822.9</v>
-      </c>
-      <c r="W42" s="11" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="X42" s="11" t="n">
-        <v>88.2</v>
+      <c r="V42" s="3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>828.2</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>90.59999999999999</v>
@@ -4076,11 +4073,11 @@
       <c r="D43" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="10" t="n">
         <v>21.3</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>29.1</v>
+      <c r="F43" s="10" t="n">
+        <v>24.7</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>8.699999999999999</v>
@@ -4092,7 +4089,7 @@
         <v>2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>13.7</v>
+        <v>3.7</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>0</v>
@@ -4116,7 +4113,7 @@
         <v>29.1</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>80.40000000000001</v>
@@ -4130,17 +4127,17 @@
       <c r="V43" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="W43" s="11" t="n">
-        <v>41.4</v>
+      <c r="W43" s="3" t="n">
+        <v>24.7</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>198.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4156,22 +4153,22 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E44" s="3" t="n">
+        <v>365.9</v>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="E44" s="10" t="n">
         <v>21.3</v>
       </c>
-      <c r="F44" s="3" t="n">
+      <c r="F44" s="10" t="n">
         <v>26.9</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="H44" s="3" t="n">
-        <v>89.40000000000001</v>
+      <c r="H44" s="8" t="n">
+        <v>19.4</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>1.9</v>
@@ -4182,11 +4179,11 @@
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="3" t="n">
-        <v>22.3</v>
+      <c r="L44" s="8" t="n">
+        <v>82.3</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>22.3</v>
+        <v>82.3</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>26.9</v>
@@ -4195,31 +4192,31 @@
         <v>100</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R44" s="11" t="n">
+      <c r="R44" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>30.4</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>162</v>
+        <v>62</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>8.6</v>
+        <v>18.6</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="X44" s="3" t="n">
-        <v>82.8</v>
+      <c r="X44" s="8" t="n">
+        <v>28.2</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>84.40000000000001</v>
@@ -4244,73 +4241,73 @@
         <v>2026.2</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>19165.6</v>
+        <v>1901.6</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1128</v>
+        <v>11298.6</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>2026.1</v>
+        <v>226.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>9.1</v>
+        <v>2.1</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>1114.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>1101</v>
+        <v>11</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>118.4</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>743.1</v>
+        <v>783.6</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>11665.9</v>
+        <v>1166.5</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>128.9</v>
+        <v>123.9</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>1148.8</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>292.8</v>
+        <v>293.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>172.8</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>1469.1</v>
+        <v>149.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>174.1</v>
+        <v>121.1</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>1450.8</v>
+        <v>1230</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>158.1</v>
       </c>
       <c r="W45" s="3" t="n">
+        <v>128.2</v>
+      </c>
+      <c r="X45" s="3" t="n">
         <v>172.2</v>
       </c>
-      <c r="X45" s="3" t="n">
-        <v>84.5</v>
-      </c>
       <c r="Y45" s="3" t="n">
-        <v>900.1</v>
+        <v>503.4</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4331,13 +4328,13 @@
       <c r="D46" s="9" t="n">
         <v>31.7</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="G46" s="11" t="n">
+      <c r="G46" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="H46" s="3" t="n">
@@ -4349,11 +4346,9 @@
       <c r="J46" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" s="11" t="n">
-        <v>11.1</v>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>20</v>
@@ -4362,7 +4357,7 @@
         <v>24.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>0.2</v>
@@ -4377,7 +4372,7 @@
         <v>29</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>22.9</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.4</v>
@@ -4392,10 +4387,10 @@
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>83.8</v>
+        <v>88.8</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>62.5</v>
+        <v>6.2</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -786,13 +786,13 @@
       <c r="J4" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="10" t="n">
         <v>20.1</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -804,7 +804,7 @@
       <c r="P4" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="10" t="n">
         <v>28.7</v>
       </c>
       <c r="R4" s="3" t="n">
@@ -819,10 +819,10 @@
       <c r="U4" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="10" t="n">
         <v>25.2</v>
       </c>
-      <c r="W4" s="3" t="n">
+      <c r="W4" s="10" t="n">
         <v>22.8</v>
       </c>
       <c r="X4" s="3" t="n">
@@ -871,13 +871,13 @@
       <c r="J5" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="10" t="n">
         <v>18.8</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -889,7 +889,7 @@
       <c r="P5" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="10" t="n">
         <v>32.6</v>
       </c>
       <c r="R5" s="3" t="n">
@@ -904,10 +904,10 @@
       <c r="U5" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="10" t="n">
         <v>24</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -956,13 +956,13 @@
       <c r="J6" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="10" t="n">
         <v>20</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -974,7 +974,7 @@
       <c r="P6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="10" t="n">
         <v>32.7</v>
       </c>
       <c r="R6" s="3" t="n">
@@ -989,10 +989,10 @@
       <c r="U6" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="10" t="n">
         <v>28.1</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="10" t="n">
         <v>23.7</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1041,13 +1041,13 @@
       <c r="J7" s="3" t="n">
         <v>7.9</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="10" t="n">
         <v>20.1</v>
       </c>
       <c r="N7" s="3" t="n">
@@ -1059,10 +1059,10 @@
       <c r="P7" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" s="10" t="n">
         <v>34.2</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="11" t="n">
         <v>2.2</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1074,10 +1074,10 @@
       <c r="U7" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="10" t="n">
         <v>29.5</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="10" t="n">
         <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1126,13 +1126,13 @@
       <c r="J8" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="10" t="n">
         <v>30.9</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="10" t="n">
         <v>20.6</v>
       </c>
       <c r="N8" s="3" t="n">
@@ -1144,7 +1144,7 @@
       <c r="P8" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="R8" s="3" t="n">
@@ -1159,10 +1159,10 @@
       <c r="U8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="10" t="n">
         <v>22.2</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="10" t="n">
         <v>21.9</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1211,13 +1211,13 @@
       <c r="J9" s="3" t="n">
         <v>27.5</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="10" t="n">
         <v>30.9</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="10" t="n">
         <v>100.2</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="10" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1229,10 +1229,10 @@
       <c r="P9" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="10" t="n">
         <v>149.6</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="9" t="n">
         <v>121.9</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1244,10 +1244,10 @@
       <c r="U9" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="9" t="n">
         <v>132.8</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="10" t="n">
         <v>116.8</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1299,10 +1299,10 @@
       <c r="K10" s="3" t="n">
         <v>11.1</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="10" t="n">
         <v>19.9</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1314,10 +1314,10 @@
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="8" t="n">
+      <c r="Q10" s="10" t="n">
         <v>29.9</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="9" t="n">
         <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1329,10 +1329,10 @@
       <c r="U10" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="10" t="n">
         <v>23.4</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1384,10 +1384,10 @@
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="10" t="n">
         <v>21.2</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="10" t="n">
         <v>20.9</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1417,7 +1417,7 @@
       <c r="V11" s="3" t="n">
         <v>27.1</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="11" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1469,10 +1469,10 @@
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="10" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="10" t="n">
         <v>23</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1554,10 +1554,10 @@
       <c r="K13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="10" t="n">
         <v>22.1</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="10" t="n">
         <v>21.9</v>
       </c>
       <c r="N13" s="3" t="n">
@@ -1639,10 +1639,10 @@
       <c r="K14" s="3" t="n">
         <v>11.1</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="10" t="n">
         <v>22.4</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="10" t="n">
         <v>22.1</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1654,7 +1654,7 @@
       <c r="P14" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="11" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="R14" s="3" t="n">
@@ -1722,10 +1722,10 @@
       <c r="K15" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="10" t="n">
         <v>21.6</v>
       </c>
       <c r="N15" s="3" t="n">
@@ -1804,13 +1804,13 @@
       <c r="J16" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="9" t="n">
         <v>36.8</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="10" t="n">
         <v>110.6</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="9" t="n">
         <v>109.8</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1822,10 +1822,10 @@
       <c r="P16" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="9" t="n">
         <v>148.7</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="9" t="n">
         <v>1221.9</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1837,10 +1837,10 @@
       <c r="U16" s="3" t="n">
         <v>76.59999999999999</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="9" t="n">
         <v>133.7</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="9" t="n">
         <v>120.7</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1892,10 +1892,10 @@
       <c r="K17" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="10" t="n">
         <v>22.1</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="10" t="n">
         <v>21.9</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1907,10 +1907,10 @@
       <c r="P17" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="9" t="n">
         <v>24.4</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1922,10 +1922,10 @@
       <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="9" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="9" t="n">
         <v>24.1</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1975,10 +1975,10 @@
       <c r="K18" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="10" t="n">
         <v>21.4</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="10" t="n">
         <v>21.1</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -1990,7 +1990,7 @@
       <c r="P18" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q18" s="3" t="n">
+      <c r="Q18" s="10" t="n">
         <v>32.1</v>
       </c>
       <c r="R18" s="3" t="n">
@@ -2005,7 +2005,7 @@
       <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="10" t="n">
         <v>28.5</v>
       </c>
       <c r="W18" s="3" t="n">
@@ -2060,10 +2060,10 @@
       <c r="K19" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="10" t="n">
         <v>22</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2075,7 +2075,7 @@
       <c r="P19" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="Q19" s="8" t="n">
+      <c r="Q19" s="10" t="n">
         <v>29.9</v>
       </c>
       <c r="R19" s="3" t="n">
@@ -2090,7 +2090,7 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="10" t="n">
         <v>24.3</v>
       </c>
       <c r="W19" s="8" t="n">
@@ -2145,10 +2145,10 @@
       <c r="K20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="N20" s="3" t="n">
@@ -2160,7 +2160,7 @@
       <c r="P20" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" s="10" t="n">
         <v>30.7</v>
       </c>
       <c r="R20" s="3" t="n">
@@ -2175,7 +2175,7 @@
       <c r="U20" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="10" t="n">
         <v>27.3</v>
       </c>
       <c r="W20" s="3" t="n">
@@ -2230,10 +2230,10 @@
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="10" t="n">
         <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2245,7 +2245,7 @@
       <c r="P21" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="3" t="n">
+      <c r="Q21" s="10" t="n">
         <v>30.6</v>
       </c>
       <c r="R21" s="3" t="n">
@@ -2260,7 +2260,7 @@
       <c r="U21" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="10" t="n">
         <v>27.8</v>
       </c>
       <c r="W21" s="8" t="n">
@@ -2315,10 +2315,10 @@
       <c r="K22" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="L22" s="10" t="n">
         <v>21.3</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="10" t="n">
         <v>21</v>
       </c>
       <c r="N22" s="3" t="n">
@@ -2330,7 +2330,7 @@
       <c r="P22" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" s="10" t="n">
         <v>32.4</v>
       </c>
       <c r="R22" s="3" t="n">
@@ -2345,7 +2345,7 @@
       <c r="U22" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="10" t="n">
         <v>26.5</v>
       </c>
       <c r="W22" s="3" t="n">
@@ -2397,13 +2397,13 @@
       <c r="J23" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="9" t="n">
         <v>49.1</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="10" t="n">
         <v>108.2</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="9" t="n">
         <v>1107</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2415,10 +2415,10 @@
       <c r="P23" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="10" t="n">
         <v>155.7</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="9" t="n">
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2430,10 +2430,10 @@
       <c r="U23" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="10" t="n">
         <v>134.4</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="9" t="n">
         <v>20.3</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2485,10 +2485,10 @@
       <c r="K24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2500,10 +2500,10 @@
       <c r="P24" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="10" t="n">
         <v>31.1</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="9" t="n">
         <v>85.59999999999999</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2515,10 +2515,10 @@
       <c r="U24" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="10" t="n">
         <v>26.9</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="9" t="n">
         <v>24.1</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2573,7 +2573,7 @@
       <c r="L25" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="M25" s="10" t="n">
         <v>22.1</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2585,10 +2585,10 @@
       <c r="P25" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="Q25" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="R25" s="3" t="n">
+      <c r="R25" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2603,7 +2603,7 @@
       <c r="V25" s="8" t="n">
         <v>14.4</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="W25" s="10" t="n">
         <v>22.8</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2656,7 +2656,7 @@
       <c r="L26" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2668,10 +2668,10 @@
       <c r="P26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="10" t="n">
         <v>24.3</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="10" t="n">
         <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2686,7 +2686,7 @@
       <c r="V26" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="W26" s="3" t="n">
+      <c r="W26" s="10" t="n">
         <v>22.8</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2738,10 +2738,10 @@
       <c r="K27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" s="11" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="10" t="n">
         <v>20.5</v>
       </c>
       <c r="N27" s="3" t="n">
@@ -2753,10 +2753,10 @@
       <c r="P27" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="10" t="n">
         <v>28.8</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="10" t="n">
         <v>24.9</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2768,10 +2768,10 @@
       <c r="U27" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="V27" s="8" t="n">
-        <v>826.9</v>
-      </c>
-      <c r="W27" s="3" t="n">
+      <c r="V27" s="11" t="n">
+        <v>82.69</v>
+      </c>
+      <c r="W27" s="10" t="n">
         <v>24.4</v>
       </c>
       <c r="X27" s="8" t="n">
@@ -2826,7 +2826,7 @@
       <c r="L28" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="M28" s="10" t="n">
         <v>20.6</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2838,10 +2838,10 @@
       <c r="P28" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="10" t="n">
         <v>31.2</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" s="10" t="n">
         <v>24.8</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2856,7 +2856,7 @@
       <c r="V28" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="W28" s="3" t="n">
+      <c r="W28" s="10" t="n">
         <v>24.6</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2911,7 +2911,7 @@
       <c r="L29" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="10" t="n">
         <v>20.6</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2923,10 +2923,10 @@
       <c r="P29" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="10" t="n">
         <v>25.3</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" s="10" t="n">
         <v>23.6</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2941,7 +2941,7 @@
       <c r="V29" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="W29" s="3" t="n">
+      <c r="W29" s="10" t="n">
         <v>21.3</v>
       </c>
       <c r="X29" s="8" t="n">
@@ -2990,13 +2990,13 @@
       <c r="J30" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="9" t="n">
         <v>328.8</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="9" t="n">
         <v>106.5</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="10" t="n">
         <v>105.2</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3008,10 +3008,10 @@
       <c r="P30" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="9" t="n">
         <v>1135.8</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="10" t="n">
         <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3021,10 +3021,10 @@
         <v>396.8</v>
       </c>
       <c r="U30" s="3" t="inlineStr"/>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="9" t="n">
         <v>126.1</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="10" t="n">
         <v>115.9</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3076,10 +3076,10 @@
       <c r="K31" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="L31" s="3" t="n">
+      <c r="L31" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="10" t="n">
         <v>21</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3091,10 +3091,10 @@
       <c r="P31" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3106,10 +3106,10 @@
       <c r="U31" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="10" t="n">
         <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3161,10 +3161,10 @@
       <c r="K32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="L32" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="M32" s="3" t="n">
+      <c r="M32" s="10" t="n">
         <v>20.1</v>
       </c>
       <c r="N32" s="3" t="n">
@@ -3176,7 +3176,7 @@
       <c r="P32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" s="3" t="n">
+      <c r="Q32" s="10" t="n">
         <v>31.1</v>
       </c>
       <c r="R32" s="3" t="n">
@@ -3194,7 +3194,7 @@
       <c r="V32" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="11" t="n">
         <v>83.8</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3246,10 +3246,10 @@
       <c r="K33" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="10" t="n">
         <v>21.5</v>
       </c>
-      <c r="M33" s="3" t="n">
+      <c r="M33" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -3261,7 +3261,7 @@
       <c r="P33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="10" t="n">
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
@@ -3331,10 +3331,10 @@
       <c r="K34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="10" t="n">
         <v>21.8</v>
       </c>
-      <c r="M34" s="3" t="n">
+      <c r="M34" s="10" t="n">
         <v>21.7</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3346,7 +3346,7 @@
       <c r="P34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="10" t="n">
         <v>30.5</v>
       </c>
       <c r="R34" s="3" t="n">
@@ -3416,10 +3416,10 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M35" s="3" t="n">
+      <c r="M35" s="10" t="n">
         <v>21.3</v>
       </c>
       <c r="N35" s="3" t="n">
@@ -3431,10 +3431,10 @@
       <c r="P35" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q35" s="3" t="n">
+      <c r="Q35" s="10" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="8" t="n">
+      <c r="R35" s="11" t="n">
         <v>46.9</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3501,10 +3501,10 @@
       <c r="K36" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="M36" s="3" t="n">
+      <c r="M36" s="10" t="n">
         <v>20.7</v>
       </c>
       <c r="N36" s="3" t="n">
@@ -3516,7 +3516,7 @@
       <c r="P36" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="3" t="n">
+      <c r="Q36" s="10" t="n">
         <v>32.1</v>
       </c>
       <c r="R36" s="3" t="n">
@@ -3534,7 +3534,7 @@
       <c r="V36" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="8" t="n">
+      <c r="W36" s="11" t="n">
         <v>46.6</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3583,13 +3583,13 @@
       <c r="J37" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="9" t="n">
         <v>35.6</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="9" t="n">
         <v>1106</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="9" t="n">
         <v>103.2</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3601,10 +3601,10 @@
       <c r="P37" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="10" t="n">
         <v>153.7</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="9" t="n">
         <v>126.2</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3616,10 +3616,10 @@
       <c r="U37" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="9" t="n">
         <v>136.8</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="9" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3669,10 +3669,10 @@
         <v>3.6</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="10" t="n">
         <v>21.2</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="10" t="n">
         <v>21</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3684,10 +3684,10 @@
       <c r="P38" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="10" t="n">
         <v>30.7</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="9" t="n">
         <v>25.2</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3699,10 +3699,10 @@
       <c r="U38" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3769,10 +3769,10 @@
       <c r="P39" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="11" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="10" t="n">
         <v>26</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3787,7 +3787,7 @@
       <c r="V39" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="W39" s="3" t="n">
+      <c r="W39" s="10" t="n">
         <v>23.2</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3857,7 +3857,7 @@
       <c r="Q40" s="3" t="n">
         <v>32.8</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="10" t="n">
         <v>26</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3872,7 +3872,7 @@
       <c r="V40" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W40" s="3" t="n">
+      <c r="W40" s="10" t="n">
         <v>23.8</v>
       </c>
       <c r="X40" s="8" t="n">
@@ -3942,7 +3942,7 @@
       <c r="Q41" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="S41" s="8" t="n">
@@ -3957,7 +3957,7 @@
       <c r="V41" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="W41" s="3" t="n">
+      <c r="W41" s="10" t="n">
         <v>23.4</v>
       </c>
       <c r="X41" s="3" t="n">
@@ -4027,7 +4027,7 @@
       <c r="Q42" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="10" t="n">
         <v>23.8</v>
       </c>
       <c r="S42" s="3" t="n">
@@ -4042,7 +4042,7 @@
       <c r="V42" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="10" t="n">
         <v>22.5</v>
       </c>
       <c r="X42" s="8" t="n">
@@ -4112,7 +4112,7 @@
       <c r="Q43" s="3" t="n">
         <v>29.1</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="10" t="n">
         <v>25.5</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4127,7 +4127,7 @@
       <c r="V43" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="W43" s="3" t="n">
+      <c r="W43" s="10" t="n">
         <v>24.7</v>
       </c>
       <c r="X43" s="3" t="n">
@@ -4179,10 +4179,10 @@
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="8" t="n">
+      <c r="L44" s="11" t="n">
         <v>82.3</v>
       </c>
-      <c r="M44" s="3" t="n">
+      <c r="M44" s="11" t="n">
         <v>82.3</v>
       </c>
       <c r="N44" s="3" t="n">
@@ -4197,7 +4197,7 @@
       <c r="Q44" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R44" s="3" t="n">
+      <c r="R44" s="10" t="n">
         <v>26.4</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4212,7 +4212,7 @@
       <c r="V44" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="W44" s="3" t="n">
+      <c r="W44" s="10" t="n">
         <v>26.3</v>
       </c>
       <c r="X44" s="8" t="n">
@@ -4261,13 +4261,13 @@
       <c r="J45" s="3" t="n">
         <v>118.4</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="9" t="n">
         <v>783.6</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="9" t="n">
         <v>1166.5</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="9" t="n">
         <v>123.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4279,10 +4279,10 @@
       <c r="P45" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="9" t="n">
         <v>172.8</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="10" t="n">
         <v>149.1</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4294,10 +4294,10 @@
       <c r="U45" s="3" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="9" t="n">
         <v>158.1</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="9" t="n">
         <v>128.2</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4347,10 +4347,10 @@
         <v>3.1</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="9" t="n">
         <v>20</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4362,10 +4362,10 @@
       <c r="P46" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="9" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="9" t="n">
         <v>21.8</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4377,10 +4377,10 @@
       <c r="U46" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="9" t="n">
         <v>26.3</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -41,6 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -49,12 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
   </fills>
@@ -763,36 +763,36 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>186.2</v>
-      </c>
-      <c r="D4" s="10" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="E4" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E4" s="11" t="n">
         <v>20</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>18.2</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>88.2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>11.8</v>
+        <v>1.7</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="10" t="n">
+      <c r="K4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" s="11" t="n">
         <v>20.2</v>
       </c>
-      <c r="M4" s="10" t="n">
+      <c r="M4" s="11" t="n">
         <v>20.1</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -804,7 +804,7 @@
       <c r="P4" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q4" s="10" t="n">
+      <c r="Q4" s="11" t="n">
         <v>28.7</v>
       </c>
       <c r="R4" s="3" t="n">
@@ -819,13 +819,13 @@
       <c r="U4" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="V4" s="10" t="n">
+      <c r="V4" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="W4" s="10" t="n">
+      <c r="W4" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="X4" s="3" t="n">
+      <c r="X4" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
@@ -848,12 +848,12 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>403.8</v>
-      </c>
-      <c r="D5" s="10" t="n">
+        <v>240.3</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="11" t="n">
         <v>18.2</v>
       </c>
       <c r="F5" s="3" t="n">
@@ -862,8 +862,8 @@
       <c r="G5" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>16.8</v>
+      <c r="H5" s="8" t="n">
+        <v>416.8</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>3.5</v>
@@ -871,13 +871,13 @@
       <c r="J5" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K5" s="10" t="n">
+      <c r="K5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="10" t="n">
+      <c r="L5" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="M5" s="10" t="n">
+      <c r="M5" s="11" t="n">
         <v>18.8</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -889,7 +889,7 @@
       <c r="P5" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q5" s="10" t="n">
+      <c r="Q5" s="11" t="n">
         <v>32.6</v>
       </c>
       <c r="R5" s="3" t="n">
@@ -904,17 +904,17 @@
       <c r="U5" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="V5" s="10" t="n">
+      <c r="V5" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="W5" s="10" t="n">
+      <c r="W5" s="11" t="n">
         <v>24</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>7174</v>
+        <v>77</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>8.199999999999999</v>
@@ -935,11 +935,11 @@
       <c r="C6" s="3" t="n">
         <v>422.3</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="3" t="n">
         <v>34.2</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>28.8</v>
+      <c r="E6" s="11" t="n">
+        <v>18.8</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>26.5</v>
@@ -947,22 +947,22 @@
       <c r="G6" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="H6" s="8" t="n">
-        <v>15.2</v>
+      <c r="H6" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="K6" s="10" t="n">
+      <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="10" t="n">
+      <c r="L6" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="M6" s="10" t="n">
+      <c r="M6" s="11" t="n">
         <v>20</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -974,7 +974,7 @@
       <c r="P6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="10" t="n">
+      <c r="Q6" s="11" t="n">
         <v>32.7</v>
       </c>
       <c r="R6" s="3" t="n">
@@ -984,15 +984,15 @@
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>92.8</v>
+        <v>155.8</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="V6" s="10" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="W6" s="10" t="n">
+      <c r="V6" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="W6" s="11" t="n">
         <v>23.7</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1020,14 +1020,14 @@
       <c r="C7" s="3" t="n">
         <v>472.5</v>
       </c>
-      <c r="D7" s="10" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E7" s="3" t="n">
+      <c r="D7" s="9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E7" s="11" t="n">
         <v>19.3</v>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>72</v>
+      <c r="F7" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>15.4</v>
@@ -1036,52 +1036,52 @@
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>84.7</v>
+        <v>64.7</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>7.9</v>
       </c>
-      <c r="K7" s="10" t="n">
+      <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="10" t="n">
+      <c r="L7" s="11" t="n">
         <v>20.1</v>
       </c>
-      <c r="M7" s="10" t="n">
+      <c r="M7" s="11" t="n">
         <v>20.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>23.5</v>
+        <v>2.3</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>100</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="11" t="n">
         <v>34.2</v>
       </c>
-      <c r="R7" s="11" t="n">
-        <v>2.2</v>
+      <c r="R7" s="9" t="n">
+        <v>2.5</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>20.6</v>
+        <v>50.6</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="V7" s="10" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="W7" s="10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V7" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W7" s="11" t="n">
         <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>27.3</v>
+        <v>2.7</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>66.2</v>
@@ -1105,10 +1105,10 @@
       <c r="C8" s="3" t="n">
         <v>299</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="3" t="n">
         <v>34.6</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="11" t="n">
         <v>20.6</v>
       </c>
       <c r="F8" s="3" t="n">
@@ -1118,33 +1118,33 @@
         <v>14</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="L8" s="10" t="n">
+      <c r="L8" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="M8" s="10" t="n">
+      <c r="M8" s="11" t="n">
         <v>20.6</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>24</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>296.5</v>
+        <v>96.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q8" s="10" t="n">
+      <c r="Q8" s="11" t="n">
         <v>21.4</v>
       </c>
       <c r="R8" s="3" t="n">
@@ -1159,10 +1159,10 @@
       <c r="U8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="V8" s="10" t="n">
+      <c r="V8" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W8" s="10" t="n">
+      <c r="W8" s="11" t="n">
         <v>21.9</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1172,7 +1172,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>20.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1783.2</v>
-      </c>
-      <c r="D9" s="9" t="n">
+        <v>178.3</v>
+      </c>
+      <c r="D9" s="10" t="n">
         <v>164.8</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="11" t="n">
         <v>96.90000000000001</v>
       </c>
-      <c r="F9" s="9" t="n">
-        <v>230.8</v>
+      <c r="F9" s="10" t="n">
+        <v>130.8</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>67.90000000000001</v>
@@ -1206,55 +1206,55 @@
         <v>89.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="K9" s="10" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="L9" s="10" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="L9" s="11" t="n">
         <v>100.2</v>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="M9" s="11" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>112.8</v>
+        <v>118.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>494.2</v>
+        <v>494.5</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q9" s="10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q9" s="11" t="n">
         <v>149.6</v>
       </c>
-      <c r="R9" s="9" t="n">
+      <c r="R9" s="10" t="n">
         <v>121.9</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>135.7</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>329.9</v>
+        <v>2329.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="V9" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="V9" s="10" t="n">
         <v>132.8</v>
       </c>
-      <c r="W9" s="10" t="n">
+      <c r="W9" s="11" t="n">
         <v>116.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>133.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>3788.8</v>
+        <v>388.8</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>41.6</v>
@@ -1273,15 +1273,15 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>35.4</v>
+        <v>356.7</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="E10" s="9" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F10" s="9" t="n">
+      <c r="E10" s="11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F10" s="10" t="n">
         <v>26.2</v>
       </c>
       <c r="G10" s="3" t="n">
@@ -1296,13 +1296,11 @@
       <c r="J10" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L10" s="10" t="n">
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="11" t="n">
         <v>19.9</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1314,10 +1312,10 @@
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="10" t="n">
+      <c r="Q10" s="11" t="n">
         <v>29.9</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" s="10" t="n">
         <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1332,14 +1330,14 @@
       <c r="V10" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="W10" s="10" t="n">
+      <c r="W10" s="11" t="n">
         <v>23.4</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>72.8</v>
+        <v>77.8</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>8.300000000000001</v>
@@ -1360,13 +1358,13 @@
       <c r="C11" s="3" t="n">
         <v>265.6</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="11" t="n">
         <v>30.1</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="11" t="n">
         <v>24.9</v>
       </c>
       <c r="G11" s="3" t="n">
@@ -1376,34 +1374,34 @@
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.6</v>
+        <v>11.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="10" t="n">
+      <c r="L11" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M11" s="10" t="n">
+      <c r="M11" s="11" t="n">
         <v>20.9</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>21.3</v>
+        <v>97.3</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q11" s="3" t="n">
+      <c r="Q11" s="11" t="n">
         <v>29.9</v>
       </c>
-      <c r="R11" s="3" t="n">
-        <v>23.5</v>
+      <c r="R11" s="11" t="n">
+        <v>25.5</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>29.8</v>
@@ -1414,20 +1412,20 @@
       <c r="U11" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="V11" s="11" t="n">
         <v>27.1</v>
       </c>
-      <c r="W11" s="11" t="n">
-        <v>94.90000000000001</v>
+      <c r="W11" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>894</v>
+        <v>84</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>5.8</v>
+        <v>159.8</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1443,15 +1441,15 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>242.1</v>
+        <v>347.1</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>81.8</v>
+        <v>31.8</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="F12" s="10" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>27.2</v>
       </c>
       <c r="G12" s="3" t="n">
@@ -1464,43 +1462,43 @@
         <v>2.7</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="K12" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="10" t="n">
+      <c r="L12" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="10" t="n">
+      <c r="M12" s="11" t="n">
         <v>23</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>927.5</v>
+        <v>27.5</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="11" t="n">
         <v>31.8</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" s="11" t="n">
         <v>24.9</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>59.8</v>
+        <v>58.8</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="V12" s="3" t="n">
-        <v>21.9</v>
+      <c r="V12" s="11" t="n">
+        <v>27.9</v>
       </c>
       <c r="W12" s="3" t="n">
         <v>24.6</v>
@@ -1512,7 +1510,7 @@
         <v>76.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>81.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1530,13 +1528,13 @@
       <c r="C13" s="3" t="n">
         <v>428.6</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="11" t="n">
         <v>32.8</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F13" s="10" t="n">
+      <c r="E13" s="11" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F13" s="11" t="n">
         <v>26.6</v>
       </c>
       <c r="G13" s="3" t="n">
@@ -1549,15 +1547,15 @@
         <v>3.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="10" t="n">
+      <c r="L13" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="M13" s="10" t="n">
+      <c r="M13" s="11" t="n">
         <v>21.9</v>
       </c>
       <c r="N13" s="3" t="n">
@@ -1569,10 +1567,10 @@
       <c r="P13" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="11" t="n">
         <v>32.6</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="11" t="n">
         <v>24.6</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1584,11 +1582,11 @@
       <c r="U13" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="W13" s="3" t="n">
-        <v>24.8</v>
+      <c r="W13" s="9" t="n">
+        <v>2.4</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>29.3</v>
@@ -1597,7 +1595,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>18.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1615,13 +1613,13 @@
       <c r="C14" s="3" t="n">
         <v>190.3</v>
       </c>
-      <c r="D14" s="8" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="E14" s="3" t="n">
+      <c r="D14" s="11" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E14" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="11" t="n">
         <v>26.3</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1631,18 +1629,18 @@
         <v>20.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="K14" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K14" s="11" t="n">
         <v>11.1</v>
       </c>
-      <c r="L14" s="10" t="n">
+      <c r="L14" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="M14" s="10" t="n">
+      <c r="M14" s="11" t="n">
         <v>22.1</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1655,13 +1653,13 @@
         <v>0.7</v>
       </c>
       <c r="Q14" s="11" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="R14" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R14" s="11" t="n">
         <v>21.1</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>24.2</v>
+        <v>202.1</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>89</v>
@@ -1669,7 +1667,7 @@
       <c r="U14" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" s="11" t="n">
         <v>22</v>
       </c>
       <c r="W14" s="3" t="n">
@@ -1681,7 +1679,9 @@
       <c r="Y14" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="Z14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1698,13 +1698,13 @@
       <c r="C15" s="3" t="n">
         <v>359.6</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="11" t="n">
         <v>32.5</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="11" t="n">
         <v>20.8</v>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="F15" s="11" t="n">
         <v>26.7</v>
       </c>
       <c r="G15" s="8" t="n">
@@ -1719,28 +1719,28 @@
       <c r="J15" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K15" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="L15" s="10" t="n">
+      <c r="K15" s="11" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="M15" s="11" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" s="10" t="n">
-        <v>21.6</v>
-      </c>
       <c r="N15" s="3" t="n">
-        <v>25.8</v>
+        <v>29.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>100.2</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="R15" s="3" t="n">
+      <c r="R15" s="11" t="n">
         <v>25.8</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1752,7 +1752,7 @@
       <c r="U15" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="11" t="n">
         <v>28.7</v>
       </c>
       <c r="W15" s="3" t="n">
@@ -1781,19 +1781,19 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1221.2</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>167.9</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>1255.1</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>131.9</v>
+        <v>1591.2</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>131.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>52.4</v>
+        <v>352.4</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>99.2</v>
@@ -1804,29 +1804,29 @@
       <c r="J16" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="K16" s="9" t="n">
+      <c r="K16" s="11" t="n">
         <v>36.8</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>110.6</v>
-      </c>
-      <c r="M16" s="9" t="n">
-        <v>109.8</v>
+        <v>1110.6</v>
+      </c>
+      <c r="M16" s="11" t="n">
+        <v>109.5</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1230.7</v>
+        <v>130.7</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1490.1</v>
+        <v>2490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" s="11" t="n">
         <v>148.7</v>
       </c>
-      <c r="R16" s="9" t="n">
-        <v>1221.9</v>
+      <c r="R16" s="11" t="n">
+        <v>121.9</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>1136.1</v>
@@ -1837,17 +1837,17 @@
       <c r="U16" s="3" t="n">
         <v>76.59999999999999</v>
       </c>
-      <c r="V16" s="9" t="n">
+      <c r="V16" s="11" t="n">
         <v>133.7</v>
       </c>
-      <c r="W16" s="9" t="n">
-        <v>120.7</v>
+      <c r="W16" s="10" t="n">
+        <v>2120.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>142.5</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1407.6</v>
+        <v>407.4</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>34.4</v>
@@ -1868,13 +1868,13 @@
       <c r="C17" s="3" t="n">
         <v>318.2</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" s="11" t="n">
         <v>31.6</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="11" t="n">
         <v>21.1</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="11" t="n">
         <v>26.3</v>
       </c>
       <c r="G17" s="3" t="n">
@@ -1889,43 +1889,43 @@
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" s="8" t="n">
-        <v>6</v>
+      <c r="K17" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="L17" s="10" t="n">
         <v>22.1</v>
       </c>
-      <c r="M17" s="10" t="n">
+      <c r="M17" s="11" t="n">
         <v>21.9</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>928</v>
+        <v>298</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q17" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q17" s="11" t="n">
         <v>29.7</v>
       </c>
-      <c r="R17" s="9" t="n">
+      <c r="R17" s="11" t="n">
         <v>24.4</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>166.4</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="V17" s="9" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W17" s="9" t="n">
+      <c r="V17" s="11" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="W17" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1935,7 +1935,7 @@
         <v>81.5</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1953,69 +1953,71 @@
       <c r="C18" s="3" t="n">
         <v>368</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="11" t="n">
         <v>32.1</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
+      <c r="F18" s="11" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>10.9</v>
+      </c>
       <c r="H18" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>20.4</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="L18" s="10" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="M18" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="M18" s="11" t="n">
         <v>21.1</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>97.3</v>
+        <v>197.3</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q18" s="10" t="n">
+      <c r="Q18" s="11" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="11" t="n">
         <v>25.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="V18" s="10" t="n">
+      <c r="V18" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="W18" s="3" t="n">
+      <c r="W18" s="11" t="n">
         <v>24.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>21.9</v>
+        <v>27.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>171.7</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>11</v>
@@ -2036,20 +2038,20 @@
       <c r="C19" s="3" t="n">
         <v>265.6</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="11" t="n">
         <v>30.4</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="11" t="n">
         <v>22.2</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="11" t="n">
         <v>26.3</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H19" s="8" t="n">
-        <v>91.40000000000001</v>
+      <c r="H19" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.6</v>
@@ -2060,10 +2062,10 @@
       <c r="K19" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="L19" s="10" t="n">
+      <c r="L19" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="M19" s="10" t="n">
+      <c r="M19" s="11" t="n">
         <v>22</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2073,12 +2075,12 @@
         <v>97.59999999999999</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q19" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q19" s="11" t="n">
         <v>29.9</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="11" t="n">
         <v>26</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2090,11 +2092,11 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="10" t="n">
+      <c r="V19" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="W19" s="8" t="n">
-        <v>28.9</v>
+      <c r="W19" s="11" t="n">
+        <v>22.9</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>27.1</v>
@@ -2103,7 +2105,7 @@
         <v>89</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2121,17 +2123,17 @@
       <c r="C20" s="3" t="n">
         <v>365.9</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="11" t="n">
         <v>31.4</v>
       </c>
-      <c r="E20" s="8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>28.5</v>
+      <c r="E20" s="11" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>26.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>19.9</v>
+        <v>29.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>20.6</v>
@@ -2140,55 +2142,55 @@
         <v>2.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="10" t="n">
+      <c r="L20" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M20" s="10" t="n">
+      <c r="M20" s="11" t="n">
         <v>21.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>25.4</v>
+        <v>25.1</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q20" s="10" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q20" s="11" t="n">
         <v>30.7</v>
       </c>
-      <c r="R20" s="3" t="n">
+      <c r="R20" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="S20" s="8" t="n">
-        <v>17.5</v>
+      <c r="S20" s="3" t="n">
+        <v>27.5</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>12.3</v>
+        <v>62.3</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="V20" s="10" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>22.8</v>
+      <c r="V20" s="9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W20" s="11" t="n">
+        <v>23.8</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>725</v>
+        <v>85</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>9.1</v>
+        <v>19.1</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2206,13 +2208,13 @@
       <c r="C21" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D21" s="8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="E21" s="3" t="n">
+      <c r="D21" s="11" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E21" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" s="11" t="n">
         <v>25.9</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2230,10 +2232,10 @@
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="10" t="n">
+      <c r="L21" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M21" s="10" t="n">
+      <c r="M21" s="11" t="n">
         <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2245,10 +2247,10 @@
       <c r="P21" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="10" t="n">
+      <c r="Q21" s="11" t="n">
         <v>30.6</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="11" t="n">
         <v>26.2</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2260,11 +2262,11 @@
       <c r="U21" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V21" s="10" t="n">
+      <c r="V21" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W21" s="8" t="n">
-        <v>26.6</v>
+      <c r="W21" s="11" t="n">
+        <v>24.6</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>28.9</v>
@@ -2289,19 +2291,19 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>399.3</v>
-      </c>
-      <c r="D22" s="3" t="n">
+        <v>2399.3</v>
+      </c>
+      <c r="D22" s="11" t="n">
         <v>32.9</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="11" t="n">
         <v>21.1</v>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="F22" s="11" t="n">
         <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>11.8</v>
+        <v>1.1</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>19.8</v>
@@ -2313,28 +2315,28 @@
         <v>4.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L22" s="10" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="L22" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="M22" s="10" t="n">
+      <c r="M22" s="11" t="n">
         <v>21</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>97.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q22" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q22" s="11" t="n">
         <v>32.4</v>
       </c>
-      <c r="R22" s="3" t="n">
-        <v>29.9</v>
+      <c r="R22" s="11" t="n">
+        <v>25.9</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>89.3</v>
@@ -2345,10 +2347,10 @@
       <c r="U22" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="V22" s="10" t="n">
+      <c r="V22" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="11" t="n">
         <v>24.6</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2358,7 +2360,7 @@
         <v>86</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>144.9</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2376,17 +2378,17 @@
       <c r="C23" s="3" t="n">
         <v>1739.6</v>
       </c>
-      <c r="D23" s="9" t="n">
-        <v>167.5</v>
-      </c>
-      <c r="E23" s="9" t="n">
+      <c r="D23" s="11" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="E23" s="11" t="n">
         <v>107.2</v>
       </c>
-      <c r="F23" s="9" t="n">
-        <v>138.8</v>
+      <c r="F23" s="11" t="n">
+        <v>132.4</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>20.3</v>
+        <v>50.3</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>101.8</v>
@@ -2395,16 +2397,16 @@
         <v>10.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>49.1</v>
+        <v>19.3</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>19.3</v>
       </c>
       <c r="L23" s="10" t="n">
         <v>108.2</v>
       </c>
-      <c r="M23" s="9" t="n">
-        <v>1107</v>
+      <c r="M23" s="10" t="n">
+        <v>10.7</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>126.8</v>
@@ -2415,26 +2417,26 @@
       <c r="P23" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q23" s="10" t="n">
+      <c r="Q23" s="11" t="n">
         <v>155.7</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="11" t="n">
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>146.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>325.1</v>
+        <v>325.7</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>79.40000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="V23" s="10" t="n">
         <v>134.4</v>
       </c>
-      <c r="W23" s="9" t="n">
-        <v>20.3</v>
+      <c r="W23" s="10" t="n">
+        <v>1120.3</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>140.8</v>
@@ -2443,7 +2445,7 @@
         <v>399</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>362.5</v>
+        <v>36.7</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2459,16 +2461,16 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>343.2</v>
-      </c>
-      <c r="D24" s="9" t="n">
+        <v>347.9</v>
+      </c>
+      <c r="D24" s="11" t="n">
         <v>31.5</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="11" t="n">
         <v>21.4</v>
       </c>
-      <c r="F24" s="9" t="n">
-        <v>26.3</v>
+      <c r="F24" s="11" t="n">
+        <v>26.5</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>10.1</v>
@@ -2482,13 +2484,11 @@
       <c r="J24" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M24" s="10" t="n">
+      <c r="M24" s="11" t="n">
         <v>21.4</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2500,14 +2500,14 @@
       <c r="P24" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="Q24" s="10" t="n">
+      <c r="Q24" s="11" t="n">
         <v>31.1</v>
       </c>
-      <c r="R24" s="9" t="n">
-        <v>85.59999999999999</v>
+      <c r="R24" s="11" t="n">
+        <v>25.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>29.4</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>65.09999999999999</v>
@@ -2518,17 +2518,17 @@
       <c r="V24" s="10" t="n">
         <v>26.9</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="11" t="n">
         <v>24.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>2981.3</v>
+        <v>79.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>7.3</v>
+        <v>17.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2546,13 +2546,13 @@
       <c r="C25" s="3" t="n">
         <v>106.7</v>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D25" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="F25" s="10" t="n">
+      <c r="F25" s="11" t="n">
         <v>23.5</v>
       </c>
       <c r="G25" s="3" t="n">
@@ -2567,14 +2567,14 @@
       <c r="J25" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="11" t="n">
         <v>23.7</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="11" t="n">
         <v>22.4</v>
       </c>
-      <c r="M25" s="10" t="n">
-        <v>22.1</v>
+      <c r="M25" s="9" t="n">
+        <v>98.09999999999999</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>26.4</v>
@@ -2585,10 +2585,10 @@
       <c r="P25" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q25" s="10" t="n">
+      <c r="Q25" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="R25" s="10" t="n">
+      <c r="R25" s="11" t="n">
         <v>24.1</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2598,21 +2598,23 @@
         <v>84.40000000000001</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W25" s="10" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="V25" s="11" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="W25" s="11" t="n">
         <v>22.8</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>8781.700000000001</v>
-      </c>
-      <c r="Z25" s="3" t="inlineStr"/>
+        <v>87.7</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2629,13 +2631,13 @@
       <c r="C26" s="3" t="n">
         <v>290</v>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D26" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="E26" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="F26" s="10" t="n">
+      <c r="E26" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" s="11" t="n">
         <v>23.1</v>
       </c>
       <c r="G26" s="3" t="n">
@@ -2650,13 +2652,13 @@
       <c r="J26" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="L26" s="3" t="n">
+      <c r="K26" s="11" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="L26" s="11" t="n">
         <v>21.4</v>
       </c>
-      <c r="M26" s="10" t="n">
+      <c r="M26" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2668,25 +2670,25 @@
       <c r="P26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" s="10" t="n">
+      <c r="Q26" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="R26" s="10" t="n">
+      <c r="R26" s="11" t="n">
         <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>28</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>192</v>
+        <v>92</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V26" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V26" s="11" t="n">
         <v>23.8</v>
       </c>
-      <c r="W26" s="10" t="n">
+      <c r="W26" s="11" t="n">
         <v>22.8</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2696,7 +2698,7 @@
         <v>91.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>2.4</v>
+        <v>12.4</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2714,17 +2716,17 @@
       <c r="C27" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D27" s="10" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E27" s="3" t="n">
+      <c r="D27" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E27" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" s="11" t="n">
         <v>25.5</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>19.9</v>
+        <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>19.1</v>
@@ -2735,53 +2737,53 @@
       <c r="J27" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="11" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="M27" s="10" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="M27" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>98</v>
+        <v>298</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q27" s="10" t="n">
+      <c r="Q27" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R27" s="10" t="n">
+      <c r="R27" s="11" t="n">
         <v>24.9</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>29</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>23.2</v>
+        <v>73.2</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="V27" s="11" t="n">
-        <v>82.69</v>
-      </c>
-      <c r="W27" s="10" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="W27" s="11" t="n">
         <v>24.4</v>
       </c>
-      <c r="X27" s="8" t="n">
-        <v>89</v>
+      <c r="X27" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>81.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>6.4</v>
+        <v>16.4</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2799,13 +2801,13 @@
       <c r="C28" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D28" s="10" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E28" s="3" t="n">
+      <c r="D28" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E28" s="11" t="n">
         <v>20.5</v>
       </c>
-      <c r="F28" s="10" t="n">
+      <c r="F28" s="11" t="n">
         <v>26.1</v>
       </c>
       <c r="G28" s="8" t="n">
@@ -2820,32 +2822,32 @@
       <c r="J28" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="11" t="n">
         <v>20.9</v>
       </c>
-      <c r="M28" s="10" t="n">
+      <c r="M28" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q28" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q28" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="R28" s="10" t="n">
+      <c r="R28" s="11" t="n">
         <v>24.8</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>27.2</v>
+        <v>2.7</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>60.2</v>
@@ -2853,10 +2855,10 @@
       <c r="U28" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="V28" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="W28" s="10" t="n">
+      <c r="W28" s="11" t="n">
         <v>24.6</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2884,20 +2886,20 @@
       <c r="C29" s="3" t="n">
         <v>246.8</v>
       </c>
-      <c r="D29" s="10" t="n">
+      <c r="D29" s="3" t="n">
         <v>31.5</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="F29" s="10" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F29" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="G29" s="8" t="n">
+      <c r="G29" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="H29" s="3" t="n">
-        <v>19.2</v>
+      <c r="H29" s="8" t="n">
+        <v>69.2</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1.6</v>
@@ -2905,50 +2907,50 @@
       <c r="J29" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="11" t="n">
         <v>8.4</v>
       </c>
-      <c r="L29" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="M29" s="10" t="n">
+      <c r="L29" s="11" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="M29" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>95.3</v>
+        <v>2.5</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="Q29" s="10" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="R29" s="10" t="n">
+      <c r="Q29" s="9" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="R29" s="11" t="n">
         <v>23.6</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>827</v>
+        <v>27</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="V29" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V29" s="11" t="n">
         <v>22.4</v>
       </c>
-      <c r="W29" s="10" t="n">
+      <c r="W29" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="X29" s="8" t="n">
-        <v>14.6</v>
+      <c r="X29" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>90.8</v>
+        <v>912.1</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>2.5</v>
@@ -2967,15 +2969,15 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>11056.2</v>
+        <v>1056.2</v>
       </c>
       <c r="D30" s="10" t="n">
         <v>145.2</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="10" t="n">
         <v>103.2</v>
       </c>
-      <c r="F30" s="10" t="n">
+      <c r="F30" s="11" t="n">
         <v>124.2</v>
       </c>
       <c r="G30" s="3" t="n">
@@ -2988,12 +2990,12 @@
         <v>7.1</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="K30" s="9" t="n">
-        <v>328.8</v>
-      </c>
-      <c r="L30" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="K30" s="11" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="L30" s="10" t="n">
         <v>106.5</v>
       </c>
       <c r="M30" s="10" t="n">
@@ -3003,38 +3005,40 @@
         <v>123.9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>487.6</v>
+        <v>2487.6</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q30" s="9" t="n">
+      <c r="Q30" s="10" t="n">
         <v>1135.8</v>
       </c>
-      <c r="R30" s="10" t="n">
+      <c r="R30" s="11" t="n">
         <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>1240.9</v>
+        <v>140.9</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>396.8</v>
       </c>
-      <c r="U30" s="3" t="inlineStr"/>
-      <c r="V30" s="9" t="n">
-        <v>126.1</v>
-      </c>
-      <c r="W30" s="10" t="n">
+      <c r="U30" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="V30" s="10" t="n">
+        <v>1126.1</v>
+      </c>
+      <c r="W30" s="11" t="n">
         <v>115.9</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>1424.7</v>
+        <v>1428.7</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>85.8</v>
+        <v>25.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3052,13 +3056,13 @@
       <c r="C31" s="3" t="n">
         <v>211.2</v>
       </c>
-      <c r="D31" s="9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="F31" s="10" t="n">
+      <c r="D31" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F31" s="11" t="n">
         <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
@@ -3073,10 +3077,8 @@
       <c r="J31" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L31" s="9" t="n">
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="11" t="n">
         <v>21.3</v>
       </c>
       <c r="M31" s="10" t="n">
@@ -3086,7 +3088,7 @@
         <v>24.8</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>927.5</v>
+        <v>97.5</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>0.6</v>
@@ -3094,7 +3096,7 @@
       <c r="Q31" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="R31" s="11" t="n">
         <v>24.1</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3104,19 +3106,19 @@
         <v>79.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="V31" s="9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="V31" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="W31" s="10" t="n">
+      <c r="W31" s="11" t="n">
         <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>24.9</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>5.2</v>
@@ -3137,14 +3139,14 @@
       <c r="C32" s="3" t="n">
         <v>384.7</v>
       </c>
-      <c r="D32" s="10" t="n">
+      <c r="D32" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="E32" s="3" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>23.2</v>
+      <c r="E32" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>25.2</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>11.8</v>
@@ -3158,17 +3160,17 @@
       <c r="J32" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="10" t="n">
+      <c r="L32" s="11" t="n">
         <v>20.1</v>
       </c>
-      <c r="M32" s="10" t="n">
+      <c r="M32" s="11" t="n">
         <v>20.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>23.5</v>
+        <v>23.9</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>100</v>
@@ -3176,7 +3178,7 @@
       <c r="P32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" s="10" t="n">
+      <c r="Q32" s="11" t="n">
         <v>31.1</v>
       </c>
       <c r="R32" s="3" t="n">
@@ -3191,20 +3193,20 @@
       <c r="U32" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="V32" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W32" s="11" t="n">
-        <v>83.8</v>
+      <c r="V32" s="11" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>7641.6</v>
+        <v>746.6</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>19.3</v>
+        <v>195.3</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3222,13 +3224,13 @@
       <c r="C33" s="3" t="n">
         <v>213.3</v>
       </c>
-      <c r="D33" s="10" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E33" s="3" t="n">
+      <c r="D33" s="9" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="E33" s="11" t="n">
         <v>19.6</v>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="F33" s="11" t="n">
         <v>24.4</v>
       </c>
       <c r="G33" s="3" t="n">
@@ -3238,22 +3240,22 @@
         <v>18.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="K33" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="L33" s="10" t="n">
+      <c r="K33" s="11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L33" s="11" t="n">
         <v>21.5</v>
       </c>
-      <c r="M33" s="10" t="n">
+      <c r="M33" s="11" t="n">
         <v>21.4</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>23.9</v>
+        <v>25.4</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>99</v>
@@ -3261,11 +3263,11 @@
       <c r="P33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="10" t="n">
+      <c r="Q33" s="11" t="n">
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>28.6</v>
+        <v>21.6</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.2</v>
@@ -3276,7 +3278,7 @@
       <c r="U33" s="3" t="n">
         <v>11.5</v>
       </c>
-      <c r="V33" s="3" t="n">
+      <c r="V33" s="11" t="n">
         <v>25.6</v>
       </c>
       <c r="W33" s="3" t="n">
@@ -3286,10 +3288,10 @@
         <v>28.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>26.1</v>
+        <v>0.1</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>144.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3307,13 +3309,13 @@
       <c r="C34" s="3" t="n">
         <v>311.6</v>
       </c>
-      <c r="D34" s="10" t="n">
+      <c r="D34" s="3" t="n">
         <v>31.9</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="11" t="n">
         <v>21.4</v>
       </c>
-      <c r="F34" s="3" t="n">
+      <c r="F34" s="11" t="n">
         <v>26.7</v>
       </c>
       <c r="G34" s="3" t="n">
@@ -3326,31 +3328,31 @@
         <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="K34" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K34" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="L34" s="10" t="n">
+      <c r="L34" s="11" t="n">
         <v>21.8</v>
       </c>
-      <c r="M34" s="10" t="n">
+      <c r="M34" s="11" t="n">
         <v>21.7</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="10" t="n">
+      <c r="Q34" s="11" t="n">
         <v>30.5</v>
       </c>
-      <c r="R34" s="3" t="n">
-        <v>25.8</v>
+      <c r="R34" s="8" t="n">
+        <v>35.8</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>30.2</v>
@@ -3361,7 +3363,7 @@
       <c r="U34" s="3" t="n">
         <v>13.3</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="V34" s="11" t="n">
         <v>27.3</v>
       </c>
       <c r="W34" s="3" t="n">
@@ -3371,7 +3373,7 @@
         <v>29.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>82.8</v>
+        <v>82</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>16.5</v>
@@ -3390,15 +3392,15 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>353.4</v>
-      </c>
-      <c r="D35" s="10" t="n">
+        <v>353.1</v>
+      </c>
+      <c r="D35" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E35" s="3" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="F35" s="3" t="n">
+      <c r="E35" s="11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F35" s="11" t="n">
         <v>25.9</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3413,32 +3415,32 @@
       <c r="J35" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="10" t="n">
+      <c r="L35" s="11" t="n">
         <v>21.6</v>
       </c>
-      <c r="M35" s="10" t="n">
+      <c r="M35" s="11" t="n">
         <v>21.3</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>97.2</v>
+        <v>297.2</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q35" s="10" t="n">
+      <c r="Q35" s="11" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="11" t="n">
+      <c r="R35" s="9" t="n">
         <v>46.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>21.8</v>
+        <v>27.8</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>61.3</v>
@@ -3446,7 +3448,7 @@
       <c r="U35" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V35" s="11" t="n">
         <v>27.8</v>
       </c>
       <c r="W35" s="8" t="n">
@@ -3456,7 +3458,7 @@
         <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>3.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8.4</v>
@@ -3477,16 +3479,16 @@
       <c r="C36" s="3" t="n">
         <v>430.7</v>
       </c>
-      <c r="D36" s="10" t="n">
+      <c r="D36" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="11" t="n">
         <v>20.9</v>
       </c>
-      <c r="F36" s="3" t="n">
+      <c r="F36" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="G36" s="8" t="n">
+      <c r="G36" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3498,25 +3500,25 @@
       <c r="J36" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="11" t="n">
         <v>30.6</v>
       </c>
-      <c r="L36" s="10" t="n">
+      <c r="L36" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="M36" s="10" t="n">
+      <c r="M36" s="11" t="n">
         <v>20.7</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>97.5</v>
+        <v>925.1</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="10" t="n">
+      <c r="Q36" s="11" t="n">
         <v>32.1</v>
       </c>
       <c r="R36" s="3" t="n">
@@ -3531,20 +3533,20 @@
       <c r="U36" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="11" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="11" t="n">
-        <v>46.6</v>
+      <c r="W36" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>28.8</v>
+        <v>28.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>72</v>
+        <v>172</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1411</v>
+        <v>111</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3563,12 +3565,12 @@
         <v>1693.7</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>155.4</v>
-      </c>
-      <c r="E37" s="9" t="n">
+        <v>14155.4</v>
+      </c>
+      <c r="E37" s="11" t="n">
         <v>102</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="11" t="n">
         <v>128.7</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3583,14 +3585,14 @@
       <c r="J37" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="K37" s="9" t="n">
+      <c r="K37" s="11" t="n">
         <v>35.6</v>
       </c>
-      <c r="L37" s="9" t="n">
+      <c r="L37" s="10" t="n">
         <v>1106</v>
       </c>
-      <c r="M37" s="9" t="n">
-        <v>103.2</v>
+      <c r="M37" s="11" t="n">
+        <v>105.2</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>124.1</v>
@@ -3599,37 +3601,37 @@
         <v>492.7</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="Q37" s="10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q37" s="11" t="n">
         <v>153.7</v>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="R37" s="10" t="n">
         <v>126.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>143.1</v>
+        <v>1143.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>324.8</v>
+        <v>2324.8</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V37" s="9" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="V37" s="11" t="n">
         <v>136.8</v>
       </c>
-      <c r="W37" s="9" t="n">
+      <c r="W37" s="10" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>122.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>3928.2</v>
+        <v>392.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>39.7</v>
+        <v>139.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3648,12 +3650,12 @@
         <v>338.7</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>31</v>
-      </c>
-      <c r="E38" s="9" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E38" s="11" t="n">
         <v>20.4</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="11" t="n">
         <v>25.7</v>
       </c>
       <c r="G38" s="3" t="n">
@@ -3669,47 +3671,47 @@
         <v>3.6</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="10" t="n">
+      <c r="L38" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="M38" s="10" t="n">
+      <c r="M38" s="11" t="n">
         <v>21</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>98.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q38" s="10" t="n">
+      <c r="Q38" s="11" t="n">
         <v>30.7</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="10" t="n">
         <v>25.2</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="V38" s="9" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="W38" s="9" t="n">
+      <c r="V38" s="10" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="W38" s="10" t="n">
         <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>88.5</v>
+        <v>28.5</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>78</v>
+        <v>29.1</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>7.9</v>
@@ -3733,16 +3735,16 @@
       <c r="D39" s="3" t="n">
         <v>31.9</v>
       </c>
-      <c r="E39" s="10" t="n">
+      <c r="E39" s="11" t="n">
         <v>20.2</v>
       </c>
-      <c r="F39" s="10" t="n">
+      <c r="F39" s="11" t="n">
         <v>26.1</v>
       </c>
-      <c r="G39" s="8" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="H39" s="8" t="n">
+      <c r="G39" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3752,12 +3754,12 @@
         <v>3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L39" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L39" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="11" t="n">
         <v>20.9</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3770,9 +3772,9 @@
         <v>0.2</v>
       </c>
       <c r="Q39" s="11" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="R39" s="10" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="R39" s="11" t="n">
         <v>26</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3782,22 +3784,22 @@
         <v>163.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>11.3</v>
+        <v>18.3</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="W39" s="10" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="W39" s="11" t="n">
         <v>23.2</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>2.7</v>
+        <v>27.5</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>88.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>23.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3813,15 +3815,15 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>153.7</v>
+        <v>1453.7</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E40" s="10" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E40" s="11" t="n">
         <v>18.8</v>
       </c>
-      <c r="F40" s="10" t="n">
+      <c r="F40" s="11" t="n">
         <v>25.9</v>
       </c>
       <c r="G40" s="3" t="n">
@@ -3839,10 +3841,10 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="11" t="n">
         <v>19.6</v>
       </c>
       <c r="N40" s="3" t="n">
@@ -3854,10 +3856,10 @@
       <c r="P40" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="11" t="n">
         <v>32.8</v>
       </c>
-      <c r="R40" s="10" t="n">
+      <c r="R40" s="11" t="n">
         <v>26</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3872,17 +3874,17 @@
       <c r="V40" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W40" s="10" t="n">
+      <c r="W40" s="11" t="n">
         <v>23.8</v>
       </c>
-      <c r="X40" s="8" t="n">
-        <v>86.90000000000001</v>
+      <c r="X40" s="3" t="n">
+        <v>26.9</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>72</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>101.6</v>
+        <v>10.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3898,15 +3900,15 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>8985.6</v>
-      </c>
-      <c r="D41" s="3" t="n">
+        <v>265.6</v>
+      </c>
+      <c r="D41" s="8" t="n">
         <v>31.6</v>
       </c>
-      <c r="E41" s="10" t="n">
+      <c r="E41" s="11" t="n">
         <v>19.6</v>
       </c>
-      <c r="F41" s="10" t="n">
+      <c r="F41" s="11" t="n">
         <v>25.6</v>
       </c>
       <c r="G41" s="3" t="n">
@@ -3922,12 +3924,12 @@
         <v>1.6</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L41" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L41" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="11" t="n">
         <v>19.8</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3939,14 +3941,14 @@
       <c r="P41" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="11" t="n">
         <v>22.3</v>
       </c>
-      <c r="R41" s="10" t="n">
+      <c r="R41" s="11" t="n">
         <v>21.4</v>
       </c>
-      <c r="S41" s="8" t="n">
-        <v>16.9</v>
+      <c r="S41" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>92.3</v>
@@ -3954,20 +3956,20 @@
       <c r="U41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V41" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="W41" s="10" t="n">
+      <c r="V41" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W41" s="11" t="n">
         <v>23.4</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>190.5</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3983,15 +3985,15 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>836.3</v>
+        <v>236.3</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>31.6</v>
       </c>
-      <c r="E42" s="10" t="n">
+      <c r="E42" s="11" t="n">
         <v>20.3</v>
       </c>
-      <c r="F42" s="10" t="n">
+      <c r="F42" s="11" t="n">
         <v>25.9</v>
       </c>
       <c r="G42" s="3" t="n">
@@ -4003,16 +4005,16 @@
       <c r="I42" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="J42" s="8" t="n">
-        <v>8</v>
+      <c r="J42" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="L42" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="L42" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="M42" s="3" t="n">
+      <c r="M42" s="11" t="n">
         <v>21.8</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -4024,36 +4026,34 @@
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="Q42" s="11" t="n">
         <v>24.1</v>
       </c>
-      <c r="R42" s="10" t="n">
+      <c r="R42" s="11" t="n">
         <v>23.8</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>29.3</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>97.7</v>
+        <v>97.2</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="W42" s="10" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X42" s="8" t="n">
-        <v>828.2</v>
+        <v>24.7</v>
+      </c>
+      <c r="W42" s="11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="Z42" s="3" t="n">
-        <v>2.9</v>
-      </c>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4073,11 +4073,11 @@
       <c r="D43" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="E43" s="10" t="n">
+      <c r="E43" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="F43" s="10" t="n">
-        <v>24.7</v>
+      <c r="F43" s="11" t="n">
+        <v>25.7</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>8.699999999999999</v>
@@ -4094,10 +4094,10 @@
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="L43" s="11" t="n">
         <v>21.6</v>
       </c>
-      <c r="M43" s="3" t="n">
+      <c r="M43" s="11" t="n">
         <v>21.5</v>
       </c>
       <c r="N43" s="3" t="n">
@@ -4109,10 +4109,10 @@
       <c r="P43" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q43" s="3" t="n">
+      <c r="Q43" s="11" t="n">
         <v>29.1</v>
       </c>
-      <c r="R43" s="10" t="n">
+      <c r="R43" s="11" t="n">
         <v>25.5</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4125,13 +4125,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W43" s="10" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W43" s="11" t="n">
         <v>24.7</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>29.1</v>
+        <v>34.1</v>
       </c>
       <c r="Y43" s="3" t="n">
         <v>78</v>
@@ -4155,35 +4155,35 @@
       <c r="C44" s="3" t="n">
         <v>365.9</v>
       </c>
-      <c r="D44" s="11" t="n">
-        <v>22.61</v>
-      </c>
-      <c r="E44" s="10" t="n">
+      <c r="D44" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E44" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="F44" s="10" t="n">
+      <c r="F44" s="11" t="n">
         <v>26.9</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>19.4</v>
+        <v>49.4</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="11" t="n">
-        <v>82.3</v>
+        <v>22.3</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>82.3</v>
+        <v>22.3</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>26.9</v>
@@ -4194,10 +4194,10 @@
       <c r="P44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" s="3" t="n">
+      <c r="Q44" s="11" t="n">
         <v>32.6</v>
       </c>
-      <c r="R44" s="10" t="n">
+      <c r="R44" s="11" t="n">
         <v>26.4</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4210,16 +4210,16 @@
         <v>18.6</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="W44" s="10" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="W44" s="11" t="n">
         <v>26.3</v>
       </c>
-      <c r="X44" s="8" t="n">
-        <v>28.2</v>
+      <c r="X44" s="3" t="n">
+        <v>32.2</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>184.4</v>
       </c>
       <c r="Z44" s="3" t="n">
         <v>16</v>
@@ -4238,40 +4238,40 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2026.2</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>1901.6</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>11298.6</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>226.1</v>
+        <v>202.6</v>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>190.6</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>1121.5</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>156.3</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>2.1</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>1114.2</v>
+        <v>1114.7</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>11</v>
+        <v>101.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>118.4</v>
-      </c>
-      <c r="K45" s="9" t="n">
-        <v>783.6</v>
-      </c>
-      <c r="L45" s="9" t="n">
-        <v>1166.5</v>
-      </c>
-      <c r="M45" s="9" t="n">
-        <v>123.9</v>
+        <v>18.4</v>
+      </c>
+      <c r="K45" s="10" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="L45" s="10" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="M45" s="10" t="n">
+        <v>10122.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1148.8</v>
+        <v>1148.7</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>293.8</v>
@@ -4279,35 +4279,35 @@
       <c r="P45" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q45" s="9" t="n">
+      <c r="Q45" s="11" t="n">
         <v>172.8</v>
       </c>
-      <c r="R45" s="10" t="n">
+      <c r="R45" s="11" t="n">
         <v>149.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>121.1</v>
+        <v>174.1</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>1230</v>
+        <v>2430</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="V45" s="9" t="n">
+      <c r="V45" s="10" t="n">
         <v>158.1</v>
       </c>
-      <c r="W45" s="9" t="n">
-        <v>128.2</v>
+      <c r="W45" s="11" t="n">
+        <v>144.9</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>172.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>503.4</v>
+        <v>583.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4325,17 +4325,17 @@
       <c r="C46" s="3" t="n">
         <v>237.6</v>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="10" t="n">
         <v>31.7</v>
       </c>
-      <c r="E46" s="10" t="n">
+      <c r="E46" s="11" t="n">
         <v>20.2</v>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="F46" s="11" t="n">
         <v>26</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>21.5</v>
+        <v>11.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>19.1</v>
@@ -4346,51 +4346,53 @@
       <c r="J46" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="9" t="n">
+      <c r="K46" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L46" s="11" t="n">
         <v>21.1</v>
       </c>
-      <c r="M46" s="9" t="n">
-        <v>20</v>
+      <c r="M46" s="11" t="n">
+        <v>21</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="9" t="n">
+      <c r="Q46" s="11" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="9" t="n">
+      <c r="R46" s="10" t="n">
         <v>21.8</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>29</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>22.9</v>
+        <v>75</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V46" s="9" t="n">
+      <c r="V46" s="10" t="n">
         <v>26.3</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="11" t="n">
         <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>88.8</v>
+        <v>823.9</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -35,14 +35,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,8 +47,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -147,9 +141,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -763,22 +754,22 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="E4" s="11" t="n">
+        <v>186.2</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E4" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="H4" s="8" t="n">
-        <v>88.2</v>
+      <c r="H4" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>1.7</v>
@@ -786,13 +777,13 @@
       <c r="J4" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L4" s="11" t="n">
+      <c r="K4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="M4" s="11" t="n">
+      <c r="M4" s="8" t="n">
         <v>20.1</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -804,10 +795,10 @@
       <c r="P4" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q4" s="11" t="n">
+      <c r="Q4" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -819,13 +810,13 @@
       <c r="U4" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="W4" s="11" t="n">
+      <c r="W4" s="8" t="n">
         <v>22.8</v>
       </c>
-      <c r="X4" s="8" t="n">
+      <c r="X4" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
@@ -848,22 +839,22 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>240.3</v>
-      </c>
-      <c r="D5" s="3" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="D5" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="8" t="n">
         <v>25.4</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="H5" s="8" t="n">
-        <v>416.8</v>
+      <c r="H5" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>3.5</v>
@@ -871,13 +862,13 @@
       <c r="J5" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="11" t="n">
+      <c r="L5" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="M5" s="11" t="n">
+      <c r="M5" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -889,10 +880,10 @@
       <c r="P5" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q5" s="11" t="n">
+      <c r="Q5" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="8" t="n">
         <v>25.4</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -904,10 +895,10 @@
       <c r="U5" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="W5" s="11" t="n">
+      <c r="W5" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -933,15 +924,15 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>422.3</v>
-      </c>
-      <c r="D6" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D6" s="8" t="n">
         <v>34.2</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="8" t="n">
         <v>26.5</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -956,13 +947,13 @@
       <c r="J6" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="11" t="n">
+      <c r="L6" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="M6" s="8" t="n">
         <v>20</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -974,25 +965,25 @@
       <c r="P6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="11" t="n">
+      <c r="Q6" s="8" t="n">
         <v>32.7</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="8" t="n">
         <v>25.7</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>155.8</v>
+        <v>55.8</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W6" s="11" t="n">
+      <c r="W6" s="8" t="n">
         <v>23.7</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1020,14 +1011,14 @@
       <c r="C7" s="3" t="n">
         <v>472.5</v>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E7" s="11" t="n">
+      <c r="D7" s="8" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="E7" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>22</v>
+      <c r="F7" s="8" t="n">
+        <v>27</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>15.4</v>
@@ -1036,22 +1027,22 @@
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>64.7</v>
+        <v>4.7</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="K7" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="11" t="n">
+      <c r="L7" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="M7" s="8" t="n">
         <v>20.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>2.3</v>
+        <v>23.5</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>100</v>
@@ -1059,11 +1050,11 @@
       <c r="P7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="11" t="n">
+      <c r="Q7" s="8" t="n">
         <v>34.2</v>
       </c>
-      <c r="R7" s="9" t="n">
-        <v>2.5</v>
+      <c r="R7" s="8" t="n">
+        <v>25.5</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>27.1</v>
@@ -1072,16 +1063,16 @@
         <v>50.6</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V7" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="W7" s="11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="W7" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>2.7</v>
+        <v>27.3</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>66.2</v>
@@ -1105,19 +1096,19 @@
       <c r="C8" s="3" t="n">
         <v>299</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="8" t="n">
         <v>34.6</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="8" t="n">
         <v>27.6</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H8" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I8" s="3" t="n">
@@ -1129,10 +1120,10 @@
       <c r="K8" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="L8" s="11" t="n">
+      <c r="L8" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="M8" s="11" t="n">
+      <c r="M8" s="8" t="n">
         <v>20.6</v>
       </c>
       <c r="N8" s="3" t="n">
@@ -1144,10 +1135,10 @@
       <c r="P8" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q8" s="11" t="n">
+      <c r="Q8" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1159,10 +1150,10 @@
       <c r="U8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="W8" s="11" t="n">
+      <c r="W8" s="8" t="n">
         <v>21.9</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1172,7 +1163,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0.6</v>
+        <v>20.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1190,13 +1181,13 @@
       <c r="C9" s="3" t="n">
         <v>178.3</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="8" t="n">
         <v>164.8</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="8" t="n">
         <v>96.90000000000001</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="8" t="n">
         <v>130.8</v>
       </c>
       <c r="G9" s="3" t="n">
@@ -1211,17 +1202,17 @@
       <c r="J9" s="3" t="n">
         <v>27.5</v>
       </c>
-      <c r="K9" s="10" t="n">
+      <c r="K9" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="L9" s="11" t="n">
+      <c r="L9" s="8" t="n">
         <v>100.2</v>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="M9" s="8" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>118.8</v>
+        <v>15.8</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>494.5</v>
@@ -1229,25 +1220,25 @@
       <c r="P9" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q9" s="11" t="n">
+      <c r="Q9" s="8" t="n">
         <v>149.6</v>
       </c>
-      <c r="R9" s="10" t="n">
+      <c r="R9" s="8" t="n">
         <v>121.9</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>135.7</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>2329.9</v>
+        <v>329.9</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="V9" s="10" t="n">
+      <c r="V9" s="8" t="n">
         <v>132.8</v>
       </c>
-      <c r="W9" s="11" t="n">
+      <c r="W9" s="8" t="n">
         <v>116.8</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1275,13 +1266,13 @@
       <c r="C10" s="3" t="n">
         <v>356.7</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="G10" s="3" t="n">
@@ -1297,10 +1288,10 @@
         <v>5.5</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="11" t="n">
+      <c r="L10" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="M10" s="11" t="n">
+      <c r="M10" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1312,10 +1303,10 @@
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="11" t="n">
+      <c r="Q10" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R10" s="10" t="n">
+      <c r="R10" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1327,10 +1318,10 @@
       <c r="U10" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="V10" s="10" t="n">
+      <c r="V10" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="W10" s="11" t="n">
+      <c r="W10" s="8" t="n">
         <v>23.4</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1358,13 +1349,13 @@
       <c r="C11" s="3" t="n">
         <v>265.6</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="G11" s="3" t="n">
@@ -1374,18 +1365,18 @@
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K11" s="11" t="n">
+      <c r="K11" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="M11" s="11" t="n">
+      <c r="M11" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1397,10 +1388,10 @@
       <c r="P11" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q11" s="11" t="n">
+      <c r="Q11" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R11" s="11" t="n">
+      <c r="R11" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="S11" s="3" t="n">
@@ -1412,10 +1403,10 @@
       <c r="U11" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V11" s="11" t="n">
+      <c r="V11" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1425,7 +1416,7 @@
         <v>84</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>159.8</v>
+        <v>5.7</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1443,13 +1434,13 @@
       <c r="C12" s="3" t="n">
         <v>347.1</v>
       </c>
-      <c r="D12" s="11" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E12" s="11" t="n">
+      <c r="D12" s="8" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E12" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="8" t="n">
         <v>27.2</v>
       </c>
       <c r="G12" s="3" t="n">
@@ -1464,43 +1455,43 @@
       <c r="J12" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="K12" s="11" t="n">
+      <c r="K12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="11" t="n">
+      <c r="M12" s="8" t="n">
         <v>23</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>27.5</v>
+        <v>97.5</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q12" s="11" t="n">
+      <c r="Q12" s="8" t="n">
         <v>31.8</v>
       </c>
-      <c r="R12" s="11" t="n">
+      <c r="R12" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>58.8</v>
+        <v>57.8</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="V12" s="11" t="n">
+      <c r="V12" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="W12" s="3" t="n">
+      <c r="W12" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X12" s="3" t="n">
@@ -1528,13 +1519,13 @@
       <c r="C13" s="3" t="n">
         <v>428.6</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="E13" s="11" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="F13" s="11" t="n">
+      <c r="E13" s="8" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F13" s="8" t="n">
         <v>26.6</v>
       </c>
       <c r="G13" s="3" t="n">
@@ -1549,13 +1540,13 @@
       <c r="J13" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K13" s="11" t="n">
+      <c r="K13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="M13" s="11" t="n">
+      <c r="M13" s="8" t="n">
         <v>21.9</v>
       </c>
       <c r="N13" s="3" t="n">
@@ -1567,10 +1558,10 @@
       <c r="P13" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q13" s="11" t="n">
+      <c r="Q13" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="R13" s="11" t="n">
+      <c r="R13" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1582,11 +1573,11 @@
       <c r="U13" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="V13" s="11" t="n">
+      <c r="V13" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="W13" s="9" t="n">
-        <v>2.4</v>
+      <c r="W13" s="8" t="n">
+        <v>24.8</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>29.3</v>
@@ -1595,7 +1586,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1613,13 +1604,13 @@
       <c r="C14" s="3" t="n">
         <v>190.3</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="8" t="n">
         <v>26.3</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1634,13 +1625,13 @@
       <c r="J14" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K14" s="11" t="n">
+      <c r="K14" s="8" t="n">
         <v>11.1</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="M14" s="11" t="n">
+      <c r="M14" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1652,10 +1643,10 @@
       <c r="P14" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q14" s="11" t="n">
+      <c r="Q14" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="R14" s="11" t="n">
+      <c r="R14" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1667,10 +1658,10 @@
       <c r="U14" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="V14" s="11" t="n">
+      <c r="V14" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="X14" s="3" t="n">
@@ -1698,16 +1689,16 @@
       <c r="C15" s="3" t="n">
         <v>359.6</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="8" t="n">
         <v>32.5</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="G15" s="3" t="n">
         <v>11.7</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1719,17 +1710,17 @@
       <c r="J15" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K15" s="11" t="n">
+      <c r="K15" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="L15" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="M15" s="11" t="n">
+      <c r="L15" s="8" t="n">
         <v>21.6</v>
       </c>
+      <c r="M15" s="8" t="n">
+        <v>21.6</v>
+      </c>
       <c r="N15" s="3" t="n">
-        <v>29.8</v>
+        <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>100</v>
@@ -1737,10 +1728,10 @@
       <c r="P15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="11" t="n">
+      <c r="Q15" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="R15" s="11" t="n">
+      <c r="R15" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1752,10 +1743,10 @@
       <c r="U15" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="V15" s="11" t="n">
+      <c r="V15" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1783,17 +1774,17 @@
       <c r="C16" s="3" t="n">
         <v>1591.2</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="9" t="n">
         <v>157.9</v>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E16" s="8" t="n">
         <v>105.5</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="8" t="n">
         <v>131.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>352.4</v>
+        <v>52.4</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>99.2</v>
@@ -1804,32 +1795,32 @@
       <c r="J16" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="K16" s="11" t="n">
+      <c r="K16" s="8" t="n">
         <v>36.8</v>
       </c>
-      <c r="L16" s="10" t="n">
-        <v>1110.6</v>
-      </c>
-      <c r="M16" s="11" t="n">
+      <c r="L16" s="8" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="M16" s="8" t="n">
         <v>109.5</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>130.7</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2490.1</v>
+        <v>490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q16" s="11" t="n">
+      <c r="Q16" s="8" t="n">
         <v>148.7</v>
       </c>
-      <c r="R16" s="11" t="n">
+      <c r="R16" s="8" t="n">
         <v>121.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1136.1</v>
+        <v>136.1</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>331.8</v>
@@ -1837,11 +1828,11 @@
       <c r="U16" s="3" t="n">
         <v>76.59999999999999</v>
       </c>
-      <c r="V16" s="11" t="n">
+      <c r="V16" s="8" t="n">
         <v>133.7</v>
       </c>
-      <c r="W16" s="10" t="n">
-        <v>2120.7</v>
+      <c r="W16" s="8" t="n">
+        <v>120.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>142.5</v>
@@ -1868,13 +1859,13 @@
       <c r="C17" s="3" t="n">
         <v>318.2</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="8" t="n">
         <v>31.6</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="8" t="n">
         <v>26.3</v>
       </c>
       <c r="G17" s="3" t="n">
@@ -1892,40 +1883,40 @@
       <c r="K17" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L17" s="10" t="n">
+      <c r="L17" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="M17" s="11" t="n">
+      <c r="M17" s="8" t="n">
         <v>21.9</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>298</v>
+        <v>98</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q17" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q17" s="8" t="n">
         <v>29.7</v>
       </c>
-      <c r="R17" s="11" t="n">
+      <c r="R17" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>22.2</v>
+        <v>27.2</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>166.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="V17" s="11" t="n">
+      <c r="V17" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="W17" s="10" t="n">
+      <c r="W17" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1953,13 +1944,13 @@
       <c r="C18" s="3" t="n">
         <v>368</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="8" t="n">
         <v>32.1</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="8" t="n">
         <v>26.7</v>
       </c>
       <c r="G18" s="3" t="n">
@@ -1980,22 +1971,22 @@
       <c r="L18" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="M18" s="11" t="n">
+      <c r="M18" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>197.3</v>
+        <v>97.3</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q18" s="11" t="n">
+      <c r="Q18" s="8" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="11" t="n">
+      <c r="R18" s="8" t="n">
         <v>25.2</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2007,17 +1998,17 @@
       <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="8" t="n">
         <v>28.5</v>
       </c>
-      <c r="W18" s="11" t="n">
+      <c r="W18" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>171.7</v>
+        <v>71.7</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>11</v>
@@ -2038,13 +2029,13 @@
       <c r="C19" s="3" t="n">
         <v>265.6</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="8" t="n">
         <v>30.4</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="8" t="n">
         <v>26.3</v>
       </c>
       <c r="G19" s="3" t="n">
@@ -2065,7 +2056,7 @@
       <c r="L19" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="M19" s="11" t="n">
+      <c r="M19" s="8" t="n">
         <v>22</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2077,10 +2068,10 @@
       <c r="P19" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q19" s="11" t="n">
+      <c r="Q19" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R19" s="11" t="n">
+      <c r="R19" s="8" t="n">
         <v>26</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2092,10 +2083,10 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="W19" s="11" t="n">
+      <c r="W19" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2105,7 +2096,7 @@
         <v>89</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>12.3</v>
+        <v>3.3</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2123,17 +2114,17 @@
       <c r="C20" s="3" t="n">
         <v>365.9</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="8" t="n">
         <v>26.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>29.9</v>
+        <v>9.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>20.6</v>
@@ -2150,22 +2141,22 @@
       <c r="L20" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M20" s="11" t="n">
+      <c r="M20" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>25.1</v>
+        <v>25.4</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q20" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q20" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="R20" s="11" t="n">
+      <c r="R20" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2177,20 +2168,20 @@
       <c r="U20" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="V20" s="9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="W20" s="11" t="n">
+      <c r="V20" s="8" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="W20" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2208,13 +2199,13 @@
       <c r="C21" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2235,7 +2226,7 @@
       <c r="L21" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M21" s="11" t="n">
+      <c r="M21" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2247,10 +2238,10 @@
       <c r="P21" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="11" t="n">
+      <c r="Q21" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R21" s="11" t="n">
+      <c r="R21" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2262,17 +2253,17 @@
       <c r="U21" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="W21" s="11" t="n">
+      <c r="W21" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>72.3</v>
+        <v>77.3</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>8.4</v>
@@ -2291,19 +2282,19 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2399.3</v>
-      </c>
-      <c r="D22" s="11" t="n">
+        <v>399.3</v>
+      </c>
+      <c r="D22" s="8" t="n">
         <v>32.9</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" s="8" t="n">
         <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1.1</v>
+        <v>11.8</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>19.8</v>
@@ -2320,26 +2311,26 @@
       <c r="L22" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="M22" s="11" t="n">
+      <c r="M22" s="8" t="n">
         <v>21</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q22" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q22" s="8" t="n">
         <v>32.4</v>
       </c>
-      <c r="R22" s="11" t="n">
+      <c r="R22" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>89.3</v>
+        <v>29.3</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>60.5</v>
@@ -2347,10 +2338,10 @@
       <c r="U22" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="W22" s="11" t="n">
+      <c r="W22" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2360,7 +2351,7 @@
         <v>86</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2378,13 +2369,13 @@
       <c r="C23" s="3" t="n">
         <v>1739.6</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="8" t="n">
         <v>157.5</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E23" s="8" t="n">
         <v>107.2</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F23" s="8" t="n">
         <v>132.4</v>
       </c>
       <c r="G23" s="3" t="n">
@@ -2399,28 +2390,28 @@
       <c r="J23" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="K23" s="10" t="n">
+      <c r="K23" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="L23" s="10" t="n">
+      <c r="L23" s="9" t="n">
         <v>108.2</v>
       </c>
-      <c r="M23" s="10" t="n">
-        <v>10.7</v>
+      <c r="M23" s="8" t="n">
+        <v>107</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>126.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>489.4</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q23" s="11" t="n">
+      <c r="Q23" s="8" t="n">
         <v>155.7</v>
       </c>
-      <c r="R23" s="11" t="n">
+      <c r="R23" s="8" t="n">
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2432,11 +2423,11 @@
       <c r="U23" s="3" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="V23" s="10" t="n">
+      <c r="V23" s="8" t="n">
         <v>134.4</v>
       </c>
-      <c r="W23" s="10" t="n">
-        <v>1120.3</v>
+      <c r="W23" s="8" t="n">
+        <v>120.3</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>140.8</v>
@@ -2463,13 +2454,13 @@
       <c r="C24" s="3" t="n">
         <v>347.9</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="D24" s="8" t="n">
         <v>31.5</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="8" t="n">
         <v>26.5</v>
       </c>
       <c r="G24" s="3" t="n">
@@ -2485,10 +2476,10 @@
         <v>3.9</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="10" t="n">
+      <c r="L24" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M24" s="11" t="n">
+      <c r="M24" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2498,16 +2489,16 @@
         <v>97.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q24" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q24" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R24" s="11" t="n">
+      <c r="R24" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>29.4</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>65.09999999999999</v>
@@ -2515,20 +2506,20 @@
       <c r="U24" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="V24" s="10" t="n">
+      <c r="V24" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="W24" s="11" t="n">
+      <c r="W24" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>22.2</v>
+        <v>28.2</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>17.3</v>
+        <v>7.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2546,13 +2537,13 @@
       <c r="C25" s="3" t="n">
         <v>106.7</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="E25" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="F25" s="11" t="n">
+      <c r="F25" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="G25" s="3" t="n">
@@ -2567,13 +2558,13 @@
       <c r="J25" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="K25" s="11" t="n">
+      <c r="K25" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="L25" s="11" t="n">
+      <c r="L25" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="M25" s="9" t="n">
+      <c r="M25" s="10" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2585,10 +2576,10 @@
       <c r="P25" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="Q25" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="R25" s="11" t="n">
+      <c r="R25" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2598,12 +2589,12 @@
         <v>84.40000000000001</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="V25" s="11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="V25" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="W25" s="11" t="n">
+      <c r="W25" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2629,19 +2620,19 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>290</v>
-      </c>
-      <c r="D26" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D26" s="8" t="n">
         <v>25.1</v>
       </c>
-      <c r="E26" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F26" s="11" t="n">
+      <c r="E26" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="F26" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>14.1</v>
+        <v>4.1</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>19.2</v>
@@ -2652,10 +2643,10 @@
       <c r="J26" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="K26" s="11" t="n">
+      <c r="K26" s="8" t="n">
         <v>6.7</v>
       </c>
-      <c r="L26" s="11" t="n">
+      <c r="L26" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="M26" s="3" t="n">
@@ -2670,10 +2661,10 @@
       <c r="P26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="R26" s="11" t="n">
+      <c r="R26" s="8" t="n">
         <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2683,12 +2674,12 @@
         <v>92</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V26" s="11" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="V26" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="W26" s="11" t="n">
+      <c r="W26" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2698,7 +2689,7 @@
         <v>91.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2716,13 +2707,13 @@
       <c r="C27" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D27" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="E27" s="11" t="n">
+      <c r="D27" s="8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E27" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F27" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="G27" s="3" t="n">
@@ -2737,10 +2728,10 @@
       <c r="J27" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K27" s="11" t="n">
+      <c r="K27" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="11" t="n">
+      <c r="L27" s="8" t="n">
         <v>20.7</v>
       </c>
       <c r="M27" s="3" t="n">
@@ -2750,15 +2741,15 @@
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>298</v>
+        <v>98</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="8" t="n">
         <v>28.8</v>
       </c>
-      <c r="R27" s="11" t="n">
+      <c r="R27" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2770,10 +2761,10 @@
       <c r="U27" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="V27" s="11" t="n">
+      <c r="V27" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="W27" s="11" t="n">
+      <c r="W27" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2783,7 +2774,7 @@
         <v>81.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>16.4</v>
+        <v>6.4</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2801,16 +2792,16 @@
       <c r="C28" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D28" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="E28" s="11" t="n">
+      <c r="D28" s="8" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E28" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="F28" s="11" t="n">
+      <c r="F28" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="G28" s="8" t="n">
+      <c r="G28" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2822,10 +2813,10 @@
       <c r="J28" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K28" s="11" t="n">
+      <c r="K28" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="11" t="n">
+      <c r="L28" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="M28" s="3" t="n">
@@ -2840,14 +2831,14 @@
       <c r="P28" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="8" t="n">
         <v>31.2</v>
       </c>
-      <c r="R28" s="11" t="n">
+      <c r="R28" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>2.7</v>
+        <v>27.2</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>60.2</v>
@@ -2855,10 +2846,10 @@
       <c r="U28" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="V28" s="11" t="n">
+      <c r="V28" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="W28" s="11" t="n">
+      <c r="W28" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2886,20 +2877,20 @@
       <c r="C29" s="3" t="n">
         <v>246.8</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="8" t="n">
         <v>31.5</v>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="E29" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="F29" s="11" t="n">
+      <c r="F29" s="8" t="n">
         <v>26</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="H29" s="8" t="n">
-        <v>69.2</v>
+      <c r="H29" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1.6</v>
@@ -2907,11 +2898,11 @@
       <c r="J29" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K29" s="11" t="n">
+      <c r="K29" s="8" t="n">
         <v>8.4</v>
       </c>
-      <c r="L29" s="11" t="n">
-        <v>20.1</v>
+      <c r="L29" s="8" t="n">
+        <v>21.1</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>20.6</v>
@@ -2920,30 +2911,30 @@
         <v>23.9</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>2.5</v>
+        <v>95.3</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="Q29" s="9" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="R29" s="11" t="n">
+      <c r="Q29" s="8" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="R29" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="V29" s="11" t="n">
+      <c r="V29" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="W29" s="11" t="n">
+      <c r="W29" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2971,20 +2962,20 @@
       <c r="C30" s="3" t="n">
         <v>1056.2</v>
       </c>
-      <c r="D30" s="10" t="n">
+      <c r="D30" s="8" t="n">
         <v>145.2</v>
       </c>
-      <c r="E30" s="10" t="n">
+      <c r="E30" s="8" t="n">
         <v>103.2</v>
       </c>
-      <c r="F30" s="11" t="n">
+      <c r="F30" s="8" t="n">
         <v>124.2</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>42</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>296.6</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>7.1</v>
@@ -2992,28 +2983,28 @@
       <c r="J30" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="K30" s="11" t="n">
+      <c r="K30" s="8" t="n">
         <v>38.8</v>
       </c>
-      <c r="L30" s="10" t="n">
+      <c r="L30" s="8" t="n">
         <v>106.5</v>
       </c>
-      <c r="M30" s="10" t="n">
+      <c r="M30" s="9" t="n">
         <v>105.2</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>123.9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>2487.6</v>
+        <v>487.6</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q30" s="10" t="n">
-        <v>1135.8</v>
-      </c>
-      <c r="R30" s="11" t="n">
+      <c r="Q30" s="8" t="n">
+        <v>135.8</v>
+      </c>
+      <c r="R30" s="8" t="n">
         <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3025,17 +3016,17 @@
       <c r="U30" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="V30" s="10" t="n">
-        <v>1126.1</v>
-      </c>
-      <c r="W30" s="11" t="n">
+      <c r="V30" s="8" t="n">
+        <v>126.1</v>
+      </c>
+      <c r="W30" s="8" t="n">
         <v>115.9</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>1428.7</v>
+        <v>24.7</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>25.8</v>
@@ -3056,13 +3047,13 @@
       <c r="C31" s="3" t="n">
         <v>211.2</v>
       </c>
-      <c r="D31" s="10" t="n">
+      <c r="D31" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="F31" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
@@ -3078,10 +3069,10 @@
         <v>2.2</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="11" t="n">
+      <c r="L31" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="M31" s="10" t="n">
+      <c r="M31" s="9" t="n">
         <v>21</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3093,10 +3084,10 @@
       <c r="P31" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q31" s="10" t="n">
+      <c r="Q31" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="R31" s="11" t="n">
+      <c r="R31" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3106,19 +3097,19 @@
         <v>79.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="V31" s="11" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="V31" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="W31" s="11" t="n">
+      <c r="W31" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>24.9</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>5.2</v>
@@ -3139,19 +3130,19 @@
       <c r="C32" s="3" t="n">
         <v>384.7</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E32" s="11" t="n">
+      <c r="E32" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="F32" s="11" t="n">
+      <c r="F32" s="8" t="n">
         <v>25.2</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="H32" s="8" t="n">
+      <c r="H32" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I32" s="3" t="n">
@@ -3160,17 +3151,17 @@
       <c r="J32" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="K32" s="11" t="n">
+      <c r="K32" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="11" t="n">
+      <c r="L32" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="M32" s="11" t="n">
+      <c r="M32" s="8" t="n">
         <v>20.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>100</v>
@@ -3178,7 +3169,7 @@
       <c r="P32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" s="11" t="n">
+      <c r="Q32" s="8" t="n">
         <v>31.1</v>
       </c>
       <c r="R32" s="3" t="n">
@@ -3193,20 +3184,20 @@
       <c r="U32" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="V32" s="11" t="n">
+      <c r="V32" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>746.6</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>195.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3224,13 +3215,13 @@
       <c r="C33" s="3" t="n">
         <v>213.3</v>
       </c>
-      <c r="D33" s="9" t="n">
-        <v>22.92</v>
-      </c>
-      <c r="E33" s="11" t="n">
+      <c r="D33" s="8" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E33" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="F33" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="G33" s="3" t="n">
@@ -3240,34 +3231,34 @@
         <v>18.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="K33" s="11" t="n">
+      <c r="K33" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="L33" s="11" t="n">
+      <c r="L33" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="M33" s="11" t="n">
+      <c r="M33" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>99</v>
+        <v>99.7</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="11" t="n">
+      <c r="Q33" s="8" t="n">
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>21.6</v>
+        <v>22.6</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.2</v>
@@ -3278,10 +3269,10 @@
       <c r="U33" s="3" t="n">
         <v>11.5</v>
       </c>
-      <c r="V33" s="11" t="n">
+      <c r="V33" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3291,7 +3282,7 @@
         <v>0.1</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3309,13 +3300,13 @@
       <c r="C34" s="3" t="n">
         <v>311.6</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="E34" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="F34" s="8" t="n">
         <v>26.7</v>
       </c>
       <c r="G34" s="3" t="n">
@@ -3330,29 +3321,29 @@
       <c r="J34" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K34" s="11" t="n">
+      <c r="K34" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="L34" s="11" t="n">
+      <c r="L34" s="8" t="n">
         <v>21.8</v>
       </c>
-      <c r="M34" s="11" t="n">
+      <c r="M34" s="8" t="n">
         <v>21.7</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="11" t="n">
+      <c r="Q34" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="R34" s="8" t="n">
-        <v>35.8</v>
+      <c r="R34" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>30.2</v>
@@ -3363,10 +3354,10 @@
       <c r="U34" s="3" t="n">
         <v>13.3</v>
       </c>
-      <c r="V34" s="11" t="n">
+      <c r="V34" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3376,7 +3367,7 @@
         <v>82</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3392,15 +3383,15 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>353.1</v>
+        <v>353.4</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E35" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="F35" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3415,32 +3406,32 @@
       <c r="J35" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K35" s="11" t="n">
+      <c r="K35" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="11" t="n">
+      <c r="L35" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M35" s="11" t="n">
+      <c r="M35" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>297.2</v>
+        <v>97.2</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q35" s="11" t="n">
+      <c r="Q35" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="9" t="n">
-        <v>46.9</v>
+      <c r="R35" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>27.8</v>
+        <v>27.5</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>61.3</v>
@@ -3448,17 +3439,17 @@
       <c r="U35" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="V35" s="11" t="n">
+      <c r="V35" s="8" t="n">
         <v>27.8</v>
       </c>
       <c r="W35" s="8" t="n">
-        <v>16.6</v>
+        <v>24.6</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8.4</v>
@@ -3477,15 +3468,15 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>430.7</v>
-      </c>
-      <c r="D36" s="3" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="D36" s="8" t="n">
         <v>32.1</v>
       </c>
-      <c r="E36" s="11" t="n">
+      <c r="E36" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="F36" s="11" t="n">
+      <c r="F36" s="8" t="n">
         <v>26.5</v>
       </c>
       <c r="G36" s="3" t="n">
@@ -3500,13 +3491,13 @@
       <c r="J36" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K36" s="11" t="n">
+      <c r="K36" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="L36" s="11" t="n">
+      <c r="L36" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="M36" s="11" t="n">
+      <c r="M36" s="8" t="n">
         <v>20.7</v>
       </c>
       <c r="N36" s="3" t="n">
@@ -3518,7 +3509,7 @@
       <c r="P36" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="11" t="n">
+      <c r="Q36" s="8" t="n">
         <v>32.1</v>
       </c>
       <c r="R36" s="3" t="n">
@@ -3533,20 +3524,20 @@
       <c r="U36" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="V36" s="11" t="n">
+      <c r="V36" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>28.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>172</v>
+        <v>72</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3564,13 +3555,13 @@
       <c r="C37" s="3" t="n">
         <v>1693.7</v>
       </c>
-      <c r="D37" s="10" t="n">
-        <v>14155.4</v>
-      </c>
-      <c r="E37" s="11" t="n">
-        <v>102</v>
-      </c>
-      <c r="F37" s="11" t="n">
+      <c r="D37" s="8" t="n">
+        <v>155.4</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="F37" s="8" t="n">
         <v>128.7</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3585,13 +3576,13 @@
       <c r="J37" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="K37" s="11" t="n">
+      <c r="K37" s="8" t="n">
         <v>35.6</v>
       </c>
-      <c r="L37" s="10" t="n">
-        <v>1106</v>
-      </c>
-      <c r="M37" s="11" t="n">
+      <c r="L37" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="M37" s="8" t="n">
         <v>105.2</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3603,35 +3594,35 @@
       <c r="P37" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="Q37" s="11" t="n">
+      <c r="Q37" s="8" t="n">
         <v>153.7</v>
       </c>
-      <c r="R37" s="10" t="n">
+      <c r="R37" s="9" t="n">
         <v>126.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>1143.1</v>
+        <v>143.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>2324.8</v>
+        <v>324.8</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="V37" s="11" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="V37" s="8" t="n">
         <v>136.8</v>
       </c>
-      <c r="W37" s="10" t="n">
+      <c r="W37" s="8" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>122.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>392.2</v>
+        <v>398.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>139.7</v>
+        <v>39.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3649,13 +3640,13 @@
       <c r="C38" s="3" t="n">
         <v>338.7</v>
       </c>
-      <c r="D38" s="10" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E38" s="11" t="n">
+      <c r="D38" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="E38" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="F38" s="8" t="n">
         <v>25.7</v>
       </c>
       <c r="G38" s="3" t="n">
@@ -3671,25 +3662,25 @@
         <v>3.6</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="11" t="n">
+      <c r="L38" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="M38" s="11" t="n">
+      <c r="M38" s="8" t="n">
         <v>21</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q38" s="11" t="n">
+      <c r="Q38" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="R38" s="10" t="n">
+      <c r="R38" s="9" t="n">
         <v>25.2</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3701,17 +3692,17 @@
       <c r="U38" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="V38" s="10" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="W38" s="10" t="n">
+      <c r="V38" s="8" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="W38" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>29.1</v>
+        <v>78</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>7.9</v>
@@ -3732,13 +3723,13 @@
       <c r="C39" s="3" t="n">
         <v>332.5</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="E39" s="11" t="n">
+      <c r="E39" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F39" s="11" t="n">
+      <c r="F39" s="8" t="n">
         <v>26.1</v>
       </c>
       <c r="G39" s="3" t="n">
@@ -3754,12 +3745,12 @@
         <v>3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L39" s="11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L39" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="M39" s="11" t="n">
+      <c r="M39" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3771,25 +3762,25 @@
       <c r="P39" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q39" s="11" t="n">
+      <c r="Q39" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="R39" s="11" t="n">
+      <c r="R39" s="8" t="n">
         <v>26</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>163.2</v>
+        <v>63.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>18.3</v>
+        <v>17.3</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="W39" s="11" t="n">
+      <c r="W39" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3799,7 +3790,7 @@
         <v>88.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>23.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3815,15 +3806,15 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1453.7</v>
-      </c>
-      <c r="D40" s="3" t="n">
+        <v>453.7</v>
+      </c>
+      <c r="D40" s="8" t="n">
         <v>32.9</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="E40" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="G40" s="3" t="n">
@@ -3833,7 +3824,7 @@
         <v>18.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.7</v>
+        <v>22.7</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>5</v>
@@ -3841,10 +3832,10 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="11" t="n">
+      <c r="L40" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="M40" s="11" t="n">
+      <c r="M40" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="N40" s="3" t="n">
@@ -3856,10 +3847,10 @@
       <c r="P40" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q40" s="11" t="n">
+      <c r="Q40" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="R40" s="11" t="n">
+      <c r="R40" s="8" t="n">
         <v>26</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3874,7 +3865,7 @@
       <c r="V40" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W40" s="11" t="n">
+      <c r="W40" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3905,10 +3896,10 @@
       <c r="D41" s="8" t="n">
         <v>31.6</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E41" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="F41" s="11" t="n">
+      <c r="F41" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="G41" s="3" t="n">
@@ -3926,10 +3917,10 @@
       <c r="K41" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="L41" s="11" t="n">
+      <c r="L41" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="M41" s="11" t="n">
+      <c r="M41" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3941,10 +3932,10 @@
       <c r="P41" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q41" s="11" t="n">
+      <c r="Q41" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="R41" s="11" t="n">
+      <c r="R41" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="S41" s="3" t="n">
@@ -3956,17 +3947,17 @@
       <c r="U41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V41" s="8" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W41" s="11" t="n">
+      <c r="V41" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="W41" s="8" t="n">
         <v>23.4</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>28</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>190.5</v>
+        <v>90.5</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>2.9</v>
@@ -3987,13 +3978,13 @@
       <c r="C42" s="3" t="n">
         <v>236.3</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="8" t="n">
         <v>31.6</v>
       </c>
-      <c r="E42" s="11" t="n">
+      <c r="E42" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="F42" s="11" t="n">
+      <c r="F42" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="G42" s="3" t="n">
@@ -4011,40 +4002,40 @@
       <c r="K42" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="L42" s="11" t="n">
+      <c r="L42" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="M42" s="11" t="n">
+      <c r="M42" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>26</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="11" t="n">
+      <c r="Q42" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="R42" s="11" t="n">
+      <c r="R42" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>29.3</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>97.2</v>
+        <v>97.7</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="W42" s="11" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="W42" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4070,13 +4061,13 @@
       <c r="C43" s="3" t="n">
         <v>372.2</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="D43" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E43" s="11" t="n">
+      <c r="E43" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="F43" s="8" t="n">
         <v>25.7</v>
       </c>
       <c r="G43" s="3" t="n">
@@ -4094,10 +4085,10 @@
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="11" t="n">
+      <c r="L43" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M43" s="11" t="n">
+      <c r="M43" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="N43" s="3" t="n">
@@ -4109,14 +4100,14 @@
       <c r="P43" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q43" s="11" t="n">
+      <c r="Q43" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="R43" s="11" t="n">
+      <c r="R43" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>30.4</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>75.59999999999999</v>
@@ -4127,7 +4118,7 @@
       <c r="V43" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W43" s="11" t="n">
+      <c r="W43" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="X43" s="3" t="n">
@@ -4155,34 +4146,34 @@
       <c r="C44" s="3" t="n">
         <v>365.9</v>
       </c>
-      <c r="D44" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E44" s="11" t="n">
+      <c r="D44" s="8" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E44" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="F44" s="11" t="n">
+      <c r="F44" s="8" t="n">
         <v>26.9</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="H44" s="8" t="n">
-        <v>49.4</v>
+      <c r="H44" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>8.6</v>
+        <v>3.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="11" t="n">
+      <c r="L44" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="M44" s="11" t="n">
+      <c r="M44" s="8" t="n">
         <v>22.3</v>
       </c>
       <c r="N44" s="3" t="n">
@@ -4194,10 +4185,10 @@
       <c r="P44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" s="11" t="n">
+      <c r="Q44" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="R44" s="11" t="n">
+      <c r="R44" s="8" t="n">
         <v>26.4</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4210,19 +4201,19 @@
         <v>18.6</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="W44" s="11" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W44" s="8" t="n">
         <v>26.3</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>32.2</v>
+        <v>32.8</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>184.4</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4240,71 +4231,71 @@
       <c r="C45" s="3" t="n">
         <v>202.6</v>
       </c>
-      <c r="D45" s="10" t="n">
+      <c r="D45" s="8" t="n">
         <v>190.6</v>
       </c>
-      <c r="E45" s="10" t="n">
-        <v>1121.5</v>
-      </c>
-      <c r="F45" s="10" t="n">
+      <c r="E45" s="8" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="F45" s="9" t="n">
         <v>156.3</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>69.09999999999999</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>1114.7</v>
+        <v>114.7</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>101.2</v>
+        <v>10.2</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="K45" s="10" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="L45" s="10" t="n">
-        <v>126.3</v>
-      </c>
-      <c r="M45" s="10" t="n">
-        <v>10122.9</v>
+      <c r="K45" s="9" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="M45" s="8" t="n">
+        <v>125.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1148.7</v>
+        <v>148.7</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>293.8</v>
+        <v>593.8</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q45" s="11" t="n">
+      <c r="Q45" s="8" t="n">
         <v>172.8</v>
       </c>
-      <c r="R45" s="11" t="n">
+      <c r="R45" s="8" t="n">
         <v>149.1</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>174.1</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>2430</v>
+        <v>250</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="V45" s="10" t="n">
+      <c r="V45" s="9" t="n">
         <v>158.1</v>
       </c>
-      <c r="W45" s="11" t="n">
+      <c r="W45" s="8" t="n">
         <v>144.9</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>172.2</v>
+        <v>172.5</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>583.7</v>
+        <v>503.7</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>34</v>
@@ -4323,15 +4314,15 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>237.6</v>
-      </c>
-      <c r="D46" s="10" t="n">
+        <v>337.6</v>
+      </c>
+      <c r="D46" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="E46" s="11" t="n">
+      <c r="E46" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F46" s="11" t="n">
+      <c r="F46" s="8" t="n">
         <v>26</v>
       </c>
       <c r="G46" s="3" t="n">
@@ -4347,12 +4338,12 @@
         <v>3.1</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L46" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L46" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="M46" s="11" t="n">
+      <c r="M46" s="8" t="n">
         <v>21</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4364,11 +4355,11 @@
       <c r="P46" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="11" t="n">
+      <c r="Q46" s="8" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="10" t="n">
-        <v>21.8</v>
+      <c r="R46" s="8" t="n">
+        <v>24.8</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>29</v>
@@ -4379,17 +4370,17 @@
       <c r="U46" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V46" s="10" t="n">
+      <c r="V46" s="9" t="n">
         <v>26.3</v>
       </c>
-      <c r="W46" s="11" t="n">
+      <c r="W46" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>823.9</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>5.7</v>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>22.3</v>
+        <v>122.3</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>34.2</v>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>178.3</v>
+        <v>1783.5</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>164.8</v>
@@ -1212,7 +1212,7 @@
         <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>15.8</v>
+        <v>115.8</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>494.5</v>
@@ -1248,7 +1248,7 @@
         <v>388.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>41.6</v>
+        <v>22.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1287,7 +1287,9 @@
       <c r="J10" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L10" s="8" t="n">
         <v>20</v>
       </c>
@@ -1435,7 +1437,7 @@
         <v>347.1</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>31.2</v>
+        <v>31.8</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>22.6</v>
@@ -1774,7 +1776,7 @@
       <c r="C16" s="3" t="n">
         <v>1591.2</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="8" t="n">
         <v>157.9</v>
       </c>
       <c r="E16" s="8" t="n">
@@ -2294,7 +2296,7 @@
         <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>11.8</v>
+        <v>118.2</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>19.8</v>
@@ -2308,8 +2310,8 @@
       <c r="K22" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="L22" s="3" t="n">
-        <v>21.3</v>
+      <c r="L22" s="10" t="n">
+        <v>22.13</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>21</v>
@@ -2403,7 +2405,7 @@
         <v>126.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>489.4</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.2</v>
@@ -2671,7 +2673,7 @@
         <v>28</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>92</v>
+        <v>28.2</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>22.9</v>
@@ -2741,7 +2743,7 @@
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.4</v>
@@ -2808,7 +2810,7 @@
         <v>18.9</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.8</v>
@@ -2829,7 +2831,7 @@
         <v>97.3</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q28" s="8" t="n">
         <v>31.2</v>
@@ -3004,8 +3006,8 @@
       <c r="Q30" s="8" t="n">
         <v>135.8</v>
       </c>
-      <c r="R30" s="8" t="n">
-        <v>120.7</v>
+      <c r="R30" s="9" t="n">
+        <v>1207.2</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>140.9</v>
@@ -3014,7 +3016,7 @@
         <v>396.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="V30" s="8" t="n">
         <v>126.1</v>
@@ -3026,7 +3028,7 @@
         <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>24.7</v>
+        <v>424.7</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>25.8</v>
@@ -3066,7 +3068,7 @@
         <v>1.4</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="8" t="n">
@@ -3097,7 +3099,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="V31" s="8" t="n">
         <v>25.2</v>
@@ -3172,7 +3174,7 @@
       <c r="Q32" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3187,7 +3189,7 @@
       <c r="V32" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="W32" s="8" t="n">
+      <c r="W32" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3249,7 +3251,7 @@
         <v>25.4</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>99.7</v>
+        <v>99</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0.2</v>
@@ -3257,8 +3259,8 @@
       <c r="Q33" s="8" t="n">
         <v>28.9</v>
       </c>
-      <c r="R33" s="3" t="n">
-        <v>22.6</v>
+      <c r="R33" s="8" t="n">
+        <v>24.6</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.2</v>
@@ -3272,7 +3274,7 @@
       <c r="V33" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3342,7 +3344,7 @@
       <c r="Q34" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3357,7 +3359,7 @@
       <c r="V34" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="W34" s="8" t="n">
+      <c r="W34" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3427,7 +3429,7 @@
       <c r="Q35" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3442,14 +3444,14 @@
       <c r="V35" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="W35" s="8" t="n">
-        <v>24.6</v>
+      <c r="W35" s="3" t="n">
+        <v>26.6</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>77.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8.4</v>
@@ -3468,7 +3470,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>30.7</v>
+        <v>430.7</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>32.1</v>
@@ -3512,7 +3514,7 @@
       <c r="Q36" s="8" t="n">
         <v>32.1</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="8" t="n">
         <v>26</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3527,7 +3529,7 @@
       <c r="V36" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="8" t="n">
+      <c r="W36" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3558,8 +3560,8 @@
       <c r="D37" s="8" t="n">
         <v>155.4</v>
       </c>
-      <c r="E37" s="9" t="n">
-        <v>102.2</v>
+      <c r="E37" s="8" t="n">
+        <v>102</v>
       </c>
       <c r="F37" s="8" t="n">
         <v>128.7</v>
@@ -3597,7 +3599,7 @@
       <c r="Q37" s="8" t="n">
         <v>153.7</v>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="R37" s="8" t="n">
         <v>126.2</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3612,14 +3614,14 @@
       <c r="V37" s="8" t="n">
         <v>136.8</v>
       </c>
-      <c r="W37" s="8" t="n">
+      <c r="W37" s="9" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>122.4</v>
+        <v>142.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>398.2</v>
+        <v>392.2</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>39.7</v>
@@ -3680,7 +3682,7 @@
       <c r="Q38" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="8" t="n">
         <v>25.2</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3695,14 +3697,14 @@
       <c r="V38" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="W38" s="8" t="n">
+      <c r="W38" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>78</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>7.9</v>
@@ -3726,8 +3728,8 @@
       <c r="D39" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="E39" s="8" t="n">
-        <v>20.2</v>
+      <c r="E39" s="10" t="n">
+        <v>22.02</v>
       </c>
       <c r="F39" s="8" t="n">
         <v>26.1</v>
@@ -3745,7 +3747,7 @@
         <v>3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L39" s="8" t="n">
         <v>21</v>
@@ -3777,7 +3779,7 @@
       <c r="U39" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="W39" s="8" t="n">
@@ -3811,7 +3813,7 @@
       <c r="D40" s="8" t="n">
         <v>32.9</v>
       </c>
-      <c r="E40" s="8" t="n">
+      <c r="E40" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="F40" s="8" t="n">
@@ -3824,7 +3826,7 @@
         <v>18.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>22.7</v>
+        <v>2.7</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>5</v>
@@ -3862,7 +3864,7 @@
       <c r="U40" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="8" t="n">
         <v>27.8</v>
       </c>
       <c r="W40" s="8" t="n">
@@ -3896,7 +3898,7 @@
       <c r="D41" s="8" t="n">
         <v>31.6</v>
       </c>
-      <c r="E41" s="8" t="n">
+      <c r="E41" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="F41" s="8" t="n">
@@ -3947,7 +3949,7 @@
       <c r="U41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="W41" s="8" t="n">
@@ -3981,7 +3983,7 @@
       <c r="D42" s="8" t="n">
         <v>31.6</v>
       </c>
-      <c r="E42" s="8" t="n">
+      <c r="E42" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="F42" s="8" t="n">
@@ -3997,7 +3999,7 @@
         <v>0.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>28.7</v>
@@ -4032,8 +4034,8 @@
       <c r="U42" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="V42" s="3" t="n">
-        <v>22.7</v>
+      <c r="V42" s="8" t="n">
+        <v>24.7</v>
       </c>
       <c r="W42" s="8" t="n">
         <v>23.5</v>
@@ -4064,7 +4066,7 @@
       <c r="D43" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E43" s="8" t="n">
+      <c r="E43" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="F43" s="8" t="n">
@@ -4115,7 +4117,7 @@
       <c r="U43" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V43" s="3" t="n">
+      <c r="V43" s="8" t="n">
         <v>27.8</v>
       </c>
       <c r="W43" s="8" t="n">
@@ -4149,7 +4151,7 @@
       <c r="D44" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="E44" s="8" t="n">
+      <c r="E44" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="F44" s="8" t="n">
@@ -4200,7 +4202,7 @@
       <c r="U44" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="V44" s="3" t="n">
+      <c r="V44" s="8" t="n">
         <v>28.5</v>
       </c>
       <c r="W44" s="8" t="n">
@@ -4229,13 +4231,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>202.6</v>
+        <v>2026.2</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>190.6</v>
       </c>
-      <c r="E45" s="8" t="n">
-        <v>121.5</v>
+      <c r="E45" s="9" t="n">
+        <v>1215.2</v>
       </c>
       <c r="F45" s="9" t="n">
         <v>156.3</v>
@@ -4253,7 +4255,7 @@
         <v>18.4</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>72.3</v>
+        <v>78.3</v>
       </c>
       <c r="L45" s="8" t="n">
         <v>126.5</v>
@@ -4280,12 +4282,12 @@
         <v>174.1</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="V45" s="9" t="n">
+      <c r="V45" s="8" t="n">
         <v>158.1</v>
       </c>
       <c r="W45" s="8" t="n">
@@ -4319,7 +4321,7 @@
       <c r="D46" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="E46" s="8" t="n">
+      <c r="E46" s="9" t="n">
         <v>20.2</v>
       </c>
       <c r="F46" s="8" t="n">
@@ -4355,8 +4357,8 @@
       <c r="P46" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="8" t="n">
-        <v>28.8</v>
+      <c r="Q46" s="9" t="n">
+        <v>228.8</v>
       </c>
       <c r="R46" s="8" t="n">
         <v>24.8</v>
@@ -4370,7 +4372,7 @@
       <c r="U46" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V46" s="9" t="n">
+      <c r="V46" s="8" t="n">
         <v>26.3</v>
       </c>
       <c r="W46" s="8" t="n">
@@ -4380,7 +4382,7 @@
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>5.7</v>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>122.3</v>
+        <v>422.3</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>34.2</v>
@@ -1163,7 +1163,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>20.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1783.5</v>
+        <v>178.3</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>164.8</v>
@@ -1248,7 +1248,7 @@
         <v>388.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>22.8</v>
+        <v>41.6</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1287,9 +1287,7 @@
       <c r="J10" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="8" t="n">
         <v>20</v>
       </c>
@@ -1883,7 +1881,7 @@
         <v>3.9</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>22.1</v>
@@ -2296,7 +2294,7 @@
         <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>118.2</v>
+        <v>16.8</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>19.8</v>
@@ -2310,8 +2308,8 @@
       <c r="K22" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="L22" s="10" t="n">
-        <v>22.13</v>
+      <c r="L22" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>21</v>
@@ -2673,10 +2671,10 @@
         <v>28</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>28.2</v>
+        <v>92</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>22.9</v>
+        <v>2</v>
       </c>
       <c r="V26" s="8" t="n">
         <v>23.8</v>
@@ -2743,7 +2741,7 @@
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.4</v>
@@ -2810,7 +2808,7 @@
         <v>18.9</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.8</v>
@@ -3006,8 +3004,8 @@
       <c r="Q30" s="8" t="n">
         <v>135.8</v>
       </c>
-      <c r="R30" s="9" t="n">
-        <v>1207.2</v>
+      <c r="R30" s="8" t="n">
+        <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>140.9</v>
@@ -3016,7 +3014,7 @@
         <v>396.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>26</v>
+        <v>10.5</v>
       </c>
       <c r="V30" s="8" t="n">
         <v>126.1</v>
@@ -3047,7 +3045,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>211.2</v>
+        <v>21.1</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>29</v>
@@ -3068,7 +3066,7 @@
         <v>1.4</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="8" t="n">
@@ -3099,7 +3097,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>18.1</v>
+        <v>8.1</v>
       </c>
       <c r="V31" s="8" t="n">
         <v>25.2</v>
@@ -3189,7 +3187,7 @@
       <c r="V32" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3274,7 +3272,7 @@
       <c r="V33" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3359,7 +3357,7 @@
       <c r="V34" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3444,8 +3442,8 @@
       <c r="V35" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="W35" s="3" t="n">
-        <v>26.6</v>
+      <c r="W35" s="8" t="n">
+        <v>24.6</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>28.9</v>
@@ -3529,7 +3527,7 @@
       <c r="V36" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3573,7 +3571,7 @@
         <v>96.5</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>110.1</v>
+        <v>10.1</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>18.1</v>
@@ -3614,14 +3612,14 @@
       <c r="V37" s="8" t="n">
         <v>136.8</v>
       </c>
-      <c r="W37" s="9" t="n">
+      <c r="W37" s="8" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>142.4</v>
+        <v>182.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>392.2</v>
+        <v>398.2</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>39.7</v>
@@ -3697,7 +3695,7 @@
       <c r="V38" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3728,8 +3726,8 @@
       <c r="D39" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="E39" s="10" t="n">
-        <v>22.02</v>
+      <c r="E39" s="8" t="n">
+        <v>20.2</v>
       </c>
       <c r="F39" s="8" t="n">
         <v>26.1</v>
@@ -3813,7 +3811,7 @@
       <c r="D40" s="8" t="n">
         <v>32.9</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="F40" s="8" t="n">
@@ -3874,7 +3872,7 @@
         <v>26.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>10.4</v>
@@ -3898,7 +3896,7 @@
       <c r="D41" s="8" t="n">
         <v>31.6</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="F41" s="8" t="n">
@@ -3983,7 +3981,7 @@
       <c r="D42" s="8" t="n">
         <v>31.6</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="8" t="n">
         <v>20.3</v>
       </c>
       <c r="F42" s="8" t="n">
@@ -4066,7 +4064,7 @@
       <c r="D43" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="F43" s="8" t="n">
@@ -4151,7 +4149,7 @@
       <c r="D44" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="F44" s="8" t="n">
@@ -4231,13 +4229,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2026.2</v>
+        <v>202.6</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>190.6</v>
       </c>
-      <c r="E45" s="9" t="n">
-        <v>1215.2</v>
+      <c r="E45" s="8" t="n">
+        <v>121.5</v>
       </c>
       <c r="F45" s="9" t="n">
         <v>156.3</v>
@@ -4321,7 +4319,7 @@
       <c r="D46" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="8" t="n">
         <v>20.2</v>
       </c>
       <c r="F46" s="8" t="n">
@@ -4340,7 +4338,7 @@
         <v>3.1</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="8" t="n">
         <v>21.1</v>
@@ -4357,8 +4355,8 @@
       <c r="P46" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="9" t="n">
-        <v>228.8</v>
+      <c r="Q46" s="8" t="n">
+        <v>28.8</v>
       </c>
       <c r="R46" s="8" t="n">
         <v>24.8</v>
@@ -4382,7 +4380,7 @@
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>83.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>5.7</v>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -153,6 +165,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -789,7 +807,7 @@
       <c r="J4" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
@@ -874,7 +892,7 @@
       <c r="J5" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
@@ -959,7 +977,7 @@
       <c r="J6" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
@@ -1044,7 +1062,7 @@
       <c r="J7" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
@@ -1129,7 +1147,7 @@
       <c r="J8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="10" t="n">
         <v>30.9</v>
       </c>
       <c r="L8" s="3" t="n">
@@ -1214,7 +1232,7 @@
       <c r="J9" s="3" t="n">
         <v>27.5</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="10" t="n">
         <v>30.9</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1805,7 +1823,7 @@
       <c r="J16" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="K16" s="3" t="n"/>
+      <c r="K16" s="13" t="n"/>
       <c r="L16" s="3" t="n"/>
       <c r="M16" s="3" t="n">
         <v>109.5</v>
@@ -1969,7 +1987,7 @@
       <c r="J18" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="K18" s="3" t="n"/>
+      <c r="K18" s="14" t="n"/>
       <c r="L18" s="3" t="n">
         <v>22.1</v>
       </c>
@@ -2392,7 +2410,7 @@
       <c r="J23" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="12" t="n">
         <v>7.7</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -2987,7 +3005,7 @@
       <c r="J30" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="12" t="n">
         <v>38.8</v>
       </c>
       <c r="L30" s="3" t="n">
@@ -3582,7 +3600,7 @@
       <c r="J37" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="12" t="n">
         <v>35.6</v>
       </c>
       <c r="L37" s="3" t="n">
@@ -4262,7 +4280,7 @@
       <c r="J45" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
